--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="709">
   <si>
     <t>IDSocio</t>
   </si>
@@ -103,115 +103,148 @@
     <t>Rutina</t>
   </si>
   <si>
+    <t>124299</t>
+  </si>
+  <si>
+    <t>333792</t>
+  </si>
+  <si>
     <t>159273</t>
   </si>
   <si>
     <t>293612</t>
   </si>
   <si>
-    <t>124299</t>
-  </si>
-  <si>
     <t>206537</t>
   </si>
   <si>
-    <t>333792</t>
+    <t>340226</t>
+  </si>
+  <si>
+    <t>340323</t>
   </si>
   <si>
     <t>340078</t>
   </si>
   <si>
-    <t>340226</t>
+    <t>340119</t>
   </si>
   <si>
     <t>340206</t>
   </si>
   <si>
+    <t>340511</t>
+  </si>
+  <si>
+    <t>341231</t>
+  </si>
+  <si>
+    <t>341246</t>
+  </si>
+  <si>
+    <t>340800</t>
+  </si>
+  <si>
+    <t>340894</t>
+  </si>
+  <si>
+    <t>341004</t>
+  </si>
+  <si>
+    <t>340796</t>
+  </si>
+  <si>
+    <t>341089</t>
+  </si>
+  <si>
+    <t>342032</t>
+  </si>
+  <si>
+    <t>342083</t>
+  </si>
+  <si>
+    <t>340214</t>
+  </si>
+  <si>
+    <t>340507</t>
+  </si>
+  <si>
     <t>340218</t>
   </si>
   <si>
-    <t>340119</t>
-  </si>
-  <si>
-    <t>340323</t>
-  </si>
-  <si>
-    <t>340214</t>
-  </si>
-  <si>
-    <t>340511</t>
-  </si>
-  <si>
-    <t>340800</t>
-  </si>
-  <si>
-    <t>340507</t>
-  </si>
-  <si>
-    <t>340796</t>
+    <t>340995</t>
+  </si>
+  <si>
+    <t>341943</t>
+  </si>
+  <si>
+    <t>342352</t>
+  </si>
+  <si>
+    <t>342553</t>
+  </si>
+  <si>
+    <t>342771</t>
+  </si>
+  <si>
+    <t>341574</t>
+  </si>
+  <si>
+    <t>342555</t>
   </si>
   <si>
     <t>340774</t>
   </si>
   <si>
-    <t>341004</t>
-  </si>
-  <si>
-    <t>340995</t>
-  </si>
-  <si>
-    <t>341089</t>
-  </si>
-  <si>
-    <t>341231</t>
-  </si>
-  <si>
-    <t>341246</t>
+    <t>342629</t>
   </si>
   <si>
     <t>342121</t>
   </si>
   <si>
+    <t>342837</t>
+  </si>
+  <si>
+    <t>343039</t>
+  </si>
+  <si>
+    <t>342458</t>
+  </si>
+  <si>
+    <t>344063</t>
+  </si>
+  <si>
     <t>341476</t>
   </si>
   <si>
-    <t>341574</t>
-  </si>
-  <si>
-    <t>342032</t>
-  </si>
-  <si>
-    <t>342083</t>
-  </si>
-  <si>
-    <t>342352</t>
+    <t>342571</t>
+  </si>
+  <si>
+    <t>342767</t>
+  </si>
+  <si>
+    <t>343524</t>
+  </si>
+  <si>
+    <t>343605</t>
+  </si>
+  <si>
+    <t>343924</t>
+  </si>
+  <si>
+    <t>343964</t>
   </si>
   <si>
     <t>341958</t>
   </si>
   <si>
+    <t>343260</t>
+  </si>
+  <si>
     <t>342022</t>
   </si>
   <si>
-    <t>341943</t>
-  </si>
-  <si>
-    <t>342458</t>
-  </si>
-  <si>
-    <t>342767</t>
-  </si>
-  <si>
-    <t>342555</t>
-  </si>
-  <si>
-    <t>342629</t>
-  </si>
-  <si>
-    <t>342553</t>
-  </si>
-  <si>
-    <t>343039</t>
+    <t>344072</t>
   </si>
   <si>
     <t>342563</t>
@@ -223,139 +256,157 @@
     <t>342575</t>
   </si>
   <si>
-    <t>342571</t>
-  </si>
-  <si>
-    <t>342771</t>
-  </si>
-  <si>
     <t>342772</t>
   </si>
   <si>
-    <t>342837</t>
-  </si>
-  <si>
-    <t>343524</t>
-  </si>
-  <si>
-    <t>343605</t>
-  </si>
-  <si>
-    <t>343260</t>
-  </si>
-  <si>
     <t>343556</t>
   </si>
   <si>
+    <t>344302</t>
+  </si>
+  <si>
+    <t>21981</t>
+  </si>
+  <si>
+    <t>17659</t>
+  </si>
+  <si>
     <t>56809</t>
   </si>
   <si>
     <t>91110</t>
   </si>
   <si>
-    <t>21981</t>
-  </si>
-  <si>
     <t>4045</t>
   </si>
   <si>
-    <t>17659</t>
+    <t>18044</t>
+  </si>
+  <si>
+    <t>18141</t>
   </si>
   <si>
     <t>17896</t>
   </si>
   <si>
-    <t>18044</t>
+    <t>17937</t>
   </si>
   <si>
     <t>18024</t>
   </si>
   <si>
+    <t>18329</t>
+  </si>
+  <si>
+    <t>19049</t>
+  </si>
+  <si>
+    <t>19064</t>
+  </si>
+  <si>
+    <t>18618</t>
+  </si>
+  <si>
+    <t>18712</t>
+  </si>
+  <si>
+    <t>18822</t>
+  </si>
+  <si>
+    <t>18614</t>
+  </si>
+  <si>
+    <t>18907</t>
+  </si>
+  <si>
+    <t>19850</t>
+  </si>
+  <si>
+    <t>19901</t>
+  </si>
+  <si>
+    <t>18032</t>
+  </si>
+  <si>
+    <t>18325</t>
+  </si>
+  <si>
     <t>18036</t>
   </si>
   <si>
-    <t>17937</t>
-  </si>
-  <si>
-    <t>18141</t>
-  </si>
-  <si>
-    <t>18032</t>
-  </si>
-  <si>
-    <t>18329</t>
-  </si>
-  <si>
-    <t>18618</t>
-  </si>
-  <si>
-    <t>18325</t>
-  </si>
-  <si>
-    <t>18614</t>
+    <t>18813</t>
+  </si>
+  <si>
+    <t>19761</t>
+  </si>
+  <si>
+    <t>20170</t>
+  </si>
+  <si>
+    <t>20370</t>
+  </si>
+  <si>
+    <t>20588</t>
+  </si>
+  <si>
+    <t>19392</t>
+  </si>
+  <si>
+    <t>20372</t>
   </si>
   <si>
     <t>18592</t>
   </si>
   <si>
-    <t>18822</t>
-  </si>
-  <si>
-    <t>18813</t>
-  </si>
-  <si>
-    <t>18907</t>
-  </si>
-  <si>
-    <t>19049</t>
-  </si>
-  <si>
-    <t>19064</t>
+    <t>20446</t>
   </si>
   <si>
     <t>19939</t>
   </si>
   <si>
+    <t>20654</t>
+  </si>
+  <si>
+    <t>20856</t>
+  </si>
+  <si>
+    <t>20275</t>
+  </si>
+  <si>
+    <t>21880</t>
+  </si>
+  <si>
     <t>19294</t>
   </si>
   <si>
-    <t>19392</t>
-  </si>
-  <si>
-    <t>19850</t>
-  </si>
-  <si>
-    <t>19901</t>
-  </si>
-  <si>
-    <t>20170</t>
+    <t>20388</t>
+  </si>
+  <si>
+    <t>20584</t>
+  </si>
+  <si>
+    <t>21341</t>
+  </si>
+  <si>
+    <t>21422</t>
+  </si>
+  <si>
+    <t>21741</t>
+  </si>
+  <si>
+    <t>21781</t>
   </si>
   <si>
     <t>19776</t>
   </si>
   <si>
+    <t>21077</t>
+  </si>
+  <si>
     <t>19840</t>
   </si>
   <si>
-    <t>19761</t>
-  </si>
-  <si>
-    <t>20275</t>
-  </si>
-  <si>
-    <t>20584</t>
-  </si>
-  <si>
-    <t>20372</t>
-  </si>
-  <si>
-    <t>20446</t>
-  </si>
-  <si>
-    <t>20370</t>
-  </si>
-  <si>
-    <t>20856</t>
+    <t>21889</t>
   </si>
   <si>
     <t>20380</t>
@@ -367,139 +418,157 @@
     <t>20392</t>
   </si>
   <si>
-    <t>20388</t>
-  </si>
-  <si>
-    <t>20588</t>
-  </si>
-  <si>
     <t>20589</t>
   </si>
   <si>
-    <t>20654</t>
-  </si>
-  <si>
-    <t>21341</t>
-  </si>
-  <si>
-    <t>21422</t>
-  </si>
-  <si>
-    <t>21077</t>
-  </si>
-  <si>
     <t>21373</t>
   </si>
   <si>
+    <t>22119</t>
+  </si>
+  <si>
     <t>PABELLON RTO</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO </t>
+  </si>
+  <si>
     <t xml:space="preserve">ALFONSO </t>
   </si>
   <si>
     <t>ASHLEY SOPHIA</t>
   </si>
   <si>
-    <t>DAVID</t>
-  </si>
-  <si>
     <t>DANIELA FERNANDA</t>
   </si>
   <si>
-    <t xml:space="preserve">LEONARDO </t>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
   </si>
   <si>
     <t xml:space="preserve">MEGAN VICTORIA </t>
   </si>
   <si>
-    <t>ALEJANDRA</t>
+    <t xml:space="preserve">FRANCISCA </t>
   </si>
   <si>
     <t>LIZETH GUADALUPE</t>
   </si>
   <si>
+    <t>EDGAR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LILA ELENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATZIRY GABRIELA </t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA SILVIA </t>
+  </si>
+  <si>
+    <t>LESLIE ANGELICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILU </t>
+  </si>
+  <si>
+    <t>GRISELDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDA LAURA </t>
+  </si>
+  <si>
+    <t>ALAN YOSUEL</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
-    <t xml:space="preserve">FRANCISCA </t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>EDGAR ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARILU </t>
+    <t xml:space="preserve">ISAREL </t>
+  </si>
+  <si>
+    <t>ALEXA CAMILA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA </t>
+  </si>
+  <si>
+    <t>LUZ VALERIA</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JOSEFINA</t>
   </si>
   <si>
     <t>AARON DE JESUS</t>
   </si>
   <si>
-    <t>LESLIE ANGELICA</t>
-  </si>
-  <si>
-    <t>GRISELDA</t>
-  </si>
-  <si>
-    <t>LILA ELENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATZIRY GABRIELA </t>
+    <t>JORGE ENRIQUE</t>
   </si>
   <si>
     <t xml:space="preserve">TOMAS </t>
   </si>
   <si>
+    <t>MARIA CONCEPCION</t>
+  </si>
+  <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELA CAROLINA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">ANTOHONY </t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGDA LAURA </t>
-  </si>
-  <si>
-    <t>ALAN YOSUEL</t>
-  </si>
-  <si>
-    <t>ALEXA CAMILA</t>
+    <t>EDNA YADIRA</t>
+  </si>
+  <si>
+    <t>LESLI TERESA</t>
+  </si>
+  <si>
+    <t>CLAUDIA ADRIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN </t>
+  </si>
+  <si>
+    <t>OSCAR DANIEL</t>
+  </si>
+  <si>
+    <t>DULCE NAYELY</t>
   </si>
   <si>
     <t xml:space="preserve">CANDIDO </t>
   </si>
   <si>
+    <t xml:space="preserve">LUIS ALFONSO </t>
+  </si>
+  <si>
     <t xml:space="preserve">CRISTIAN URIEL </t>
   </si>
   <si>
-    <t xml:space="preserve">ISAREL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABRIELA CAROLINA </t>
-  </si>
-  <si>
-    <t>LESLI TERESA</t>
-  </si>
-  <si>
-    <t>JOSEFINA</t>
-  </si>
-  <si>
-    <t>JORGE ENRIQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA CRISTINA </t>
-  </si>
-  <si>
-    <t>LETICIA</t>
+    <t xml:space="preserve">MARINA </t>
   </si>
   <si>
     <t>ALEXIS SEBASTIAN</t>
@@ -511,130 +580,142 @@
     <t xml:space="preserve">MARIA DEL ROSARIO </t>
   </si>
   <si>
-    <t>EDNA YADIRA</t>
-  </si>
-  <si>
-    <t>LUZ VALERIA</t>
-  </si>
-  <si>
     <t>FATIMA GUADALUPE</t>
   </si>
   <si>
-    <t>MARIA CONCEPCION</t>
-  </si>
-  <si>
-    <t>CLAUDIA ADRIANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUIS ALFONSO </t>
-  </si>
-  <si>
     <t>LAURA YAZMIN</t>
   </si>
   <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CASTELLON</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t xml:space="preserve">IBARRA </t>
   </si>
   <si>
-    <t>CASTELLON</t>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CURIEL</t>
   </si>
   <si>
     <t>VALDEZ</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
+    <t>ALQUISIRA</t>
   </si>
   <si>
     <t xml:space="preserve">VALENZUELA </t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BARAJAS</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>ANDONAEGUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMIREZ </t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ARREDONDO</t>
+  </si>
+  <si>
+    <t>PEÑUÑURI</t>
+  </si>
+  <si>
+    <t>PELAYO</t>
+  </si>
+  <si>
     <t>MEZA</t>
   </si>
   <si>
-    <t>ALQUISIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CURIEL</t>
-  </si>
-  <si>
-    <t>PEÑUÑURI</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ANDONAEGUI</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t xml:space="preserve">CABELLO </t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>GUDILLO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABELLO </t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>BARAJAS</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>OLARTE</t>
   </si>
   <si>
+    <t>ESQUIVEL</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAONA </t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ARREDONDO</t>
+    <t xml:space="preserve">DELA CRUZ </t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTRO </t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>AMES</t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">GAONA </t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUDILLO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t xml:space="preserve">ACENCIO </t>
@@ -646,259 +727,280 @@
     <t xml:space="preserve">MARQUEZ </t>
   </si>
   <si>
-    <t xml:space="preserve">DELA CRUZ </t>
-  </si>
-  <si>
-    <t>ESQUIVEL</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASTRO </t>
-  </si>
-  <si>
-    <t>AMES</t>
-  </si>
-  <si>
     <t>CAPIZ</t>
   </si>
   <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>CARMONA</t>
+  </si>
+  <si>
     <t>PINEDA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CARMONA</t>
+    <t>NUÑO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>NUÑO</t>
+    <t>SANTANA</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GARNIDO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>ZAMORA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ITURIOS</t>
+  </si>
+  <si>
+    <t>VEZDUZCO</t>
+  </si>
+  <si>
     <t>VALENZUELA</t>
   </si>
   <si>
-    <t>SANTANA</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>ITURIOS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VEZDUZCO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>ZATARAIN</t>
+  </si>
+  <si>
+    <t>DELOERA</t>
+  </si>
+  <si>
+    <t>GERONIMO</t>
+  </si>
+  <si>
+    <t>OLIVAREZ</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
   </si>
   <si>
     <t>MUÑIZ</t>
   </si>
   <si>
-    <t>ZAMORA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GARNIDO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
+    <t>BECERRA</t>
   </si>
   <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>OLIVAREZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ZATARAIN</t>
-  </si>
-  <si>
-    <t>FELIX</t>
+    <t>SALGADO</t>
   </si>
   <si>
     <t xml:space="preserve">OSORIO </t>
   </si>
   <si>
-    <t>GERONIMO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>BECERRA</t>
-  </si>
-  <si>
-    <t>DELOERA</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
+    <t>ARANDA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVILEZ </t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
   </si>
   <si>
     <t>ARAMBULA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVILEZ </t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>6611874122</t>
+  </si>
+  <si>
+    <t>6612356208</t>
+  </si>
+  <si>
     <t>7351340175</t>
   </si>
   <si>
     <t>6642018969</t>
   </si>
   <si>
-    <t>6611874122</t>
-  </si>
-  <si>
     <t>6611029556</t>
   </si>
   <si>
-    <t>6612356208</t>
+    <t>6612457962</t>
+  </si>
+  <si>
+    <t>6195181188</t>
   </si>
   <si>
     <t>6611255339</t>
   </si>
   <si>
-    <t>6612457962</t>
+    <t>6627448010</t>
   </si>
   <si>
     <t>6648559380</t>
   </si>
   <si>
+    <t>6611146703</t>
+  </si>
+  <si>
+    <t>6641096895</t>
+  </si>
+  <si>
+    <t>5545626086</t>
+  </si>
+  <si>
+    <t>6643700182</t>
+  </si>
+  <si>
+    <t>6611169305</t>
+  </si>
+  <si>
+    <t>6612393040</t>
+  </si>
+  <si>
+    <t>6645991198</t>
+  </si>
+  <si>
+    <t>6612393915</t>
+  </si>
+  <si>
+    <t>6611721658</t>
+  </si>
+  <si>
+    <t>6645807893</t>
+  </si>
+  <si>
+    <t>6441340324</t>
+  </si>
+  <si>
+    <t>6611108616</t>
+  </si>
+  <si>
     <t>4463394887</t>
   </si>
   <si>
-    <t>6627448010</t>
-  </si>
-  <si>
-    <t>6195181188</t>
-  </si>
-  <si>
-    <t>6441340324</t>
-  </si>
-  <si>
-    <t>6611146703</t>
-  </si>
-  <si>
-    <t>6643700182</t>
-  </si>
-  <si>
-    <t>6611108616</t>
-  </si>
-  <si>
-    <t>6645991198</t>
+    <t>6616162514</t>
+  </si>
+  <si>
+    <t>6611110729</t>
+  </si>
+  <si>
+    <t>6673421986</t>
+  </si>
+  <si>
+    <t>6611192305</t>
+  </si>
+  <si>
+    <t>6615273140</t>
+  </si>
+  <si>
+    <t>7291799451</t>
+  </si>
+  <si>
+    <t>6611143877</t>
   </si>
   <si>
     <t>6611193456</t>
   </si>
   <si>
-    <t>6612393040</t>
-  </si>
-  <si>
-    <t>6616162514</t>
-  </si>
-  <si>
-    <t>6612393915</t>
-  </si>
-  <si>
-    <t>6641096895</t>
-  </si>
-  <si>
-    <t>5545626086</t>
+    <t>6644644841</t>
   </si>
   <si>
     <t>6613322085</t>
   </si>
   <si>
+    <t>6611954909</t>
+  </si>
+  <si>
+    <t>6862144489</t>
+  </si>
+  <si>
+    <t>6631533043</t>
+  </si>
+  <si>
+    <t>6616165544</t>
+  </si>
+  <si>
     <t>6611726857</t>
   </si>
   <si>
-    <t>7291799451</t>
-  </si>
-  <si>
-    <t>6611721658</t>
-  </si>
-  <si>
-    <t>6645807893</t>
-  </si>
-  <si>
-    <t>6673421986</t>
+    <t>3251050507</t>
+  </si>
+  <si>
+    <t>6611143806</t>
+  </si>
+  <si>
+    <t>6611173965</t>
+  </si>
+  <si>
+    <t>6195778145</t>
+  </si>
+  <si>
+    <t>6611162254</t>
+  </si>
+  <si>
+    <t>6647907702</t>
   </si>
   <si>
     <t>7224496778</t>
   </si>
   <si>
+    <t>6611160032</t>
+  </si>
+  <si>
     <t>6611116361</t>
   </si>
   <si>
-    <t>6611110729</t>
-  </si>
-  <si>
-    <t>6631533043</t>
-  </si>
-  <si>
-    <t>6611143806</t>
-  </si>
-  <si>
-    <t>6611143877</t>
-  </si>
-  <si>
-    <t>6644644841</t>
-  </si>
-  <si>
-    <t>6611192305</t>
-  </si>
-  <si>
-    <t>6862144489</t>
+    <t>6645752792</t>
   </si>
   <si>
     <t>6611400473</t>
@@ -910,85 +1012,97 @@
     <t>6648438264</t>
   </si>
   <si>
-    <t>3251050507</t>
-  </si>
-  <si>
-    <t>6615273140</t>
-  </si>
-  <si>
     <t>6611162957</t>
   </si>
   <si>
-    <t>6611954909</t>
-  </si>
-  <si>
-    <t>6611173965</t>
-  </si>
-  <si>
-    <t>6195778145</t>
-  </si>
-  <si>
-    <t>6611160032</t>
-  </si>
-  <si>
     <t>6611352488</t>
   </si>
   <si>
+    <t>6611357801</t>
+  </si>
+  <si>
     <t>ROSARITO</t>
   </si>
   <si>
+    <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
+  </si>
+  <si>
+    <t>C D LOS FISIOS</t>
+  </si>
+  <si>
     <t>AGUSTIN DE ITUBIDE 418</t>
   </si>
   <si>
-    <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
+    <t>FRANCISCO BONILLA 14</t>
   </si>
   <si>
     <t>SAN FRANCISCO</t>
   </si>
   <si>
-    <t>FRANCISCO BONILLA 14</t>
-  </si>
-  <si>
-    <t>C D LOS FISIOS</t>
+    <t>LAZARO CARDENAS  8741</t>
   </si>
   <si>
     <t>LOMAS DE BELEN</t>
   </si>
   <si>
+    <t>HACIENDA SAN FERNANDO</t>
+  </si>
+  <si>
+    <t>BUENA VISTA</t>
+  </si>
+  <si>
     <t>JOSE MARIA IGLESIAS 20</t>
   </si>
   <si>
+    <t>COLONIA MORELOS</t>
+  </si>
+  <si>
+    <t>LUIS CABRERA  20</t>
+  </si>
+  <si>
+    <t>CARRETERA LIBRE ENCENADA</t>
+  </si>
+  <si>
+    <t>EL NOGAL 7207</t>
+  </si>
+  <si>
+    <t>AMPLIACION REFORMA</t>
+  </si>
+  <si>
     <t>EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>BUENA VISTA</t>
-  </si>
-  <si>
-    <t>EL NOGAL 7207</t>
-  </si>
-  <si>
-    <t>COLONIA MORELOS</t>
-  </si>
-  <si>
-    <t>LAZARO CARDENAS  8741</t>
-  </si>
-  <si>
-    <t>LUIS CABRERA  20</t>
-  </si>
-  <si>
-    <t>CARRETERA LIBRE ENCENADA</t>
-  </si>
-  <si>
-    <t>AMPLIACION REFORMA</t>
+    <t>ROSA MAR</t>
+  </si>
+  <si>
+    <t>TUXTLA GUTIERREZ</t>
+  </si>
+  <si>
+    <t>PUERTO NUEVO</t>
   </si>
   <si>
     <t>CUENCA DIAZ</t>
   </si>
   <si>
-    <t>ROSA MAR</t>
-  </si>
-  <si>
-    <t>PUERTO NUEVO</t>
+    <t>PABLO BONILLA 22</t>
+  </si>
+  <si>
+    <t>LUCIO BLANCO</t>
+  </si>
+  <si>
+    <t>LA BARCA</t>
+  </si>
+  <si>
+    <t>MARIANO ESCOBEDO 1</t>
+  </si>
+  <si>
+    <t>MAR DE ARAFURA 1881</t>
+  </si>
+  <si>
+    <t>PACIFICO 2651</t>
+  </si>
+  <si>
+    <t>AVENIDA VALLARTA 2110</t>
   </si>
   <si>
     <t>CUMBRES SAJAMA</t>
@@ -997,21 +1111,6 @@
     <t>CALLE LAGUNA 2043</t>
   </si>
   <si>
-    <t>PABLO BONILLA 22</t>
-  </si>
-  <si>
-    <t>TUXTLA GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LUCIO BLANCO</t>
-  </si>
-  <si>
-    <t>LA BARCA</t>
-  </si>
-  <si>
-    <t>PACIFICO 2651</t>
-  </si>
-  <si>
     <t>GALATEA MZA</t>
   </si>
   <si>
@@ -1021,115 +1120,145 @@
     <t>Femenino</t>
   </si>
   <si>
+    <t>02-06-1992</t>
+  </si>
+  <si>
+    <t>28-03-2008</t>
+  </si>
+  <si>
     <t>21-09-1984</t>
   </si>
   <si>
     <t>13-12-2010</t>
   </si>
   <si>
-    <t>02-06-1992</t>
-  </si>
-  <si>
     <t>13-11-2008</t>
   </si>
   <si>
-    <t>28-03-2008</t>
+    <t>10-11-1988</t>
+  </si>
+  <si>
+    <t>04-04-1996</t>
   </si>
   <si>
     <t>18-08-1991</t>
   </si>
   <si>
-    <t>10-11-1988</t>
+    <t>10-10-1973</t>
   </si>
   <si>
     <t>20-12-1993</t>
   </si>
   <si>
+    <t>06-01-2010</t>
+  </si>
+  <si>
+    <t>19-04-1980</t>
+  </si>
+  <si>
+    <t>26-03-2006</t>
+  </si>
+  <si>
+    <t>15-05-1995</t>
+  </si>
+  <si>
+    <t>21-10-1988</t>
+  </si>
+  <si>
+    <t>11-03-2003</t>
+  </si>
+  <si>
+    <t>06-04-1994</t>
+  </si>
+  <si>
+    <t>17-01-1986</t>
+  </si>
+  <si>
+    <t>10-07-1996</t>
+  </si>
+  <si>
+    <t>03-09-1993</t>
+  </si>
+  <si>
+    <t>13-12-1990</t>
+  </si>
+  <si>
+    <t>10-03-2010</t>
+  </si>
+  <si>
     <t>06-02-2009</t>
   </si>
   <si>
-    <t>10-10-1973</t>
-  </si>
-  <si>
-    <t>04-04-1996</t>
-  </si>
-  <si>
-    <t>13-12-1990</t>
-  </si>
-  <si>
-    <t>06-01-2010</t>
-  </si>
-  <si>
-    <t>15-05-1995</t>
-  </si>
-  <si>
-    <t>10-03-2010</t>
-  </si>
-  <si>
-    <t>06-04-1994</t>
+    <t>07-02-1966</t>
+  </si>
+  <si>
+    <t>15-09-1998</t>
+  </si>
+  <si>
+    <t>02-01-2006</t>
+  </si>
+  <si>
+    <t>26-02-1961</t>
+  </si>
+  <si>
+    <t>09-11-2007</t>
+  </si>
+  <si>
+    <t>07-06-1991</t>
+  </si>
+  <si>
+    <t>23-06-1960</t>
   </si>
   <si>
     <t>11-07-2000</t>
   </si>
   <si>
-    <t>11-03-2003</t>
-  </si>
-  <si>
-    <t>07-02-1966</t>
-  </si>
-  <si>
-    <t>17-01-1986</t>
-  </si>
-  <si>
-    <t>19-04-1980</t>
-  </si>
-  <si>
-    <t>26-03-2006</t>
+    <t>28-10-1993</t>
   </si>
   <si>
     <t>15-02-2009</t>
   </si>
   <si>
+    <t>21-04-2000</t>
+  </si>
+  <si>
+    <t>06-05-1979</t>
+  </si>
+  <si>
+    <t>27-05-1990</t>
+  </si>
+  <si>
+    <t>13-03-2007</t>
+  </si>
+  <si>
     <t>06-06-2009</t>
   </si>
   <si>
-    <t>07-06-1991</t>
-  </si>
-  <si>
-    <t>10-07-1996</t>
-  </si>
-  <si>
-    <t>03-09-1993</t>
-  </si>
-  <si>
-    <t>02-01-2006</t>
+    <t>10-05-1995</t>
+  </si>
+  <si>
+    <t>13-04-1999</t>
+  </si>
+  <si>
+    <t>06-10-1971</t>
+  </si>
+  <si>
+    <t>30-03-1985</t>
+  </si>
+  <si>
+    <t>04-09-1989</t>
   </si>
   <si>
     <t>02-02-1983</t>
   </si>
   <si>
+    <t>19-10-1970</t>
+  </si>
+  <si>
     <t>12-01-2008</t>
   </si>
   <si>
-    <t>15-09-1998</t>
-  </si>
-  <si>
-    <t>27-05-1990</t>
-  </si>
-  <si>
-    <t>09-11-2007</t>
-  </si>
-  <si>
-    <t>23-06-1960</t>
-  </si>
-  <si>
-    <t>28-10-1993</t>
-  </si>
-  <si>
-    <t>26-02-1961</t>
-  </si>
-  <si>
-    <t>06-05-1979</t>
+    <t>21-01-2006</t>
   </si>
   <si>
     <t>07-05-2006</t>
@@ -1141,136 +1270,157 @@
     <t>23-03-1981</t>
   </si>
   <si>
-    <t>10-05-1995</t>
-  </si>
-  <si>
     <t>03-10-2008</t>
   </si>
   <si>
-    <t>21-04-2000</t>
-  </si>
-  <si>
-    <t>13-04-1999</t>
-  </si>
-  <si>
-    <t>06-10-1971</t>
-  </si>
-  <si>
-    <t>19-10-1970</t>
-  </si>
-  <si>
     <t>08-02-2003</t>
   </si>
   <si>
+    <t>11-05-2006</t>
+  </si>
+  <si>
+    <t>ROSARITOVFBG@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MAGOB0048@GMAIL.COM</t>
+  </si>
+  <si>
     <t>P8INEDA@GMAIL.COM</t>
   </si>
   <si>
     <t>ANA.RODRIGUEZ300@GMAIL.COM</t>
   </si>
   <si>
-    <t>ROSARITOVFBG@GMAIL.COM</t>
-  </si>
-  <si>
     <t>IABARAHERMNANDEZ@GMIL.COM</t>
   </si>
   <si>
-    <t>MAGOB0048@GMAIL.COM</t>
+    <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LUIS.CURIEL4@OUTLOOK.COM</t>
   </si>
   <si>
     <t>VICTORIAVAL150891@GMAIL.COM</t>
   </si>
   <si>
-    <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
+    <t>ALQUISIRASANTANA@GMAIL.COM</t>
   </si>
   <si>
     <t>SOLANOLISETH93@GMAIL.COM</t>
   </si>
   <si>
+    <t>HERRARAGONZEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ELENA_BARAJAS@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>SANDOVALATZIRY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
+  </si>
+  <si>
+    <t>ANGIELESLIE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LICORTRUIZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARIOORIVERAAV77@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NAJERAVILLA3@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YOSUELMORENO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARTINITURIOS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
+  </si>
+  <si>
     <t>LUISJAVIER@GMAIL.COM</t>
   </si>
   <si>
-    <t>ALQUISIRASANTANA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LUIS.CURIEL4@OUTLOOK.COM</t>
-  </si>
-  <si>
-    <t>MARTINITURIOS@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>HERRARAGONZEZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LICORTRUIZ@GMAIL.COM</t>
+    <t>MCELEEZ5@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GONZALEZISRAEL98523@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DELOERAMARTINEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LUZVALERIAGARCIA01@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>OLIVAREZVALDES354@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
   </si>
   <si>
     <t>AARONRAMIREZ12323@GMAIL.COM</t>
   </si>
   <si>
-    <t>ANGIELESLIE@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MCELEEZ5@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MARIOORIVERAAV77@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ELENA_BARAJAS@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>SANDOVALATZIRY@GMAIL.COM</t>
+    <t>MELISAMARLUM1@GMAIL.COM</t>
   </si>
   <si>
     <t>LARTESLAZAE@GMAIL.COM</t>
   </si>
   <si>
+    <t>MARIAZAMORA5432@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SAGAOS0910@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ACOSTAARANDA@GMAIL.COM</t>
+  </si>
+  <si>
     <t>ESCOBARPEREZANTON@GMAIL.COM</t>
   </si>
   <si>
-    <t>OLIVAREZVALDES354@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NAJERAVILLA3@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>YOSUELMORENO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
+    <t>EDNADELACRUZ64@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LESLITERESAG09@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CAGAOS0910@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>OSCARTB42@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SANHEZNAYELI@GMAIL.COM</t>
   </si>
   <si>
     <t>SANCHEZCANDIDO586@GMAIL.COM</t>
   </si>
   <si>
+    <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>URIELCORTEZ1212@GMAIL.COM</t>
   </si>
   <si>
-    <t>GONZALEZISRAEL98523@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>SAGAOS0910@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LESLITERESAG09@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MELISAMARLUM1@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DELOERAMARTINEZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+    <t>REPEZSERVANTESMARINA@GMAIL.COM</t>
   </si>
   <si>
     <t>ACENCALEXIS@GMAIL.COM</t>
@@ -1282,139 +1432,157 @@
     <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
   </si>
   <si>
-    <t>EDNADELACRUZ64@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LUZVALERIAGARCIA01@GMAIL.COM</t>
-  </si>
-  <si>
     <t>FATIMAGUADALUPEG76@GMAIL.COM</t>
   </si>
   <si>
-    <t>MARIAZAMORA5432@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CAGAOS0910@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
-  </si>
-  <si>
     <t>LAURACAPIZ5@GMAIL.COM</t>
   </si>
   <si>
+    <t>BERMUDEZALFREDO486@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>20-09-2022 08:58:25</t>
+  </si>
+  <si>
+    <t>12-01-2026 12:08:27</t>
+  </si>
+  <si>
     <t>20-03-2023 11:49:41</t>
   </si>
   <si>
     <t>19-05-2025 14:37:27</t>
   </si>
   <si>
-    <t>20-09-2022 08:58:25</t>
-  </si>
-  <si>
     <t>14-11-2023 12:46:29</t>
   </si>
   <si>
-    <t>12-01-2026 12:08:27</t>
+    <t>02-02-2026 15:45:17</t>
+  </si>
+  <si>
+    <t>02-02-2026 17:55:59</t>
   </si>
   <si>
     <t>02-02-2026 12:17:03</t>
   </si>
   <si>
-    <t>02-02-2026 15:45:17</t>
+    <t>02-02-2026 13:09:36</t>
   </si>
   <si>
     <t>02-02-2026 15:21:09</t>
   </si>
   <si>
+    <t>03-02-2026 10:48:54</t>
+  </si>
+  <si>
+    <t>05-02-2026 08:07:14</t>
+  </si>
+  <si>
+    <t>05-02-2026 09:21:15</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:02:55</t>
+  </si>
+  <si>
+    <t>04-02-2026 08:33:41</t>
+  </si>
+  <si>
+    <t>04-02-2026 14:06:05</t>
+  </si>
+  <si>
+    <t>03-02-2026 18:55:15</t>
+  </si>
+  <si>
+    <t>04-02-2026 16:50:13</t>
+  </si>
+  <si>
+    <t>09-02-2026 07:22:55</t>
+  </si>
+  <si>
+    <t>09-02-2026 09:56:51</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:27:52</t>
+  </si>
+  <si>
+    <t>03-02-2026 10:45:27</t>
+  </si>
+  <si>
     <t>02-02-2026 15:31:29</t>
   </si>
   <si>
-    <t>02-02-2026 13:09:36</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:55:59</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:27:52</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:48:54</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:02:55</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:45:27</t>
-  </si>
-  <si>
-    <t>03-02-2026 18:55:15</t>
+    <t>04-02-2026 13:46:53</t>
+  </si>
+  <si>
+    <t>08-02-2026 12:52:54</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:48:28</t>
+  </si>
+  <si>
+    <t>10-02-2026 08:47:39</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:54:00</t>
+  </si>
+  <si>
+    <t>06-02-2026 14:15:10</t>
+  </si>
+  <si>
+    <t>10-02-2026 08:50:56</t>
   </si>
   <si>
     <t>03-02-2026 18:09:17</t>
   </si>
   <si>
-    <t>04-02-2026 14:06:05</t>
-  </si>
-  <si>
-    <t>04-02-2026 13:46:53</t>
-  </si>
-  <si>
-    <t>04-02-2026 16:50:13</t>
-  </si>
-  <si>
-    <t>05-02-2026 08:07:14</t>
-  </si>
-  <si>
-    <t>05-02-2026 09:21:15</t>
+    <t>10-02-2026 14:18:11</t>
   </si>
   <si>
     <t>09-02-2026 11:46:22</t>
   </si>
   <si>
+    <t>10-02-2026 19:27:31</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:24:54</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:49:38</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:14:13</t>
+  </si>
+  <si>
     <t>06-02-2026 06:06:25</t>
   </si>
   <si>
-    <t>06-02-2026 14:15:10</t>
-  </si>
-  <si>
-    <t>09-02-2026 07:22:55</t>
-  </si>
-  <si>
-    <t>09-02-2026 09:56:51</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:48:28</t>
+    <t>10-02-2026 09:38:32</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:51:20</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:01:41</t>
+  </si>
+  <si>
+    <t>13-02-2026 19:48:54</t>
+  </si>
+  <si>
+    <t>16-02-2026 06:13:03</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:20:26</t>
   </si>
   <si>
     <t>08-02-2026 14:21:04</t>
   </si>
   <si>
+    <t>12-02-2026 14:13:40</t>
+  </si>
+  <si>
     <t>09-02-2026 07:08:58</t>
   </si>
   <si>
-    <t>08-02-2026 12:52:54</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:49:38</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:51:20</t>
-  </si>
-  <si>
-    <t>10-02-2026 08:50:56</t>
-  </si>
-  <si>
-    <t>10-02-2026 14:18:11</t>
-  </si>
-  <si>
-    <t>10-02-2026 08:47:39</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:24:54</t>
+    <t>16-02-2026 13:36:33</t>
   </si>
   <si>
     <t>10-02-2026 09:22:29</t>
@@ -1426,175 +1594,202 @@
     <t>10-02-2026 10:09:05</t>
   </si>
   <si>
-    <t>10-02-2026 09:38:32</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:54:00</t>
-  </si>
-  <si>
     <t>10-02-2026 17:56:14</t>
   </si>
   <si>
-    <t>10-02-2026 19:27:31</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:01:41</t>
-  </si>
-  <si>
-    <t>13-02-2026 19:48:54</t>
-  </si>
-  <si>
-    <t>12-02-2026 14:13:40</t>
-  </si>
-  <si>
     <t>13-02-2026 17:19:14</t>
   </si>
   <si>
+    <t>16-02-2026 18:36:55</t>
+  </si>
+  <si>
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
+    <t>Forzoso</t>
+  </si>
+  <si>
     <t>Sin contrato</t>
   </si>
   <si>
-    <t>Forzoso</t>
-  </si>
-  <si>
     <t>No Forzoso</t>
   </si>
   <si>
+    <t>PROMO FEBRERO 12 MESES</t>
+  </si>
+  <si>
+    <t>COBACH $399</t>
+  </si>
+  <si>
     <t>CONVENIOS $549</t>
   </si>
   <si>
-    <t>COBACH $399</t>
-  </si>
-  <si>
-    <t>PROMO FEBRERO 12 MESES</t>
-  </si>
-  <si>
     <t>RECURRENTE $649 LE</t>
   </si>
   <si>
+    <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
     <t>549</t>
   </si>
   <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
     <t>649</t>
   </si>
   <si>
+    <t>1449</t>
+  </si>
+  <si>
+    <t>02-02-2026 09:13:36</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:46:13</t>
+  </si>
+  <si>
     <t>06-02-2026 14:13:33</t>
   </si>
   <si>
     <t>03-02-2026 12:59:16</t>
   </si>
   <si>
-    <t>02-02-2026 09:13:36</t>
-  </si>
-  <si>
     <t>09-02-2026 07:12:53</t>
   </si>
   <si>
-    <t>04-02-2026 17:46:13</t>
+    <t>02-02-2026 15:51:10</t>
+  </si>
+  <si>
+    <t>02-02-2026 17:59:38</t>
   </si>
   <si>
     <t>02-02-2026 12:23:43</t>
   </si>
   <si>
-    <t>02-02-2026 15:51:10</t>
+    <t>02-02-2026 13:12:52</t>
   </si>
   <si>
     <t>02-02-2026 15:25:17</t>
   </si>
   <si>
+    <t>03-02-2026 10:49:46</t>
+  </si>
+  <si>
+    <t>12-02-2026 08:10:36</t>
+  </si>
+  <si>
+    <t>06-02-2026 11:30:26</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:06:01</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:38:43</t>
+  </si>
+  <si>
+    <t>04-02-2026 14:10:01</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:00:59</t>
+  </si>
+  <si>
+    <t>04-02-2026 16:55:59</t>
+  </si>
+  <si>
+    <t>09-02-2026 07:26:06</t>
+  </si>
+  <si>
+    <t>09-02-2026 09:59:58</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:29:47</t>
+  </si>
+  <si>
+    <t>03-02-2026 10:46:51</t>
+  </si>
+  <si>
     <t>02-02-2026 15:33:41</t>
   </si>
   <si>
-    <t>02-02-2026 13:12:52</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:59:38</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:29:47</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:49:46</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:06:01</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:46:51</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:00:59</t>
+    <t>04-02-2026 13:50:36</t>
+  </si>
+  <si>
+    <t>10-02-2026 13:26:35</t>
+  </si>
+  <si>
+    <t>11-02-2026 17:26:32</t>
+  </si>
+  <si>
+    <t>12-02-2026 08:44:08</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:54:42</t>
+  </si>
+  <si>
+    <t>06-02-2026 14:17:32</t>
+  </si>
+  <si>
+    <t>12-02-2026 08:45:46</t>
   </si>
   <si>
     <t>03-02-2026 18:14:38</t>
   </si>
   <si>
-    <t>04-02-2026 14:10:01</t>
-  </si>
-  <si>
-    <t>04-02-2026 13:50:36</t>
-  </si>
-  <si>
-    <t>04-02-2026 16:55:59</t>
-  </si>
-  <si>
-    <t>12-02-2026 08:10:36</t>
-  </si>
-  <si>
-    <t>06-02-2026 11:30:26</t>
+    <t>10-02-2026 14:24:03</t>
   </si>
   <si>
     <t>09-02-2026 11:48:02</t>
   </si>
   <si>
+    <t>10-02-2026 19:33:59</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:31:31</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:56:45</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:15:43</t>
+  </si>
+  <si>
     <t>06-02-2026 06:07:12</t>
   </si>
   <si>
-    <t>06-02-2026 14:17:32</t>
-  </si>
-  <si>
-    <t>09-02-2026 07:26:06</t>
-  </si>
-  <si>
-    <t>09-02-2026 09:59:58</t>
-  </si>
-  <si>
-    <t>11-02-2026 17:26:32</t>
+    <t>12-02-2026 09:19:27</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:52:10</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:08:34</t>
+  </si>
+  <si>
+    <t>13-02-2026 21:16:17</t>
+  </si>
+  <si>
+    <t>16-02-2026 06:15:53</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:26:12</t>
   </si>
   <si>
     <t>08-02-2026 14:23:23</t>
   </si>
   <si>
+    <t>12-02-2026 14:15:35</t>
+  </si>
+  <si>
     <t>09-02-2026 07:10:14</t>
   </si>
   <si>
-    <t>10-02-2026 13:26:35</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:56:45</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:52:10</t>
-  </si>
-  <si>
-    <t>12-02-2026 08:45:46</t>
-  </si>
-  <si>
-    <t>10-02-2026 14:24:03</t>
-  </si>
-  <si>
-    <t>12-02-2026 08:44:08</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:31:31</t>
+    <t>16-02-2026 13:47:02</t>
   </si>
   <si>
     <t>10-02-2026 09:23:44</t>
@@ -1606,127 +1801,142 @@
     <t>10-02-2026 10:13:10</t>
   </si>
   <si>
-    <t>12-02-2026 09:19:27</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:54:42</t>
-  </si>
-  <si>
     <t>10-02-2026 17:57:08</t>
   </si>
   <si>
-    <t>10-02-2026 19:33:59</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:08:34</t>
-  </si>
-  <si>
-    <t>13-02-2026 21:16:17</t>
-  </si>
-  <si>
-    <t>12-02-2026 14:15:35</t>
-  </si>
-  <si>
     <t>13-02-2026 17:22:43</t>
   </si>
   <si>
+    <t>16-02-2026 18:38:24</t>
+  </si>
+  <si>
+    <t>02-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>04-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>06-03-2026 23:59:59</t>
   </si>
   <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>02-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>04-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>12-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>10-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>11-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>13-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>14-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>08-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>10-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>13-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>14-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>02-02-2026 09:13:09</t>
   </si>
   <si>
+    <t>02-02-2026 15:48:41</t>
+  </si>
+  <si>
+    <t>02-02-2026 17:58:39</t>
+  </si>
+  <si>
     <t>02-02-2026 12:20:17</t>
   </si>
   <si>
-    <t>02-02-2026 15:48:41</t>
+    <t>02-02-2026 13:11:40</t>
   </si>
   <si>
     <t>02-02-2026 15:24:50</t>
   </si>
   <si>
+    <t>12-02-2026 08:09:33</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:05:31</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:37:45</t>
+  </si>
+  <si>
+    <t>04-02-2026 14:09:27</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:00:08</t>
+  </si>
+  <si>
+    <t>04-02-2026 16:55:19</t>
+  </si>
+  <si>
+    <t>09-02-2026 07:25:07</t>
+  </si>
+  <si>
+    <t>09-02-2026 09:59:31</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:29:21</t>
+  </si>
+  <si>
     <t>02-02-2026 15:32:47</t>
   </si>
   <si>
-    <t>02-02-2026 13:11:40</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:58:39</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:29:21</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:05:31</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:00:08</t>
+    <t>04-02-2026 13:49:21</t>
+  </si>
+  <si>
+    <t>10-02-2026 13:25:41</t>
+  </si>
+  <si>
+    <t>11-02-2026 17:25:59</t>
   </si>
   <si>
     <t>03-02-2026 18:14:07</t>
   </si>
   <si>
-    <t>04-02-2026 14:09:27</t>
-  </si>
-  <si>
-    <t>04-02-2026 13:49:21</t>
-  </si>
-  <si>
-    <t>04-02-2026 16:55:19</t>
-  </si>
-  <si>
-    <t>12-02-2026 08:09:33</t>
-  </si>
-  <si>
-    <t>09-02-2026 07:25:07</t>
-  </si>
-  <si>
-    <t>09-02-2026 09:59:31</t>
-  </si>
-  <si>
-    <t>11-02-2026 17:25:59</t>
-  </si>
-  <si>
-    <t>10-02-2026 13:25:41</t>
+    <t>10-02-2026 14:22:52</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:33:24</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:29:22</t>
   </si>
   <si>
     <t>09-02-2026 19:56:10</t>
   </si>
   <si>
-    <t>10-02-2026 14:22:52</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:29:22</t>
+    <t>12-02-2026 09:18:59</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:07:45</t>
+  </si>
+  <si>
+    <t>13-02-2026 21:15:42</t>
+  </si>
+  <si>
+    <t>16-02-2026 06:15:06</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:25:33</t>
+  </si>
+  <si>
+    <t>12-02-2026 14:14:58</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:45:53</t>
   </si>
   <si>
     <t>12-02-2026 09:24:12</t>
@@ -1735,136 +1945,154 @@
     <t>10-02-2026 10:12:39</t>
   </si>
   <si>
-    <t>12-02-2026 09:18:59</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:33:24</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:07:45</t>
-  </si>
-  <si>
-    <t>13-02-2026 21:15:42</t>
-  </si>
-  <si>
-    <t>12-02-2026 14:14:58</t>
-  </si>
-  <si>
     <t>13-02-2026 17:21:47</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>26090522002470001083</t>
+  </si>
+  <si>
+    <t>26090522083420001215</t>
+  </si>
+  <si>
     <t>26090522136900001292</t>
   </si>
   <si>
     <t>26090522038960001153</t>
   </si>
   <si>
-    <t>26090522002470001083</t>
-  </si>
-  <si>
     <t>26090522182800001336</t>
   </si>
   <si>
-    <t>26090522083420001215</t>
+    <t>26090522015280001114</t>
+  </si>
+  <si>
+    <t>26090522019700001121</t>
   </si>
   <si>
     <t>26090522008660001094</t>
   </si>
   <si>
-    <t>26090522015280001114</t>
+    <t>26090522010420001102</t>
   </si>
   <si>
     <t>26090522014340001109</t>
   </si>
   <si>
+    <t>26090522036450001146</t>
+  </si>
+  <si>
+    <t>26090522288870001483</t>
+  </si>
+  <si>
+    <t>26090522134390001286</t>
+  </si>
+  <si>
+    <t>26090522055130001172</t>
+  </si>
+  <si>
+    <t>26090522381310001574</t>
+  </si>
+  <si>
+    <t>26090522075300001207</t>
+  </si>
+  <si>
+    <t>26090522054800001170</t>
+  </si>
+  <si>
+    <t>26090522080820001212</t>
+  </si>
+  <si>
+    <t>26090522183260001338</t>
+  </si>
+  <si>
+    <t>26090522187170001346</t>
+  </si>
+  <si>
+    <t>26090522014560001110</t>
+  </si>
+  <si>
+    <t>26090522036400001145</t>
+  </si>
+  <si>
     <t>26090522014690001111</t>
   </si>
   <si>
-    <t>26090522010420001102</t>
-  </si>
-  <si>
-    <t>26090522019700001121</t>
-  </si>
-  <si>
-    <t>26090522014560001110</t>
-  </si>
-  <si>
-    <t>26090522036450001146</t>
-  </si>
-  <si>
-    <t>26090522055130001172</t>
-  </si>
-  <si>
-    <t>26090522036400001145</t>
-  </si>
-  <si>
-    <t>26090522054800001170</t>
+    <t>26090522075050001206</t>
+  </si>
+  <si>
+    <t>26090522231320001412</t>
+  </si>
+  <si>
+    <t>26090522271360001469</t>
+  </si>
+  <si>
+    <t>26090522289600001486</t>
+  </si>
+  <si>
+    <t>26090522241780001425</t>
+  </si>
+  <si>
+    <t>26090522136960001293</t>
+  </si>
+  <si>
+    <t>26090522289640001487</t>
   </si>
   <si>
     <t>26090522052370001168</t>
   </si>
   <si>
-    <t>26090522075300001207</t>
-  </si>
-  <si>
-    <t>26090522075050001206</t>
-  </si>
-  <si>
-    <t>26090522080820001212</t>
-  </si>
-  <si>
-    <t>26090522288870001483</t>
-  </si>
-  <si>
-    <t>26090522134390001286</t>
+    <t>26090522232400001415</t>
   </si>
   <si>
     <t>26090522189440001352</t>
   </si>
   <si>
+    <t>26090522247060001432</t>
+  </si>
+  <si>
+    <t>26090522268680001467</t>
+  </si>
+  <si>
+    <t>26090522212640001380</t>
+  </si>
+  <si>
+    <t>26090522388310001582</t>
+  </si>
+  <si>
     <t>26090522129910001272</t>
   </si>
   <si>
-    <t>26090522136960001293</t>
-  </si>
-  <si>
-    <t>26090522183260001338</t>
-  </si>
-  <si>
-    <t>26090522187170001346</t>
-  </si>
-  <si>
-    <t>26090522271360001469</t>
+    <t>26090522290010001489</t>
+  </si>
+  <si>
+    <t>26090522241540001424</t>
+  </si>
+  <si>
+    <t>26090522323730001533</t>
+  </si>
+  <si>
+    <t>26090522331810001546</t>
+  </si>
+  <si>
+    <t>26090522377270001563</t>
+  </si>
+  <si>
+    <t>26090522380980001572</t>
   </si>
   <si>
     <t>26090522172990001325</t>
   </si>
   <si>
+    <t>26090522294330001500</t>
+  </si>
+  <si>
     <t>26090522182720001335</t>
   </si>
   <si>
-    <t>26090522231320001412</t>
-  </si>
-  <si>
-    <t>26090522212640001380</t>
-  </si>
-  <si>
-    <t>26090522241540001424</t>
-  </si>
-  <si>
-    <t>26090522289640001487</t>
-  </si>
-  <si>
-    <t>26090522232400001415</t>
-  </si>
-  <si>
-    <t>26090522289600001486</t>
-  </si>
-  <si>
-    <t>26090522268680001467</t>
+    <t>26090522389160001583</t>
   </si>
   <si>
     <t>26090522226960001399</t>
@@ -1876,30 +2104,15 @@
     <t>26090522227950001405</t>
   </si>
   <si>
-    <t>26090522290010001489</t>
-  </si>
-  <si>
-    <t>26090522241780001425</t>
-  </si>
-  <si>
     <t>26090522241950001426</t>
   </si>
   <si>
-    <t>26090522247060001432</t>
-  </si>
-  <si>
-    <t>26090522323730001533</t>
-  </si>
-  <si>
-    <t>26090522331810001546</t>
-  </si>
-  <si>
-    <t>26090522294330001500</t>
-  </si>
-  <si>
     <t>26090522326300001537</t>
   </si>
   <si>
+    <t>26090522405140001594</t>
+  </si>
+  <si>
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
   </si>
   <si>
@@ -1919,6 +2132,9 @@
   </si>
   <si>
     <t>Juan Lomeli Salcedo</t>
+  </si>
+  <si>
+    <t>Anton Omar Sanchez Ruiz</t>
   </si>
   <si>
     <t>sin rutina</t>
@@ -2282,7 +2498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2379,73 +2595,79 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H2" t="s">
-        <v>258</v>
+        <v>281</v>
+      </c>
+      <c r="I2" t="s">
+        <v>335</v>
       </c>
       <c r="J2" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K2" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="L2" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="M2" t="s">
-        <v>430</v>
-      </c>
-      <c r="N2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="O2" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="P2" t="s">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="Q2" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="R2" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
       <c r="S2" t="s">
-        <v>538</v>
+        <v>598</v>
+      </c>
+      <c r="T2" t="s">
+        <v>610</v>
       </c>
       <c r="U2" t="s">
-        <v>579</v>
+        <v>644</v>
+      </c>
+      <c r="V2" t="s">
+        <v>280</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>580</v>
+        <v>645</v>
       </c>
       <c r="AA2" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="AB2" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC2" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2453,73 +2675,79 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G3" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="J3" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K3" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="L3" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="M3" t="s">
-        <v>431</v>
+        <v>476</v>
       </c>
       <c r="N3" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O3" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P3" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="Q3" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="R3" t="s">
-        <v>491</v>
+        <v>545</v>
       </c>
       <c r="S3" t="s">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="U3" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>581</v>
+        <v>646</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>700</v>
       </c>
       <c r="AA3" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="AB3" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC3" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2527,79 +2755,73 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="F4" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="G4" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>260</v>
-      </c>
-      <c r="I4" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="J4" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K4" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="L4" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="M4" t="s">
-        <v>432</v>
+        <v>477</v>
+      </c>
+      <c r="N4" t="s">
+        <v>529</v>
       </c>
       <c r="O4" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P4" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="Q4" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="R4" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
       <c r="S4" t="s">
-        <v>540</v>
-      </c>
-      <c r="T4" t="s">
-        <v>549</v>
+        <v>600</v>
       </c>
       <c r="U4" t="s">
-        <v>579</v>
-      </c>
-      <c r="V4" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>582</v>
+        <v>647</v>
       </c>
       <c r="AA4" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AB4" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC4" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2607,73 +2829,73 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H5" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="J5" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K5" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="L5" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="M5" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="N5" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O5" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P5" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="Q5" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="R5" t="s">
-        <v>493</v>
+        <v>547</v>
       </c>
       <c r="S5" t="s">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="U5" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>583</v>
+        <v>648</v>
       </c>
       <c r="AA5" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="AB5" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC5" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2681,79 +2903,73 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H6" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="J6" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K6" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="L6" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="M6" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="N6" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O6" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P6" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="Q6" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="R6" t="s">
-        <v>494</v>
+        <v>548</v>
       </c>
       <c r="S6" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="U6" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>584</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="AA6" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="AB6" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC6" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2761,79 +2977,82 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F7" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="G7" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H7" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="I7" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="J7" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K7" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="L7" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="M7" t="s">
-        <v>435</v>
+        <v>480</v>
+      </c>
+      <c r="N7" t="s">
+        <v>529</v>
       </c>
       <c r="O7" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="P7" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="Q7" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="R7" t="s">
-        <v>495</v>
+        <v>549</v>
       </c>
       <c r="S7" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="T7" t="s">
-        <v>550</v>
+        <v>611</v>
       </c>
       <c r="U7" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V7" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>585</v>
+        <v>650</v>
       </c>
       <c r="AA7" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="AB7" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC7" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2841,82 +3060,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H8" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="I8" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="J8" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K8" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="L8" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="M8" t="s">
-        <v>436</v>
-      </c>
-      <c r="N8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O8" t="s">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="P8" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="Q8" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="R8" t="s">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="S8" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="T8" t="s">
-        <v>551</v>
+        <v>612</v>
       </c>
       <c r="U8" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V8" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>586</v>
+        <v>651</v>
       </c>
       <c r="AA8" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="AB8" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC8" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2924,79 +3140,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="G9" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H9" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="I9" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="J9" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K9" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="L9" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="M9" t="s">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="O9" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P9" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q9" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R9" t="s">
-        <v>497</v>
+        <v>551</v>
       </c>
       <c r="S9" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="T9" t="s">
-        <v>552</v>
+        <v>613</v>
       </c>
       <c r="U9" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V9" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>587</v>
+        <v>652</v>
       </c>
       <c r="AA9" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB9" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="AC9" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -3004,79 +3220,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="G10" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H10" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="I10" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="J10" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K10" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="L10" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="M10" t="s">
-        <v>438</v>
+        <v>483</v>
       </c>
       <c r="O10" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P10" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q10" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R10" t="s">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="S10" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="T10" t="s">
-        <v>553</v>
+        <v>614</v>
       </c>
       <c r="U10" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V10" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>588</v>
+        <v>653</v>
       </c>
       <c r="AA10" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB10" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="AC10" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -3084,79 +3300,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="G11" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H11" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="I11" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="J11" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K11" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="L11" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="M11" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="O11" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P11" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q11" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R11" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="S11" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="T11" t="s">
-        <v>554</v>
+        <v>615</v>
       </c>
       <c r="U11" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V11" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>589</v>
+        <v>654</v>
       </c>
       <c r="AA11" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB11" t="s">
-        <v>632</v>
+        <v>704</v>
       </c>
       <c r="AC11" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -3164,79 +3380,73 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="G12" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H12" t="s">
-        <v>268</v>
-      </c>
-      <c r="I12" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="J12" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K12" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="L12" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="M12" t="s">
-        <v>440</v>
+        <v>485</v>
+      </c>
+      <c r="N12" t="s">
+        <v>529</v>
       </c>
       <c r="O12" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P12" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="Q12" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="R12" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="S12" t="s">
-        <v>540</v>
-      </c>
-      <c r="T12" t="s">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="U12" t="s">
-        <v>579</v>
-      </c>
-      <c r="V12" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>590</v>
+        <v>655</v>
       </c>
       <c r="AA12" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="AB12" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC12" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3244,79 +3454,85 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="G13" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H13" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="I13" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="J13" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K13" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="L13" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="M13" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="O13" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P13" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q13" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R13" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="S13" t="s">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="T13" t="s">
-        <v>556</v>
+        <v>616</v>
       </c>
       <c r="U13" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V13" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>591</v>
+        <v>656</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>701</v>
       </c>
       <c r="AA13" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB13" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC13" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3324,73 +3540,79 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="F14" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="G14" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H14" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="J14" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K14" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="L14" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="M14" t="s">
-        <v>442</v>
+        <v>487</v>
       </c>
       <c r="N14" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O14" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P14" t="s">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="Q14" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="R14" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="S14" t="s">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="U14" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>592</v>
+        <v>657</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>701</v>
       </c>
       <c r="AA14" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="AB14" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC14" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3398,82 +3620,82 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="G15" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H15" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="I15" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="J15" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K15" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="L15" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="M15" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="N15" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O15" t="s">
-        <v>481</v>
+        <v>533</v>
       </c>
       <c r="P15" t="s">
-        <v>485</v>
+        <v>537</v>
       </c>
       <c r="Q15" t="s">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="R15" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="S15" t="s">
-        <v>539</v>
+        <v>601</v>
       </c>
       <c r="T15" t="s">
-        <v>557</v>
+        <v>617</v>
       </c>
       <c r="U15" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V15" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>593</v>
+        <v>658</v>
       </c>
       <c r="AA15" t="s">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="AB15" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC15" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3481,73 +3703,88 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="F16" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="G16" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H16" t="s">
-        <v>272</v>
+        <v>295</v>
+      </c>
+      <c r="I16" t="s">
+        <v>343</v>
       </c>
       <c r="J16" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K16" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="L16" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="M16" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="N16" t="s">
-        <v>478</v>
+        <v>530</v>
       </c>
       <c r="O16" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="P16" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="Q16" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="R16" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="S16" t="s">
-        <v>539</v>
+        <v>604</v>
+      </c>
+      <c r="T16" t="s">
+        <v>618</v>
       </c>
       <c r="U16" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V16" t="s">
+        <v>280</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>594</v>
+        <v>659</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>701</v>
       </c>
       <c r="AA16" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="AB16" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC16" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3555,82 +3792,79 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="G17" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H17" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="I17" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="J17" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K17" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="L17" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="M17" t="s">
-        <v>445</v>
-      </c>
-      <c r="N17" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="O17" t="s">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="P17" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="Q17" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="R17" t="s">
-        <v>505</v>
+        <v>559</v>
       </c>
       <c r="S17" t="s">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="T17" t="s">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="U17" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V17" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>595</v>
+        <v>660</v>
       </c>
       <c r="AA17" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="AB17" t="s">
-        <v>632</v>
+        <v>705</v>
       </c>
       <c r="AC17" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3638,79 +3872,82 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="G18" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H18" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="I18" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="J18" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K18" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="L18" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="M18" t="s">
-        <v>446</v>
+        <v>491</v>
+      </c>
+      <c r="N18" t="s">
+        <v>529</v>
       </c>
       <c r="O18" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="P18" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="Q18" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="R18" t="s">
-        <v>506</v>
+        <v>560</v>
       </c>
       <c r="S18" t="s">
-        <v>539</v>
+        <v>601</v>
       </c>
       <c r="T18" t="s">
-        <v>559</v>
+        <v>620</v>
       </c>
       <c r="U18" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V18" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>596</v>
+        <v>661</v>
       </c>
       <c r="AA18" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="AB18" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC18" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3718,79 +3955,82 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="G19" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H19" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="I19" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="J19" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K19" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="L19" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="M19" t="s">
-        <v>447</v>
+        <v>492</v>
+      </c>
+      <c r="N19" t="s">
+        <v>529</v>
       </c>
       <c r="O19" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="P19" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="Q19" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="R19" t="s">
-        <v>507</v>
+        <v>561</v>
       </c>
       <c r="S19" t="s">
-        <v>542</v>
+        <v>599</v>
       </c>
       <c r="T19" t="s">
-        <v>560</v>
+        <v>621</v>
       </c>
       <c r="U19" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V19" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>597</v>
+        <v>662</v>
       </c>
       <c r="AA19" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="AB19" t="s">
-        <v>634</v>
+        <v>703</v>
       </c>
       <c r="AC19" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3798,79 +4038,79 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F20" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="G20" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H20" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="I20" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="J20" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K20" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="L20" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="M20" t="s">
-        <v>448</v>
+        <v>493</v>
       </c>
       <c r="O20" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P20" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q20" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R20" t="s">
-        <v>508</v>
+        <v>562</v>
       </c>
       <c r="S20" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="T20" t="s">
-        <v>561</v>
+        <v>622</v>
       </c>
       <c r="U20" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V20" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>598</v>
+        <v>663</v>
       </c>
       <c r="AA20" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB20" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC20" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3878,82 +4118,79 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F21" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="G21" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H21" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="I21" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="J21" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K21" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="L21" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="M21" t="s">
-        <v>449</v>
-      </c>
-      <c r="N21" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="O21" t="s">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="P21" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="Q21" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="R21" t="s">
-        <v>509</v>
+        <v>563</v>
       </c>
       <c r="S21" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="T21" t="s">
-        <v>562</v>
+        <v>623</v>
       </c>
       <c r="U21" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V21" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>599</v>
+        <v>664</v>
       </c>
       <c r="AA21" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="AB21" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC21" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3961,85 +4198,79 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="F22" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="G22" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H22" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="I22" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="J22" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K22" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="L22" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="M22" t="s">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="O22" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P22" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q22" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R22" t="s">
-        <v>510</v>
+        <v>564</v>
       </c>
       <c r="S22" t="s">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="T22" t="s">
-        <v>563</v>
+        <v>624</v>
       </c>
       <c r="U22" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V22" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>600</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>630</v>
+        <v>665</v>
       </c>
       <c r="AA22" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB22" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC22" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -4047,79 +4278,73 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F23" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="G23" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H23" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="J23" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K23" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="L23" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
       <c r="M23" t="s">
-        <v>451</v>
+        <v>496</v>
       </c>
       <c r="N23" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O23" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P23" t="s">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="Q23" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="R23" t="s">
-        <v>511</v>
+        <v>565</v>
       </c>
       <c r="S23" t="s">
-        <v>538</v>
+        <v>601</v>
       </c>
       <c r="U23" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>601</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>630</v>
+        <v>666</v>
       </c>
       <c r="AA23" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="AB23" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC23" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -4127,73 +4352,79 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="F24" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="G24" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H24" t="s">
+        <v>303</v>
+      </c>
+      <c r="I24" t="s">
+        <v>340</v>
+      </c>
+      <c r="J24" t="s">
+        <v>366</v>
+      </c>
+      <c r="K24" t="s">
+        <v>390</v>
+      </c>
+      <c r="L24" t="s">
+        <v>443</v>
+      </c>
+      <c r="M24" t="s">
+        <v>497</v>
+      </c>
+      <c r="O24" t="s">
+        <v>531</v>
+      </c>
+      <c r="P24" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>539</v>
+      </c>
+      <c r="R24" t="s">
+        <v>566</v>
+      </c>
+      <c r="S24" t="s">
+        <v>598</v>
+      </c>
+      <c r="T24" t="s">
+        <v>625</v>
+      </c>
+      <c r="U24" t="s">
+        <v>644</v>
+      </c>
+      <c r="V24" t="s">
         <v>280</v>
-      </c>
-      <c r="J24" t="s">
-        <v>333</v>
-      </c>
-      <c r="K24" t="s">
-        <v>357</v>
-      </c>
-      <c r="L24" t="s">
-        <v>404</v>
-      </c>
-      <c r="M24" t="s">
-        <v>452</v>
-      </c>
-      <c r="N24" t="s">
-        <v>478</v>
-      </c>
-      <c r="O24" t="s">
-        <v>479</v>
-      </c>
-      <c r="P24" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>487</v>
-      </c>
-      <c r="R24" t="s">
-        <v>512</v>
-      </c>
-      <c r="S24" t="s">
-        <v>541</v>
-      </c>
-      <c r="U24" t="s">
-        <v>257</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>602</v>
+        <v>667</v>
       </c>
       <c r="AA24" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="AB24" t="s">
-        <v>632</v>
+        <v>704</v>
       </c>
       <c r="AC24" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -4201,73 +4432,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="F25" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="G25" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H25" t="s">
-        <v>281</v>
+        <v>304</v>
+      </c>
+      <c r="I25" t="s">
+        <v>349</v>
       </c>
       <c r="J25" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K25" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="L25" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
       <c r="M25" t="s">
-        <v>453</v>
-      </c>
-      <c r="N25" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="O25" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="P25" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="Q25" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="R25" t="s">
-        <v>513</v>
+        <v>567</v>
       </c>
       <c r="S25" t="s">
-        <v>538</v>
+        <v>599</v>
+      </c>
+      <c r="T25" t="s">
+        <v>626</v>
       </c>
       <c r="U25" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V25" t="s">
+        <v>644</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>603</v>
+        <v>668</v>
       </c>
       <c r="AA25" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="AB25" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC25" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4275,73 +4512,85 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F26" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="G26" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H26" t="s">
-        <v>282</v>
+        <v>305</v>
+      </c>
+      <c r="I26" t="s">
+        <v>335</v>
       </c>
       <c r="J26" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K26" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="L26" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="M26" t="s">
-        <v>454</v>
-      </c>
-      <c r="N26" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="O26" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="P26" t="s">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="Q26" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="R26" t="s">
-        <v>514</v>
+        <v>568</v>
       </c>
       <c r="S26" t="s">
-        <v>538</v>
+        <v>605</v>
+      </c>
+      <c r="T26" t="s">
+        <v>627</v>
       </c>
       <c r="U26" t="s">
-        <v>579</v>
+        <v>644</v>
+      </c>
+      <c r="V26" t="s">
+        <v>280</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>604</v>
+        <v>669</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>702</v>
       </c>
       <c r="AA26" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="AB26" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC26" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4349,79 +4598,85 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F27" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="G27" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H27" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="I27" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="J27" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K27" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="L27" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="M27" t="s">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="O27" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P27" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q27" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R27" t="s">
-        <v>515</v>
+        <v>569</v>
       </c>
       <c r="S27" t="s">
-        <v>541</v>
+        <v>606</v>
       </c>
       <c r="T27" t="s">
-        <v>564</v>
+        <v>628</v>
       </c>
       <c r="U27" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V27" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>605</v>
+        <v>670</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>702</v>
       </c>
       <c r="AA27" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB27" t="s">
-        <v>632</v>
+        <v>705</v>
       </c>
       <c r="AC27" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4429,79 +4684,79 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="F28" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="G28" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H28" t="s">
-        <v>284</v>
-      </c>
-      <c r="I28" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="J28" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K28" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="L28" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="M28" t="s">
-        <v>456</v>
+        <v>501</v>
+      </c>
+      <c r="N28" t="s">
+        <v>529</v>
       </c>
       <c r="O28" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P28" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="Q28" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="R28" t="s">
-        <v>516</v>
+        <v>570</v>
       </c>
       <c r="S28" t="s">
-        <v>541</v>
-      </c>
-      <c r="T28" t="s">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="U28" t="s">
-        <v>579</v>
-      </c>
-      <c r="V28" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>606</v>
+        <v>671</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>701</v>
       </c>
       <c r="AA28" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AB28" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC28" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4509,85 +4764,73 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="F29" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="G29" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H29" t="s">
-        <v>285</v>
-      </c>
-      <c r="I29" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="J29" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K29" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="L29" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="M29" t="s">
-        <v>457</v>
+        <v>502</v>
+      </c>
+      <c r="N29" t="s">
+        <v>529</v>
       </c>
       <c r="O29" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P29" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="Q29" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="R29" t="s">
-        <v>517</v>
+        <v>571</v>
       </c>
       <c r="S29" t="s">
-        <v>544</v>
-      </c>
-      <c r="T29" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="U29" t="s">
-        <v>579</v>
-      </c>
-      <c r="V29" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>607</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>631</v>
+        <v>672</v>
       </c>
       <c r="AA29" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AB29" t="s">
-        <v>634</v>
+        <v>703</v>
       </c>
       <c r="AC29" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4595,73 +4838,73 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="G30" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H30" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="J30" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K30" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="L30" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="M30" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="N30" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O30" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P30" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="Q30" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="R30" t="s">
-        <v>518</v>
+        <v>572</v>
       </c>
       <c r="S30" t="s">
-        <v>545</v>
+        <v>600</v>
       </c>
       <c r="U30" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>608</v>
+        <v>673</v>
       </c>
       <c r="AA30" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="AB30" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC30" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4669,73 +4912,79 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F31" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="G31" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H31" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="J31" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K31" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="L31" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="M31" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="N31" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O31" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P31" t="s">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="Q31" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="R31" t="s">
-        <v>519</v>
+        <v>573</v>
       </c>
       <c r="S31" t="s">
-        <v>541</v>
+        <v>603</v>
       </c>
       <c r="U31" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>609</v>
+        <v>674</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>699</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>701</v>
       </c>
       <c r="AA31" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="AB31" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC31" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4743,85 +4992,79 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="F32" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="G32" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H32" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="I32" t="s">
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="J32" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K32" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="L32" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="M32" t="s">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="O32" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P32" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q32" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R32" t="s">
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="S32" t="s">
-        <v>546</v>
+        <v>601</v>
       </c>
       <c r="T32" t="s">
-        <v>567</v>
+        <v>629</v>
       </c>
       <c r="U32" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V32" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>610</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
       <c r="AA32" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB32" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC32" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4829,82 +5072,79 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="G33" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H33" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="I33" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="J33" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="K33" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="L33" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="M33" t="s">
-        <v>461</v>
-      </c>
-      <c r="N33" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="O33" t="s">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="P33" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="Q33" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="R33" t="s">
-        <v>521</v>
+        <v>575</v>
       </c>
       <c r="S33" t="s">
-        <v>541</v>
+        <v>605</v>
       </c>
       <c r="T33" t="s">
-        <v>568</v>
+        <v>630</v>
       </c>
       <c r="U33" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V33" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>611</v>
+        <v>676</v>
       </c>
       <c r="AA33" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="AB33" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC33" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -4912,73 +5152,73 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F34" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="G34" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H34" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="J34" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K34" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="L34" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="M34" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="N34" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O34" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P34" t="s">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="Q34" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="R34" t="s">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="S34" t="s">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="U34" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>612</v>
+        <v>677</v>
       </c>
       <c r="AA34" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="AB34" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC34" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4986,79 +5226,79 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F35" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G35" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H35" t="s">
-        <v>291</v>
+        <v>314</v>
+      </c>
+      <c r="I35" t="s">
+        <v>353</v>
       </c>
       <c r="J35" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K35" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="L35" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="M35" t="s">
-        <v>463</v>
-      </c>
-      <c r="N35" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="O35" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="P35" t="s">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="Q35" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="R35" t="s">
-        <v>523</v>
+        <v>577</v>
       </c>
       <c r="S35" t="s">
-        <v>543</v>
+        <v>605</v>
+      </c>
+      <c r="T35" t="s">
+        <v>631</v>
       </c>
       <c r="U35" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V35" t="s">
+        <v>280</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>613</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>630</v>
+        <v>678</v>
       </c>
       <c r="AA35" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="AB35" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC35" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -5066,79 +5306,79 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="G36" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H36" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="I36" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="J36" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K36" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="L36" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
       <c r="M36" t="s">
-        <v>464</v>
+        <v>509</v>
       </c>
       <c r="O36" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P36" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q36" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R36" t="s">
-        <v>524</v>
+        <v>578</v>
       </c>
       <c r="S36" t="s">
-        <v>546</v>
+        <v>606</v>
       </c>
       <c r="T36" t="s">
-        <v>569</v>
+        <v>632</v>
       </c>
       <c r="U36" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V36" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>614</v>
+        <v>679</v>
       </c>
       <c r="AA36" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB36" t="s">
-        <v>632</v>
+        <v>706</v>
       </c>
       <c r="AC36" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -5146,79 +5386,82 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F37" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="G37" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H37" t="s">
-        <v>293</v>
+        <v>316</v>
+      </c>
+      <c r="I37" t="s">
+        <v>355</v>
       </c>
       <c r="J37" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K37" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="L37" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="M37" t="s">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="N37" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O37" t="s">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="P37" t="s">
-        <v>482</v>
+        <v>537</v>
       </c>
       <c r="Q37" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="R37" t="s">
-        <v>525</v>
+        <v>579</v>
       </c>
       <c r="S37" t="s">
-        <v>543</v>
+        <v>602</v>
+      </c>
+      <c r="T37" t="s">
+        <v>633</v>
       </c>
       <c r="U37" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V37" t="s">
+        <v>280</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>615</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="AA37" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="AB37" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC37" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -5226,79 +5469,73 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="G38" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H38" t="s">
-        <v>294</v>
-      </c>
-      <c r="I38" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J38" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K38" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="L38" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="M38" t="s">
-        <v>466</v>
+        <v>511</v>
+      </c>
+      <c r="N38" t="s">
+        <v>529</v>
       </c>
       <c r="O38" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P38" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="Q38" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="R38" t="s">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="S38" t="s">
-        <v>544</v>
-      </c>
-      <c r="T38" t="s">
-        <v>570</v>
+        <v>604</v>
       </c>
       <c r="U38" t="s">
-        <v>579</v>
-      </c>
-      <c r="V38" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>616</v>
+        <v>681</v>
       </c>
       <c r="AA38" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="AB38" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC38" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5306,73 +5543,73 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F39" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="G39" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H39" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="J39" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K39" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="L39" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="M39" t="s">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="N39" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O39" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="P39" t="s">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="Q39" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="R39" t="s">
-        <v>527</v>
+        <v>581</v>
       </c>
       <c r="S39" t="s">
-        <v>546</v>
+        <v>600</v>
       </c>
       <c r="U39" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>617</v>
+        <v>682</v>
       </c>
       <c r="AA39" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="AB39" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC39" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5380,82 +5617,85 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="G40" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H40" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="I40" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="J40" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K40" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="L40" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
       <c r="M40" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="O40" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P40" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q40" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R40" t="s">
-        <v>528</v>
+        <v>582</v>
       </c>
       <c r="S40" t="s">
-        <v>543</v>
+        <v>603</v>
       </c>
       <c r="T40" t="s">
-        <v>571</v>
+        <v>634</v>
       </c>
       <c r="U40" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V40" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>618</v>
+        <v>683</v>
       </c>
       <c r="Y40" t="s">
-        <v>628</v>
+        <v>699</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>701</v>
       </c>
       <c r="AA40" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB40" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC40" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5463,79 +5703,73 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F41" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="G41" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H41" t="s">
-        <v>297</v>
-      </c>
-      <c r="I41" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="J41" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K41" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="M41" t="s">
-        <v>469</v>
+        <v>514</v>
+      </c>
+      <c r="N41" t="s">
+        <v>529</v>
       </c>
       <c r="O41" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P41" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="Q41" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="R41" t="s">
-        <v>529</v>
+        <v>583</v>
       </c>
       <c r="S41" t="s">
-        <v>546</v>
-      </c>
-      <c r="T41" t="s">
-        <v>572</v>
+        <v>605</v>
       </c>
       <c r="U41" t="s">
-        <v>579</v>
-      </c>
-      <c r="V41" t="s">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>619</v>
+        <v>684</v>
       </c>
       <c r="AA41" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AB41" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="AC41" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -5543,85 +5777,79 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E42" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F42" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="G42" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H42" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="I42" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="J42" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K42" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="L42" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="M42" t="s">
-        <v>470</v>
+        <v>515</v>
       </c>
       <c r="O42" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P42" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q42" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R42" t="s">
-        <v>530</v>
+        <v>584</v>
       </c>
       <c r="S42" t="s">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="T42" t="s">
-        <v>573</v>
+        <v>635</v>
       </c>
       <c r="U42" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V42" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W42" t="s">
         <v>2</v>
       </c>
       <c r="X42" t="s">
-        <v>620</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="AA42" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB42" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC42" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -5629,73 +5857,85 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E43" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="F43" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="G43" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="H43" t="s">
-        <v>299</v>
+        <v>322</v>
+      </c>
+      <c r="I43" t="s">
+        <v>358</v>
       </c>
       <c r="J43" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K43" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="L43" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="M43" t="s">
-        <v>471</v>
+        <v>516</v>
       </c>
       <c r="N43" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O43" t="s">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="P43" t="s">
-        <v>482</v>
+        <v>537</v>
       </c>
       <c r="Q43" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="R43" t="s">
-        <v>531</v>
+        <v>585</v>
       </c>
       <c r="S43" t="s">
-        <v>546</v>
+        <v>608</v>
+      </c>
+      <c r="T43" t="s">
+        <v>636</v>
       </c>
       <c r="U43" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V43" t="s">
+        <v>280</v>
       </c>
       <c r="W43" t="s">
         <v>2</v>
       </c>
       <c r="X43" t="s">
-        <v>621</v>
+        <v>686</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>699</v>
       </c>
       <c r="AA43" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="AB43" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC43" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -5703,73 +5943,82 @@
         <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="F44" t="s">
-        <v>246</v>
+        <v>201</v>
       </c>
       <c r="G44" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H44" t="s">
-        <v>300</v>
+        <v>323</v>
+      </c>
+      <c r="I44" t="s">
+        <v>359</v>
       </c>
       <c r="J44" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K44" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="L44" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="M44" t="s">
-        <v>472</v>
+        <v>517</v>
       </c>
       <c r="N44" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="O44" t="s">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="P44" t="s">
-        <v>482</v>
+        <v>538</v>
       </c>
       <c r="Q44" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="R44" t="s">
-        <v>532</v>
+        <v>586</v>
       </c>
       <c r="S44" t="s">
-        <v>546</v>
+        <v>604</v>
+      </c>
+      <c r="T44" t="s">
+        <v>637</v>
       </c>
       <c r="U44" t="s">
-        <v>257</v>
+        <v>644</v>
+      </c>
+      <c r="V44" t="s">
+        <v>280</v>
       </c>
       <c r="W44" t="s">
         <v>2</v>
       </c>
       <c r="X44" t="s">
-        <v>622</v>
+        <v>687</v>
       </c>
       <c r="AA44" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="AB44" t="s">
-        <v>632</v>
+        <v>704</v>
       </c>
       <c r="AC44" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -5777,79 +6026,82 @@
         <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F45" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H45" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="I45" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="J45" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K45" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="L45" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="M45" t="s">
-        <v>473</v>
+        <v>518</v>
+      </c>
+      <c r="N45" t="s">
+        <v>529</v>
       </c>
       <c r="O45" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="P45" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="Q45" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="R45" t="s">
-        <v>533</v>
+        <v>587</v>
       </c>
       <c r="S45" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="T45" t="s">
-        <v>574</v>
+        <v>638</v>
       </c>
       <c r="U45" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V45" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W45" t="s">
         <v>2</v>
       </c>
       <c r="X45" t="s">
-        <v>623</v>
+        <v>688</v>
       </c>
       <c r="AA45" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="AB45" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC45" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -5857,79 +6109,73 @@
         <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E46" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="G46" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H46" t="s">
-        <v>302</v>
-      </c>
-      <c r="I46" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J46" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K46" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="L46" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="M46" t="s">
-        <v>474</v>
+        <v>519</v>
+      </c>
+      <c r="N46" t="s">
+        <v>529</v>
       </c>
       <c r="O46" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P46" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="Q46" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="R46" t="s">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="S46" t="s">
-        <v>547</v>
-      </c>
-      <c r="T46" t="s">
-        <v>575</v>
+        <v>609</v>
       </c>
       <c r="U46" t="s">
-        <v>579</v>
-      </c>
-      <c r="V46" t="s">
-        <v>257</v>
+        <v>644</v>
       </c>
       <c r="W46" t="s">
         <v>2</v>
       </c>
       <c r="X46" t="s">
-        <v>624</v>
+        <v>689</v>
       </c>
       <c r="AA46" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AB46" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC46" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="47" spans="1:29">
@@ -5937,85 +6183,79 @@
         <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E47" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="F47" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="G47" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="H47" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="I47" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="J47" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K47" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="M47" t="s">
-        <v>475</v>
-      </c>
-      <c r="N47" t="s">
-        <v>478</v>
+        <v>520</v>
       </c>
       <c r="O47" t="s">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="P47" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="Q47" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="R47" t="s">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="S47" t="s">
-        <v>548</v>
+        <v>603</v>
       </c>
       <c r="T47" t="s">
-        <v>576</v>
+        <v>639</v>
       </c>
       <c r="U47" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V47" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W47" t="s">
         <v>2</v>
       </c>
       <c r="X47" t="s">
-        <v>625</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>628</v>
+        <v>690</v>
       </c>
       <c r="AA47" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="AB47" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC47" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="48" spans="1:29">
@@ -6023,79 +6263,73 @@
         <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="G48" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H48" t="s">
-        <v>304</v>
-      </c>
-      <c r="I48" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J48" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="K48" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="L48" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="M48" t="s">
-        <v>476</v>
+        <v>521</v>
+      </c>
+      <c r="N48" t="s">
+        <v>529</v>
       </c>
       <c r="O48" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="P48" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="Q48" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="R48" t="s">
-        <v>536</v>
+        <v>590</v>
       </c>
       <c r="S48" t="s">
-        <v>543</v>
-      </c>
-      <c r="T48" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="U48" t="s">
-        <v>579</v>
-      </c>
-      <c r="V48" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W48" t="s">
         <v>2</v>
       </c>
       <c r="X48" t="s">
-        <v>626</v>
+        <v>691</v>
       </c>
       <c r="AA48" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="AB48" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC48" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="49" spans="1:29">
@@ -6103,79 +6337,547 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E49" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="G49" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H49" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="I49" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="J49" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="K49" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="L49" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s">
-        <v>477</v>
+        <v>522</v>
+      </c>
+      <c r="N49" t="s">
+        <v>530</v>
       </c>
       <c r="O49" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="P49" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="Q49" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="R49" t="s">
-        <v>537</v>
+        <v>591</v>
       </c>
       <c r="S49" t="s">
-        <v>547</v>
+        <v>604</v>
       </c>
       <c r="T49" t="s">
-        <v>578</v>
+        <v>640</v>
       </c>
       <c r="U49" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="V49" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="W49" t="s">
         <v>2</v>
       </c>
       <c r="X49" t="s">
-        <v>627</v>
+        <v>692</v>
       </c>
       <c r="AA49" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="AB49" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="AC49" t="s">
-        <v>635</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" t="s">
+        <v>234</v>
+      </c>
+      <c r="F50" t="s">
+        <v>229</v>
+      </c>
+      <c r="G50" t="s">
+        <v>279</v>
+      </c>
+      <c r="H50" t="s">
+        <v>329</v>
+      </c>
+      <c r="J50" t="s">
+        <v>367</v>
+      </c>
+      <c r="K50" t="s">
+        <v>415</v>
+      </c>
+      <c r="L50" t="s">
+        <v>469</v>
+      </c>
+      <c r="M50" t="s">
+        <v>523</v>
+      </c>
+      <c r="N50" t="s">
+        <v>529</v>
+      </c>
+      <c r="O50" t="s">
+        <v>532</v>
+      </c>
+      <c r="P50" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>541</v>
+      </c>
+      <c r="R50" t="s">
+        <v>592</v>
+      </c>
+      <c r="S50" t="s">
+        <v>605</v>
+      </c>
+      <c r="U50" t="s">
+        <v>644</v>
+      </c>
+      <c r="W50" t="s">
+        <v>2</v>
+      </c>
+      <c r="X50" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" t="s">
+        <v>278</v>
+      </c>
+      <c r="G51" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" t="s">
+        <v>330</v>
+      </c>
+      <c r="I51" t="s">
+        <v>363</v>
+      </c>
+      <c r="J51" t="s">
+        <v>367</v>
+      </c>
+      <c r="K51" t="s">
+        <v>416</v>
+      </c>
+      <c r="L51" t="s">
+        <v>470</v>
+      </c>
+      <c r="M51" t="s">
+        <v>524</v>
+      </c>
+      <c r="O51" t="s">
+        <v>531</v>
+      </c>
+      <c r="P51" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>539</v>
+      </c>
+      <c r="R51" t="s">
+        <v>593</v>
+      </c>
+      <c r="S51" t="s">
+        <v>603</v>
+      </c>
+      <c r="T51" t="s">
+        <v>641</v>
+      </c>
+      <c r="U51" t="s">
+        <v>644</v>
+      </c>
+      <c r="V51" t="s">
+        <v>280</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+      <c r="X51" t="s">
+        <v>694</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>699</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" t="s">
+        <v>236</v>
+      </c>
+      <c r="F52" t="s">
+        <v>257</v>
+      </c>
+      <c r="G52" t="s">
+        <v>279</v>
+      </c>
+      <c r="H52" t="s">
+        <v>331</v>
+      </c>
+      <c r="I52" t="s">
+        <v>364</v>
+      </c>
+      <c r="J52" t="s">
+        <v>367</v>
+      </c>
+      <c r="K52" t="s">
+        <v>417</v>
+      </c>
+      <c r="L52" t="s">
+        <v>471</v>
+      </c>
+      <c r="M52" t="s">
+        <v>525</v>
+      </c>
+      <c r="O52" t="s">
+        <v>531</v>
+      </c>
+      <c r="P52" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>539</v>
+      </c>
+      <c r="R52" t="s">
+        <v>594</v>
+      </c>
+      <c r="S52" t="s">
+        <v>605</v>
+      </c>
+      <c r="T52" t="s">
+        <v>642</v>
+      </c>
+      <c r="U52" t="s">
+        <v>644</v>
+      </c>
+      <c r="V52" t="s">
+        <v>644</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2</v>
+      </c>
+      <c r="X52" t="s">
+        <v>695</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>704</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>216</v>
+      </c>
+      <c r="F53" t="s">
+        <v>265</v>
+      </c>
+      <c r="G53" t="s">
+        <v>279</v>
+      </c>
+      <c r="H53" t="s">
+        <v>332</v>
+      </c>
+      <c r="J53" t="s">
+        <v>367</v>
+      </c>
+      <c r="K53" t="s">
+        <v>418</v>
+      </c>
+      <c r="L53" t="s">
+        <v>472</v>
+      </c>
+      <c r="M53" t="s">
+        <v>526</v>
+      </c>
+      <c r="N53" t="s">
+        <v>529</v>
+      </c>
+      <c r="O53" t="s">
+        <v>532</v>
+      </c>
+      <c r="P53" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>541</v>
+      </c>
+      <c r="R53" t="s">
+        <v>595</v>
+      </c>
+      <c r="S53" t="s">
+        <v>605</v>
+      </c>
+      <c r="U53" t="s">
+        <v>280</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X53" t="s">
+        <v>696</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" t="s">
+        <v>237</v>
+      </c>
+      <c r="F54" t="s">
+        <v>193</v>
+      </c>
+      <c r="G54" t="s">
+        <v>279</v>
+      </c>
+      <c r="H54" t="s">
+        <v>333</v>
+      </c>
+      <c r="I54" t="s">
+        <v>365</v>
+      </c>
+      <c r="J54" t="s">
+        <v>367</v>
+      </c>
+      <c r="K54" t="s">
+        <v>419</v>
+      </c>
+      <c r="L54" t="s">
+        <v>473</v>
+      </c>
+      <c r="M54" t="s">
+        <v>527</v>
+      </c>
+      <c r="O54" t="s">
+        <v>531</v>
+      </c>
+      <c r="P54" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>539</v>
+      </c>
+      <c r="R54" t="s">
+        <v>596</v>
+      </c>
+      <c r="S54" t="s">
+        <v>607</v>
+      </c>
+      <c r="T54" t="s">
+        <v>643</v>
+      </c>
+      <c r="U54" t="s">
+        <v>644</v>
+      </c>
+      <c r="V54" t="s">
+        <v>280</v>
+      </c>
+      <c r="W54" t="s">
+        <v>2</v>
+      </c>
+      <c r="X54" t="s">
+        <v>697</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" t="s">
+        <v>238</v>
+      </c>
+      <c r="F55" t="s">
+        <v>246</v>
+      </c>
+      <c r="G55" t="s">
+        <v>279</v>
+      </c>
+      <c r="H55" t="s">
+        <v>334</v>
+      </c>
+      <c r="J55" t="s">
+        <v>366</v>
+      </c>
+      <c r="K55" t="s">
+        <v>420</v>
+      </c>
+      <c r="L55" t="s">
+        <v>474</v>
+      </c>
+      <c r="M55" t="s">
+        <v>528</v>
+      </c>
+      <c r="N55" t="s">
+        <v>529</v>
+      </c>
+      <c r="O55" t="s">
+        <v>532</v>
+      </c>
+      <c r="P55" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>541</v>
+      </c>
+      <c r="R55" t="s">
+        <v>597</v>
+      </c>
+      <c r="S55" t="s">
+        <v>604</v>
+      </c>
+      <c r="U55" t="s">
+        <v>280</v>
+      </c>
+      <c r="W55" t="s">
+        <v>2</v>
+      </c>
+      <c r="X55" t="s">
+        <v>698</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>707</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340218</t>
+          <t>159273</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LUIS JAVIER</t>
+          <t xml:space="preserve">ALFONSO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,14 +883,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4463394887</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SAN FRANCISCO</t>
-        </is>
-      </c>
+          <t>7351340175</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -898,60 +894,56 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06-02-2009</t>
+          <t>21-09-1984</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LUISJAVIER@GMAIL.COM</t>
+          <t>P8INEDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-02-2026 15:31:29</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>20-03-2023 11:49:41</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 15:33:41</t>
+          <t>06-02-2026 14:13:33</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:32:47</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,36 +951,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26090522014690001111</t>
+          <t>26090522136900001292</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340226</t>
+          <t>293612</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>91110</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>ASHLEY SOPHIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NUÑO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,14 +1010,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6612457962</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
-        </is>
-      </c>
+          <t>6642018969</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1033,17 +1021,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-11-1988</t>
+          <t>13-12-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
+          <t>ANA.RODRIGUEZ300@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:17</t>
+          <t>19-05-2025 14:37:27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1053,44 +1041,36 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 15:51:10</t>
+          <t>03-02-2026 12:59:16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:48:41</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1098,14 +1078,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090522015280001114</t>
+          <t>26090522038960001153</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1122,12 +1102,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>159273</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56809</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALFONSO </t>
+          <t>DANIELA FERNANDA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">IBARRA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PINEDA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,28 +1137,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7351340175</t>
+          <t>6611029556</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21-09-1984</t>
+          <t>13-11-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>P8INEDA@GMAIL.COM</t>
+          <t>IABARAHERMNANDEZ@GMIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20-03-2023 11:49:41</t>
+          <t>14-11-2023 12:46:29</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1193,28 +1173,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>06-02-2026 14:13:33</t>
+          <t>09-02-2026 07:12:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1225,14 +1205,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522136900001292</t>
+          <t>26090522182800001336</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1249,12 +1229,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>293612</t>
+          <t>340226</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1244,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ASHLEY SOPHIA</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>NUÑO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,10 +1264,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6642018969</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6612457962</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1295,17 +1279,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-12-2010</t>
+          <t>10-11-1988</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ANA.RODRIGUEZ300@GMAIL.COM</t>
+          <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19-05-2025 14:37:27</t>
+          <t>02-02-2026 15:45:17</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1315,36 +1299,44 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 12:59:16</t>
+          <t>02-02-2026 15:51:10</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:48:41</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1352,14 +1344,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26090522038960001153</t>
+          <t>26090522015280001114</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1376,12 +1368,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>206537</t>
+          <t>340323</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1383,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DANIELA FERNANDA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBARRA </t>
+          <t xml:space="preserve"> CURIEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,67 +1403,75 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6611029556</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6195181188</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C D LOS FISIOS</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-11-2008</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IABARAHERMNANDEZ@GMIL.COM</t>
+          <t>LUIS.CURIEL4@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14-11-2023 12:46:29</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:55:59</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>09-02-2026 07:12:53</t>
+          <t>02-02-2026 17:59:38</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:58:39</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26090522182800001336</t>
+          <t>26090522019700001121</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340323</t>
+          <t>340218</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>LUIS JAVIER</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CURIEL</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6195181188</t>
+          <t>4463394887</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C D LOS FISIOS</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>06-02-2009</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LUIS.CURIEL4@OUTLOOK.COM</t>
+          <t>LUISJAVIER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 17:55:59</t>
+          <t>02-02-2026 15:31:29</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 17:59:38</t>
+          <t>02-02-2026 15:33:41</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 17:58:39</t>
+          <t>02-02-2026 15:32:47</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26090522019700001121</t>
+          <t>26090522014690001111</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1626,24 +1626,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340774</t>
+          <t>340214</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AARON DE JESUS</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PEÑUÑURI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MUÑIZ</t>
+          <t>ITURIOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6611193456</t>
+          <t>6441340324</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11-07-2000</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AARONRAMIREZ12323@GMAIL.COM</t>
+          <t>MARTINITURIOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:09:17</t>
+          <t>02-02-2026 15:27:52</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1719,17 +1719,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:14:38</t>
+          <t>02-02-2026 15:29:47</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:14:07</t>
+          <t>02-02-2026 15:29:21</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26090522052370001168</t>
+          <t>26090522014560001110</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340214</t>
+          <t>340774</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>AARON DE JESUS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PEÑUÑURI</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ITURIOS</t>
+          <t>MUÑIZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6441340324</t>
+          <t>6611193456</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>11-07-2000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MARTINITURIOS@GMAIL.COM</t>
+          <t>AARONRAMIREZ12323@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:27:52</t>
+          <t>03-02-2026 18:09:17</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1854,17 +1854,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:47</t>
+          <t>03-02-2026 18:14:38</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:21</t>
+          <t>03-02-2026 18:14:07</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26090522014560001110</t>
+          <t>26090522052370001168</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1908,12 +1908,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341476</t>
+          <t>340078</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTOHONY </t>
+          <t xml:space="preserve">MEGAN VICTORIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1943,67 +1943,75 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6611726857</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6611255339</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AGUSTIN DE ITUBIDE 418</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06-06-2009</t>
+          <t>18-08-1991</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
+          <t>VICTORIAVAL150891@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-02-2026 06:06:25</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 12:17:03</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06-02-2026 06:07:12</t>
+          <t>02-02-2026 12:23:43</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-02-2026 12:20:17</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2011,14 +2019,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522129910001272</t>
+          <t>26090522008660001094</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2035,12 +2043,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341231</t>
+          <t>340119</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2050,17 +2058,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LILA ELENA</t>
+          <t xml:space="preserve">FRANCISCA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>ALQUISIRA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GARNIDO</t>
+          <t>SANTANA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2070,12 +2078,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6641096895</t>
+          <t>6627448010</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LAZARO CARDENAS  8741</t>
+          <t>FRANCISCO BONILLA 14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2085,17 +2093,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19-04-1980</t>
+          <t>10-10-1973</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ELENA_BARAJAS@HOTMAIL.COM</t>
+          <t>ALQUISIRASANTANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>05-02-2026 08:07:14</t>
+          <t>02-02-2026 13:09:36</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2116,17 +2124,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>12-02-2026 08:10:36</t>
+          <t>02-02-2026 13:12:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>12-02-2026 08:09:33</t>
+          <t>02-02-2026 13:11:40</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2136,7 +2144,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2146,19 +2154,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522288870001483</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522010420001102</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>499</t>
@@ -2178,12 +2178,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341246</t>
+          <t>340511</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATZIRY GABRIELA </t>
+          <t>EDGAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2213,28 +2213,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5545626086</t>
+          <t>6611146703</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26-03-2006</t>
+          <t>06-01-2010</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SANDOVALATZIRY@GMAIL.COM</t>
+          <t>HERRARAGONZEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-02-2026 09:21:15</t>
+          <t>03-02-2026 10:48:54</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2249,28 +2249,28 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-02-2026 11:30:26</t>
+          <t>03-02-2026 10:49:46</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2281,22 +2281,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522134390001286</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522036450001146</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2313,12 +2305,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340078</t>
+          <t>341231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGAN VICTORIA </t>
+          <t>LILA ELENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARNIDO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,12 +2340,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6611255339</t>
+          <t>6641096895</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AGUSTIN DE ITUBIDE 418</t>
+          <t>LAZARO CARDENAS  8741</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2363,17 +2355,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18-08-1991</t>
+          <t>19-04-1980</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>VICTORIAVAL150891@GMAIL.COM</t>
+          <t>ELENA_BARAJAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 12:17:03</t>
+          <t>05-02-2026 08:07:14</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2394,17 +2386,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 12:23:43</t>
+          <t>12-02-2026 08:10:36</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-02-2026 12:20:17</t>
+          <t>12-02-2026 08:09:33</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2414,7 +2406,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2424,11 +2416,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522008660001094</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26090522288870001483</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2448,12 +2448,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340119</t>
+          <t>283070</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2463,17 +2463,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCA </t>
+          <t xml:space="preserve">ESTHELA ESMERALDA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ALQUISIRA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANTANA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6627448010</t>
+          <t>6643229624</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FRANCISCO BONILLA 14</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2498,20 +2498,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10-10-1973</t>
+          <t>26-09-1993</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ALQUISIRASANTANA@GMAIL.COM</t>
+          <t>PROF.ESMERALDALOPEZ@GMIAL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 13:09:36</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>13-03-2025 16:34:09</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2529,17 +2533,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 13:12:52</t>
+          <t>20-02-2026 21:03:03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-02-2026 13:11:40</t>
+          <t>20-02-2026 21:02:28</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26090522010420001102</t>
+          <t>26130522537140003237</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2583,12 +2587,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340511</t>
+          <t>310494</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2598,17 +2602,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR ALEJANDRO</t>
+          <t>ROMINA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2618,28 +2622,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6611146703</t>
+          <t>6241476864</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06-01-2010</t>
+          <t>13-06-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>HERRARAGONZEZ@GMAIL.COM</t>
+          <t>ROMINAMENDOZA771@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-02-2026 10:48:54</t>
+          <t>20-08-2025 21:04:13</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2664,18 +2668,18 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 10:49:46</t>
+          <t>19-02-2026 09:19:08</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2686,11 +2690,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26090522036450001146</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26090522490090001681</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>399</t>
@@ -2710,12 +2722,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341958</t>
+          <t>340507</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2725,17 +2737,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDIDO </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>VEZDUZCO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2745,7 +2757,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7224496778</t>
+          <t>6611108616</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2756,17 +2768,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>02-02-1983</t>
+          <t>10-03-2010</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
+          <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>08-02-2026 14:21:04</t>
+          <t>03-02-2026 10:45:27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2781,28 +2793,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>08-02-2026 14:23:23</t>
+          <t>03-02-2026 10:46:51</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2813,14 +2825,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26090522172990001325</t>
+          <t>26090522036400001145</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2837,12 +2849,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340507</t>
+          <t>340800</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2852,17 +2864,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>ANDONAEGUI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VEZDUZCO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2872,10 +2884,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6611108616</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6643700182</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LOMAS DE BELEN</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2883,17 +2899,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10-03-2010</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
+          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-02-2026 10:45:27</t>
+          <t>03-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2903,22 +2919,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 10:46:51</t>
+          <t>03-02-2026 19:06:01</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2926,13 +2942,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:05:31</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2940,14 +2964,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26090522036400001145</t>
+          <t>26090522055130001172</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2964,12 +2988,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342022</t>
+          <t>340894</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2979,17 +3003,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN URIEL </t>
+          <t xml:space="preserve">ANA SILVIA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2999,67 +3023,79 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6611116361</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6611169305</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN FERNANDO</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12-01-2008</t>
+          <t>21-10-1988</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>URIELCORTEZ1212@GMAIL.COM</t>
+          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 07:08:58</t>
+          <t>04-02-2026 08:33:41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:14</t>
+          <t>16-02-2026 08:38:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:37:45</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3067,14 +3103,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26090522182720001335</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26090522381310001574</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3091,12 +3135,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>341246</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3106,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGDA LAURA </t>
+          <t xml:space="preserve">ATZIRY GABRIELA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3126,14 +3170,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6611721658</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>LUIS CABRERA  20</t>
-        </is>
-      </c>
+          <t>5545626086</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3141,60 +3181,56 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-07-1996</t>
+          <t>26-03-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NAJERAVILLA3@GMAIL.COM</t>
+          <t>SANDOVALATZIRY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 07:22:55</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>05-02-2026 09:21:15</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 07:26:06</t>
+          <t>06-02-2026 11:30:26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>09-02-2026 07:25:07</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3202,14 +3238,22 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26090522183260001338</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26090522134390001286</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3226,12 +3270,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340800</t>
+          <t>334877</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3241,17 +3285,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>KAROL IRENE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ANDONAEGUI</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3261,32 +3305,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6643700182</t>
+          <t>6644046543</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOMAS DE BELEN</t>
+          <t>OAXACA  2053</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>21-09-1997</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
+          <t>MUNOZHERNANDEZKAROL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-02-2026 19:02:55</t>
+          <t>15-01-2026 00:11:29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3301,27 +3345,27 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-02-2026 19:06:01</t>
+          <t>19-02-2026 13:40:21</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:31</t>
+          <t>19-02-2026 13:39:32</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3341,14 +3385,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26090522055130001172</t>
+          <t>26090522494370001695</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3365,12 +3409,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340894</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3380,17 +3424,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA SILVIA </t>
+          <t xml:space="preserve">ANTOHONY </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3400,79 +3444,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6611169305</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>HACIENDA SAN FERNANDO</t>
-        </is>
-      </c>
+          <t>6611726857</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21-10-1988</t>
+          <t>06-06-2009</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
+          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-02-2026 08:33:41</t>
+          <t>06-02-2026 06:06:25</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:43</t>
+          <t>06-02-2026 06:07:12</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:37:45</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3480,22 +3512,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26090522381310001574</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522129910001272</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3512,12 +3536,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>341574</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3527,17 +3551,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LESLIE ANGELICA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AVALOS</t>
+          <t>VALDES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>OLIVAREZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3547,75 +3571,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6612393040</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>BUENA VISTA</t>
-        </is>
-      </c>
+          <t>7291799451</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>11-03-2003</t>
+          <t>07-06-1991</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ANGIELESLIE@GMAIL.COM</t>
+          <t>OLIVAREZVALDES354@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-02-2026 14:06:05</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>06-02-2026 14:15:10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-02-2026 14:10:01</t>
+          <t>06-02-2026 14:17:32</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>04-02-2026 14:09:27</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3623,36 +3639,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26090522075300001207</t>
+          <t>26090522136960001293</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342352</t>
+          <t>341004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3662,17 +3678,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ALEXA CAMILA</t>
+          <t>LESLIE ANGELICA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>AVALOS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZATARAIN</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3682,12 +3698,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6673421986</t>
+          <t>6612393040</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AMPLIACION REFORMA</t>
+          <t>BUENA VISTA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3697,17 +3713,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02-01-2006</t>
+          <t>11-03-2003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
+          <t>ANGIELESLIE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 17:48:28</t>
+          <t>04-02-2026 14:06:05</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3728,17 +3744,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>11-02-2026 17:26:32</t>
+          <t>04-02-2026 14:10:01</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11-02-2026 17:25:59</t>
+          <t>04-02-2026 14:09:27</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3758,19 +3774,11 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26090522271360001469</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522075300001207</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3790,12 +3798,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341574</t>
+          <t>340995</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3805,17 +3813,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t xml:space="preserve">CABELLO </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OLIVAREZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3825,10 +3833,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7291799451</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6616162514</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EL NOGAL 7207</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3836,56 +3848,60 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07-06-1991</t>
+          <t>07-02-1966</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>OLIVAREZVALDES354@GMAIL.COM</t>
+          <t>MCELEEZ5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>06-02-2026 14:15:10</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 13:46:53</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>06-02-2026 14:17:32</t>
+          <t>04-02-2026 13:50:36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>04-02-2026 13:49:21</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3893,14 +3909,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26090522136960001293</t>
+          <t>26090522075050001206</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3917,12 +3933,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341089</t>
+          <t>342032</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3932,17 +3948,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GRISELDA</t>
+          <t xml:space="preserve">MAGDA LAURA </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3952,12 +3968,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6612393915</t>
+          <t>6611721658</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COLONIA MORELOS</t>
+          <t>LUIS CABRERA  20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3967,52 +3983,48 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>17-01-1986</t>
+          <t>10-07-1996</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MARIOORIVERAAV77@GMAIL.COM</t>
+          <t>NAJERAVILLA3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>04-02-2026 16:50:13</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 07:22:55</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:59</t>
+          <t>09-02-2026 07:26:06</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:19</t>
+          <t>09-02-2026 07:25:07</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4022,7 +4034,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4032,14 +4044,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26090522080820001212</t>
+          <t>26090522183260001338</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4056,12 +4068,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342083</t>
+          <t>341958</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4071,17 +4083,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ALAN YOSUEL</t>
+          <t xml:space="preserve">CANDIDO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ARREDONDO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4091,14 +4103,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6645807893</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>CARRETERA LIBRE ENCENADA</t>
-        </is>
-      </c>
+          <t>7224496778</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4106,60 +4114,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03-09-1993</t>
+          <t>02-02-1983</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>YOSUELMORENO@GMAIL.COM</t>
+          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 09:56:51</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>08-02-2026 14:21:04</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 09:59:58</t>
+          <t>08-02-2026 14:23:23</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>09-02-2026 09:59:31</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4167,14 +4171,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26090522187170001346</t>
+          <t>26090522172990001325</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4191,12 +4195,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342555</t>
+          <t>342022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4206,17 +4210,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSEFINA</t>
+          <t xml:space="preserve">CRISTIAN URIEL </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GUDILLO</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WENCESLAO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4226,28 +4230,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6611143877</t>
+          <t>6611116361</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>23-06-1960</t>
+          <t>12-01-2008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
+          <t>URIELCORTEZ1212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 08:50:56</t>
+          <t>09-02-2026 07:08:58</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4262,22 +4266,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:46</t>
+          <t>09-02-2026 07:10:14</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4294,22 +4298,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26090522289640001487</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522182720001335</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4326,12 +4322,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340995</t>
+          <t>342083</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4341,17 +4337,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>ALAN YOSUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABELLO </t>
+          <t>ARREDONDO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4361,12 +4357,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6616162514</t>
+          <t>6645807893</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EL NOGAL 7207</t>
+          <t>CARRETERA LIBRE ENCENADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4376,17 +4372,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>07-02-1966</t>
+          <t>03-09-1993</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MCELEEZ5@GMAIL.COM</t>
+          <t>YOSUELMORENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>04-02-2026 13:46:53</t>
+          <t>09-02-2026 09:56:51</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4407,17 +4403,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>04-02-2026 13:50:36</t>
+          <t>09-02-2026 09:59:58</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>04-02-2026 13:49:21</t>
+          <t>09-02-2026 09:59:31</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4427,7 +4423,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4437,7 +4433,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26090522075050001206</t>
+          <t>26090522187170001346</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4461,12 +4457,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343039</t>
+          <t>342121</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4476,17 +4472,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t xml:space="preserve">TOMAS </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>OLARTE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4496,14 +4492,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6862144489</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>PUERTO NUEVO</t>
-        </is>
-      </c>
+          <t>6613322085</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4511,60 +4503,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-05-1979</t>
+          <t>15-02-2009</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+          <t>LARTESLAZAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:54</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 11:46:22</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11-02-2026 16:31:31</t>
+          <t>09-02-2026 11:48:02</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>11-02-2026 16:29:22</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4572,36 +4560,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26090522268680001467</t>
+          <t>26090522189440001352</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Anton Omar Sanchez Ruiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342563</t>
+          <t>342571</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4611,17 +4599,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ALEXIS SEBASTIAN</t>
+          <t>EDNA YADIRA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACENCIO </t>
+          <t xml:space="preserve">DELA CRUZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4631,10 +4619,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6611400473</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>3251050507</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>PABLO BONILLA 22</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4642,56 +4634,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07-05-2006</t>
+          <t>10-05-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ACENCALEXIS@GMAIL.COM</t>
+          <t>EDNADELACRUZ64@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 09:22:29</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 09:38:32</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 09:23:44</t>
+          <t>12-02-2026 09:19:27</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>12-02-2026 09:18:59</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4699,14 +4695,22 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26090522226960001399</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26090522290010001489</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4723,12 +4727,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342570</t>
+          <t>342563</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4738,17 +4742,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARTHA ISABEL</t>
+          <t>ALEXIS SEBASTIAN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t xml:space="preserve">ACENCIO </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ARAMBULA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4758,14 +4762,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6611362361</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>CUMBRES SAJAMA</t>
-        </is>
-      </c>
+          <t>6611400473</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4773,60 +4773,56 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>09-02-1988</t>
+          <t>07-05-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
+          <t>ACENCALEXIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 09:36:01</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>10-02-2026 09:22:29</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12-02-2026 09:25:39</t>
+          <t>10-02-2026 09:23:44</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:24:12</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4834,18 +4830,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26090522290130001490</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522226960001399</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4862,12 +4854,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342575</t>
+          <t>342570</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4877,17 +4869,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DEL ROSARIO </t>
+          <t>MARTHA ISABEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUEZ </t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>ARAMBULA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4897,12 +4889,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6648438264</t>
+          <t>6611362361</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CALLE LAGUNA 2043</t>
+          <t>CUMBRES SAJAMA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4912,17 +4904,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-03-1981</t>
+          <t>09-02-1988</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
+          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 10:09:05</t>
+          <t>10-02-2026 09:36:01</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4943,17 +4935,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 10:13:10</t>
+          <t>12-02-2026 09:25:39</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>10-02-2026 10:12:39</t>
+          <t>12-02-2026 09:24:12</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4963,7 +4955,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4973,10 +4965,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26090522227950001405</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
+          <t>26090522290130001490</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4985,24 +4981,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342121</t>
+          <t>342575</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5012,17 +5008,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOMAS </t>
+          <t xml:space="preserve">MARIA DEL ROSARIO </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OLARTE</t>
+          <t xml:space="preserve">MARQUEZ </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5032,67 +5028,75 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6613322085</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6648438264</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CALLE LAGUNA 2043</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-02-2009</t>
+          <t>23-03-1981</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LARTESLAZAE@GMAIL.COM</t>
+          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 11:46:22</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 10:09:05</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 11:48:02</t>
+          <t>10-02-2026 10:13:10</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>10-02-2026 10:12:39</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5100,36 +5104,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26090522189440001352</t>
+          <t>26090522227950001405</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342772</t>
+          <t>342458</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5139,17 +5143,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FATIMA GUADALUPE</t>
+          <t xml:space="preserve">GABRIELA CAROLINA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GAONA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GERONIMO</t>
+          <t xml:space="preserve">OSORIO </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5159,28 +5163,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6611162957</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6631533043</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CUENCA DIAZ</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-10-2008</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FATIMAGUADALUPEG76@GMAIL.COM</t>
+          <t>SAGAOS0910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 17:56:14</t>
+          <t>09-02-2026 19:49:38</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5190,36 +5198,44 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 17:57:08</t>
+          <t>09-02-2026 19:56:45</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:56:10</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5227,14 +5243,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26090522241950001426</t>
+          <t>26090522212640001380</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5386,12 +5402,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342571</t>
+          <t>342772</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5401,17 +5417,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EDNA YADIRA</t>
+          <t>FATIMA GUADALUPE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELA CRUZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>GERONIMO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5421,14 +5437,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3251050507</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>PABLO BONILLA 22</t>
-        </is>
-      </c>
+          <t>6611162957</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5436,60 +5448,56 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10-05-1995</t>
+          <t>03-10-2008</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>EDNADELACRUZ64@GMAIL.COM</t>
+          <t>FATIMAGUADALUPEG76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 09:38:32</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>10-02-2026 17:56:14</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>12-02-2026 09:19:27</t>
+          <t>10-02-2026 17:57:08</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:18:59</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5497,22 +5505,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26090522290010001489</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522241950001426</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5529,12 +5529,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344063</t>
+          <t>340206</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR </t>
+          <t>LIZETH GUADALUPE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5564,67 +5564,75 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6616165544</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6648559380</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>20-12-1993</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ACOSTAARANDA@GMAIL.COM</t>
+          <t>SOLANOLISETH93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 13:14:13</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 15:21:09</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 13:15:43</t>
+          <t>02-02-2026 15:25:17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:24:50</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5632,24 +5640,24 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26090522388310001582</t>
+          <t>26090522014340001109</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5791,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342458</t>
+          <t>343260</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5798,17 +5806,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA CAROLINA </t>
+          <t xml:space="preserve">LUIS ALFONSO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA </t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSORIO </t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5818,12 +5826,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6631533043</t>
+          <t>6611160032</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CUENCA DIAZ</t>
+          <t>PACIFICO 2651</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5833,52 +5841,48 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>19-10-1970</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>SAGAOS0910@GMAIL.COM</t>
+          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:38</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 14:13:40</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 19:56:45</t>
+          <t>12-02-2026 14:15:35</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>09-02-2026 19:56:10</t>
+          <t>12-02-2026 14:14:58</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5898,14 +5902,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26090522212640001380</t>
+          <t>26090522294330001500</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5922,12 +5926,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343260</t>
+          <t>342767</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5937,17 +5941,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ALFONSO </t>
+          <t>LESLI TERESA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>GERONIMO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5957,75 +5961,67 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6611160032</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>PACIFICO 2651</t>
-        </is>
-      </c>
+          <t>6611143806</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19-10-1970</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
+          <t>LESLITERESAG09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>12-02-2026 14:13:40</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>10-02-2026 17:51:20</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>12-02-2026 14:15:35</t>
+          <t>10-02-2026 17:52:10</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>12-02-2026 14:14:58</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6033,14 +6029,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26090522294330001500</t>
+          <t>26090522241540001424</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6057,12 +6053,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342767</t>
+          <t>342629</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6072,17 +6068,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LESLI TERESA</t>
+          <t>JORGE ENRIQUE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GERONIMO</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6092,10 +6088,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6611143806</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6644644841</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ROSA MAR</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6103,42 +6103,38 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>28-10-1993</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LESLITERESAG09@GMAIL.COM</t>
+          <t>MELISAMARLUM1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 17:51:20</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:18:11</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 17:52:10</t>
+          <t>10-02-2026 14:24:03</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6146,13 +6142,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10-02-2026 14:22:52</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6160,14 +6164,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26090522241540001424</t>
+          <t>26090522232400001415</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6184,12 +6188,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>340206</t>
+          <t>341089</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6199,17 +6203,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LIZETH GUADALUPE</t>
+          <t>GRISELDA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6219,12 +6223,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6648559380</t>
+          <t>6612393915</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>COLONIA MORELOS</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6234,48 +6238,52 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20-12-1993</t>
+          <t>17-01-1986</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>SOLANOLISETH93@GMAIL.COM</t>
+          <t>MARIOORIVERAAV77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>02-02-2026 15:21:09</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>04-02-2026 16:50:13</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>02-02-2026 15:25:17</t>
+          <t>04-02-2026 16:55:59</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>02-02-2026 15:24:50</t>
+          <t>04-02-2026 16:55:19</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6285,7 +6293,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6295,36 +6303,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26090522014340001109</t>
+          <t>26090522080820001212</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343556</t>
+          <t>340796</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6334,17 +6342,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LAURA YAZMIN</t>
+          <t xml:space="preserve">MARILU </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CAPIZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6354,12 +6362,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6611352488</t>
+          <t>6645991198</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GALATEA MZA</t>
+          <t>JOSE MARIA IGLESIAS 20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6369,48 +6377,52 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>08-02-2003</t>
+          <t>06-04-1994</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>LAURACAPIZ5@GMAIL.COM</t>
+          <t>LICORTRUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:14</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>03-02-2026 18:55:15</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>13-02-2026 17:22:43</t>
+          <t>03-02-2026 19:00:59</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13-02-2026 17:21:47</t>
+          <t>03-02-2026 19:00:08</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6420,7 +6432,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6430,14 +6442,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26090522326300001537</t>
+          <t>26090522054800001170</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6454,12 +6466,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342629</t>
+          <t>343556</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6469,17 +6481,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JORGE ENRIQUE</t>
+          <t>LAURA YAZMIN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CAPIZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6489,12 +6501,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6644644841</t>
+          <t>6611352488</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ROSA MAR</t>
+          <t>GALATEA MZA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6504,17 +6516,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>28-10-1993</t>
+          <t>08-02-2003</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MELISAMARLUM1@GMAIL.COM</t>
+          <t>LAURACAPIZ5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 14:18:11</t>
+          <t>13-02-2026 17:19:14</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6535,17 +6547,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 14:24:03</t>
+          <t>13-02-2026 17:22:43</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10-02-2026 14:22:52</t>
+          <t>13-02-2026 17:21:47</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6565,7 +6577,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26090522232400001415</t>
+          <t>26090522326300001537</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6577,24 +6589,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344826</t>
+          <t>343524</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6604,17 +6616,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t>CLAUDIA ADRIANA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6624,39 +6636,35 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9517836968</t>
+          <t>6611173965</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
+          <t>LUCIO BLANCO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13-08-1999</t>
+          <t>13-04-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BH462951@GMAIL.COM</t>
+          <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18-02-2026 14:38:52</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:01:41</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6674,17 +6682,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18-02-2026 14:42:52</t>
+          <t>13-02-2026 16:08:34</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>18-02-2026 14:42:22</t>
+          <t>13-02-2026 16:07:45</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6704,7 +6712,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26090522463100001659</t>
+          <t>26090522323730001533</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6728,12 +6736,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344302</t>
+          <t>344421</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6743,48 +6751,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t xml:space="preserve">CASANDRA </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BERMUDEZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MELEMDREZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6611357801</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6319726958</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>11-05-2006</t>
+          <t>16-10-1993</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BERMUDEZALFREDO486@GMAIL.COM</t>
+          <t>MELEMDREZFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 18:36:55</t>
+          <t>17-02-2026 09:20:40</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6794,36 +6806,44 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 18:38:24</t>
+          <t>20-02-2026 09:43:23</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>20-02-2026 09:41:31</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6831,14 +6851,22 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26090522405140001594</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>26090522522690001726</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6855,12 +6883,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>340796</t>
+          <t>343605</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6870,52 +6898,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARILU </t>
+          <t xml:space="preserve">IVAN </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t xml:space="preserve">AVILEZ </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6645991198</t>
+          <t>6195778145</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JOSE MARIA IGLESIAS 20</t>
+          <t>LA BARCA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>06-04-1994</t>
+          <t>06-10-1971</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LICORTRUIZ@GMAIL.COM</t>
+          <t>CAGAOS0910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-02-2026 18:55:15</t>
+          <t>13-02-2026 19:48:54</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6940,17 +6968,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:59</t>
+          <t>13-02-2026 21:16:17</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:08</t>
+          <t>13-02-2026 21:15:42</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6960,7 +6988,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6970,10 +6998,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26090522054800001170</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
+          <t>26090522331810001546</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6994,12 +7026,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344072</t>
+          <t>344826</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7009,17 +7041,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINA </t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7029,32 +7061,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6645752792</t>
+          <t>9517836968</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AVENIDA VALLARTA 2110</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>21-01-2006</t>
+          <t>13-08-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>REPEZSERVANTESMARINA@GMAIL.COM</t>
+          <t>BH462951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-02-2026 13:36:33</t>
+          <t>18-02-2026 14:38:52</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7079,17 +7111,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>16-02-2026 13:47:02</t>
+          <t>18-02-2026 14:42:52</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>16-02-2026 13:45:53</t>
+          <t>18-02-2026 14:42:22</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7109,7 +7141,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26090522389160001583</t>
+          <t>26090522463100001659</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7133,12 +7165,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344823</t>
+          <t>344920</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7148,17 +7180,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ROSA ELENA</t>
+          <t xml:space="preserve">NAOMI NICOLE </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t xml:space="preserve">AGUIRRE </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7168,14 +7200,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9515137595</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
-        </is>
-      </c>
+          <t>6611134520</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7183,64 +7211,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>02-03-1998</t>
+          <t>18-03-2009</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
+          <t>CAMACHONAOIMI77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-02-2026 14:26:16</t>
+          <t>18-02-2026 18:04:22</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-02-2026 14:37:29</t>
+          <t>20-02-2026 16:49:34</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>18-02-2026 14:36:30</t>
-        </is>
-      </c>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7248,14 +7268,18 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26090522462920001658</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
+          <t>26090522530570001751</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7272,12 +7296,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343524</t>
+          <t>344072</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7287,17 +7311,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CLAUDIA ADRIANA</t>
+          <t xml:space="preserve">MARINA </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7307,12 +7331,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6611173965</t>
+          <t>6645752792</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LUCIO BLANCO</t>
+          <t>AVENIDA VALLARTA 2110</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7322,20 +7346,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13-04-1999</t>
+          <t>21-01-2006</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
+          <t>REPEZSERVANTESMARINA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>13-02-2026 16:01:41</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>16-02-2026 13:36:33</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7353,17 +7381,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>13-02-2026 16:08:34</t>
+          <t>16-02-2026 13:47:02</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13-02-2026 16:07:45</t>
+          <t>16-02-2026 13:45:53</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7383,7 +7411,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26090522323730001533</t>
+          <t>26090522389160001583</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7407,12 +7435,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343605</t>
+          <t>345346</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>87511</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7422,99 +7450,99 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVAN </t>
+          <t>ARNULFO MIGUEL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILEZ </t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5634728993</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAN DE AYUTLA LOTE 12 </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>23-05-1976</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>MIGUEL.A.PEREZ0723@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:58:03</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>20-02-2026 17:03:21</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>20-02-2026 17:02:35</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>6195778145</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>LA BARCA</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>06-10-1971</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>CAGAOS0910@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>13-02-2026 19:48:54</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>13-02-2026 21:16:17</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>13-02-2026 21:15:42</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7522,18 +7550,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26090522331810001546</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522531130001753</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7693,12 +7717,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>342352</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7708,17 +7732,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MARIA CONCEPCION</t>
+          <t>ALEXA CAMILA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>ZATARAIN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7728,12 +7752,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6611954909</t>
+          <t>6673421986</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TUXTLA GUTIERREZ</t>
+          <t>AMPLIACION REFORMA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7743,17 +7767,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21-04-2000</t>
+          <t>02-01-2006</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>MARIAZAMORA5432@HOTMAIL.COM</t>
+          <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:27:31</t>
+          <t>09-02-2026 17:48:28</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7774,17 +7798,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:59</t>
+          <t>11-02-2026 17:26:32</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:24</t>
+          <t>11-02-2026 17:25:59</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7804,11 +7828,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26090522247060001432</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26090522271360001469</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -7816,24 +7848,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343924</t>
+          <t>344302</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7843,17 +7875,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OSCAR DANIEL</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>BERMUDEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7863,14 +7895,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6611162254</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>MARIANO ESCOBEDO 1</t>
-        </is>
-      </c>
+          <t>6611357801</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7878,17 +7906,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>30-03-1985</t>
+          <t>11-05-2006</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>OSCARTB42@GMAIL.COM</t>
+          <t>BERMUDEZALFREDO486@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 06:13:03</t>
+          <t>16-02-2026 18:36:55</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7898,22 +7926,22 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 06:15:53</t>
+          <t>16-02-2026 18:38:24</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7921,21 +7949,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>16-02-2026 06:15:06</t>
-        </is>
-      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7943,19 +7963,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26090522377270001563</t>
+          <t>26090522405140001594</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7967,12 +7987,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343964</t>
+          <t>344823</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7982,17 +8002,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DULCE NAYELY</t>
+          <t>ROSA ELENA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8002,12 +8022,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6647907702</t>
+          <t>9515137595</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MAR DE ARAFURA 1881</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8017,52 +8037,52 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>04-09-1989</t>
+          <t>02-03-1998</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>SANHEZNAYELI@GMAIL.COM</t>
+          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 08:20:26</t>
+          <t>18-02-2026 14:26:16</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 08:26:12</t>
+          <t>18-02-2026 14:37:29</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>16-02-2026 08:25:33</t>
+          <t>18-02-2026 14:36:30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8082,22 +8102,832 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26090522380980001572</t>
+          <t>26090522462920001658</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>342555</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20372</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>JOSEFINA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GUDILLO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>WENCESLAO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6611143877</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>23-06-1960</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>10-02-2026 08:50:56</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>12-02-2026 08:45:46</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26090522289640001487</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>343039</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20856</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LETICIA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SALGADO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6862144489</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PUERTO NUEVO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>06-05-1979</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:24:54</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:31:31</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:29:22</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26090522268680001467</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Anton Omar Sanchez Ruiz</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>342837</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20654</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MARIA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZAMORA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6611954909</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TUXTLA GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>21-04-2000</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>MARIAZAMORA5432@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:27:31</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:33:59</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:33:24</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26090522247060001432</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>344063</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21880</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESAR </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ARANDA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6616165544</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>13-03-2007</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ACOSTAARANDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:14:13</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:15:43</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26090522388310001582</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>343924</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21741</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OSCAR DANIEL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6611162254</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MARIANO ESCOBEDO 1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>30-03-1985</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>OSCARTB42@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:13:03</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:15:53</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:15:06</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26090522377270001563</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Carlos Abraham Mijares Fernandez</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>343964</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21781</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DULCE NAYELY</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6647907702</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>MAR DE ARAFURA 1881</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>04-09-1989</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>SANHEZNAYELI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:20:26</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:26:12</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:25:33</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26090522380980001572</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>124299</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6611874122</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
+          <t>6193992701</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -628,60 +624,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02-06-1992</t>
+          <t>16-08-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ROSARITOVFBG@GMAIL.COM</t>
+          <t>NIMRADHNIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20-09-2022 08:58:25</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>02-08-2023 12:36:58</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-02-2026 09:13:36</t>
+          <t>23-02-2026 10:15:21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-02-2026 09:13:09</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26090522002470001083</t>
+          <t>26090522575760001775</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -713,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>333792</t>
+          <t>124299</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONARDO </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CASTELLON</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,10 +740,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6612356208</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6611874122</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -759,56 +755,60 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-03-2008</t>
+          <t>02-06-1992</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MAGOB0048@GMAIL.COM</t>
+          <t>ROSARITOVFBG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-01-2026 12:08:27</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>20-09-2022 08:58:25</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-02-2026 17:46:13</t>
+          <t>02-02-2026 09:13:36</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-02-2026 09:13:09</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,22 +816,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522083420001215</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>CARLOS ABRAHAM FERNANDEZ MASCULINO</t>
-        </is>
-      </c>
+          <t>26090522002470001083</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -848,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>159273</t>
+          <t>333792</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>56809</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALFONSO </t>
+          <t xml:space="preserve">LEONARDO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CASTELLON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PINEDA</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7351340175</t>
+          <t>6612356208</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -894,17 +886,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-09-1984</t>
+          <t>28-03-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P8INEDA@GMAIL.COM</t>
+          <t>MAGOB0048@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20-03-2023 11:49:41</t>
+          <t>12-01-2026 12:08:27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -919,28 +911,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>06-02-2026 14:13:33</t>
+          <t>04-02-2026 17:46:13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -951,14 +943,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26090522136900001292</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26090522083420001215</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>CARLOS ABRAHAM FERNANDEZ MASCULINO</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>293612</t>
+          <t>340226</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASHLEY SOPHIA</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>NUÑO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,10 +1010,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6642018969</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6612457962</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1021,17 +1025,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-12-2010</t>
+          <t>10-11-1988</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ANA.RODRIGUEZ300@GMAIL.COM</t>
+          <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19-05-2025 14:37:27</t>
+          <t>02-02-2026 15:45:17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1041,36 +1045,44 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 12:59:16</t>
+          <t>02-02-2026 15:51:10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:48:41</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1078,14 +1090,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090522038960001153</t>
+          <t>26090522015280001114</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1102,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>206537</t>
+          <t>340323</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DANIELA FERNANDA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBARRA </t>
+          <t xml:space="preserve"> CURIEL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,67 +1149,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6611029556</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6195181188</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C D LOS FISIOS</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13-11-2008</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IABARAHERMNANDEZ@GMIL.COM</t>
+          <t>LUIS.CURIEL4@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>14-11-2023 12:46:29</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:55:59</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>09-02-2026 07:12:53</t>
+          <t>02-02-2026 17:59:38</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:58:39</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1205,14 +1225,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522182800001336</t>
+          <t>26090522019700001121</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1229,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340226</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1244,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>DANIELA FERNANDA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t xml:space="preserve">IBARRA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NUÑO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1264,14 +1284,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6612457962</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AVENIDA LUCRECIA TORIS 6B COLONIA OBRERA</t>
-        </is>
-      </c>
+          <t>6611029556</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1279,17 +1295,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10-11-1988</t>
+          <t>13-11-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ALEJANDRACASTELLANOS6863@GMAIL.COM</t>
+          <t>IABARAHERMNANDEZ@GMIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:17</t>
+          <t>14-11-2023 12:46:29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1299,44 +1315,36 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:51:10</t>
+          <t>09-02-2026 07:12:53</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:48:41</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1344,14 +1352,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26090522015280001114</t>
+          <t>26090522182800001336</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1368,12 +1376,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340323</t>
+          <t>340218</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1383,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>LUIS JAVIER</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CURIEL</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6195181188</t>
+          <t>4463394887</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C D LOS FISIOS</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1418,17 +1426,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-04-1996</t>
+          <t>06-02-2009</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LUIS.CURIEL4@OUTLOOK.COM</t>
+          <t>LUISJAVIER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-02-2026 17:55:59</t>
+          <t>02-02-2026 15:31:29</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1449,7 +1457,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-02-2026 17:59:38</t>
+          <t>02-02-2026 15:33:41</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1459,7 +1467,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-02-2026 17:58:39</t>
+          <t>02-02-2026 15:32:47</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1479,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26090522019700001121</t>
+          <t>26090522014690001111</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1491,24 +1499,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340218</t>
+          <t>159273</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1518,17 +1526,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUIS JAVIER</t>
+          <t xml:space="preserve">ALFONSO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1538,14 +1546,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4463394887</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SAN FRANCISCO</t>
-        </is>
-      </c>
+          <t>7351340175</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1553,60 +1557,56 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>06-02-2009</t>
+          <t>21-09-1984</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LUISJAVIER@GMAIL.COM</t>
+          <t>P8INEDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:31:29</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>20-03-2023 11:49:41</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:33:41</t>
+          <t>06-02-2026 14:13:33</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:32:47</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1614,24 +1614,24 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26090522014690001111</t>
+          <t>26090522136900001292</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340078</t>
+          <t>341231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGAN VICTORIA </t>
+          <t>LILA ELENA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARNIDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6611255339</t>
+          <t>6641096895</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AGUSTIN DE ITUBIDE 418</t>
+          <t>LAZARO CARDENAS  8741</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1958,17 +1958,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18-08-1991</t>
+          <t>19-04-1980</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>VICTORIAVAL150891@GMAIL.COM</t>
+          <t>ELENA_BARAJAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 12:17:03</t>
+          <t>05-02-2026 08:07:14</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1989,17 +1989,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 12:23:43</t>
+          <t>12-02-2026 08:10:36</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-02-2026 12:20:17</t>
+          <t>12-02-2026 08:09:33</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2019,11 +2019,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522008660001094</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26090522288870001483</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>499</t>
@@ -2043,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340119</t>
+          <t>283070</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2058,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCA </t>
+          <t xml:space="preserve">ESTHELA ESMERALDA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALQUISIRA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTANA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2078,12 +2086,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6627448010</t>
+          <t>6643229624</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FRANCISCO BONILLA 14</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2093,20 +2101,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-10-1973</t>
+          <t>26-09-1993</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ALQUISIRASANTANA@GMAIL.COM</t>
+          <t>PROF.ESMERALDALOPEZ@GMIAL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 13:09:36</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>13-03-2025 16:34:09</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2124,17 +2136,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 13:12:52</t>
+          <t>20-02-2026 21:03:03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-02-2026 13:11:40</t>
+          <t>20-02-2026 21:02:28</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2144,7 +2156,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2154,7 +2166,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522010420001102</t>
+          <t>26130522537140003237</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2178,12 +2190,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340511</t>
+          <t>310494</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2193,17 +2205,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDGAR ALEJANDRO</t>
+          <t>ROMINA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2213,28 +2225,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6611146703</t>
+          <t>6241476864</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>06-01-2010</t>
+          <t>13-06-2008</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>HERRARAGONZEZ@GMAIL.COM</t>
+          <t>ROMINAMENDOZA771@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 10:48:54</t>
+          <t>20-08-2025 21:04:13</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2259,18 +2271,18 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 10:49:46</t>
+          <t>19-02-2026 09:19:08</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2281,11 +2293,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522036450001146</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26090522490090001681</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>399</t>
@@ -2305,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341231</t>
+          <t>340078</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LILA ELENA</t>
+          <t xml:space="preserve">MEGAN VICTORIA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GARNIDO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2340,12 +2360,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6641096895</t>
+          <t>6611255339</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LAZARO CARDENAS  8741</t>
+          <t>AGUSTIN DE ITUBIDE 418</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2355,17 +2375,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19-04-1980</t>
+          <t>18-08-1991</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ELENA_BARAJAS@HOTMAIL.COM</t>
+          <t>VICTORIAVAL150891@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>05-02-2026 08:07:14</t>
+          <t>02-02-2026 12:17:03</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2386,17 +2406,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12-02-2026 08:10:36</t>
+          <t>02-02-2026 12:23:43</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12-02-2026 08:09:33</t>
+          <t>02-02-2026 12:20:17</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2406,7 +2426,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2416,19 +2436,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522288870001483</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522008660001094</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2448,12 +2460,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>283070</t>
+          <t>340119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80571</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2463,17 +2475,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTHELA ESMERALDA </t>
+          <t xml:space="preserve">FRANCISCA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ALQUISIRA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SANTANA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2483,12 +2495,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643229624</t>
+          <t>6627448010</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>FRANCISCO BONILLA 14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2498,24 +2510,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-09-1993</t>
+          <t>10-10-1973</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PROF.ESMERALDALOPEZ@GMIAL.COM</t>
+          <t>ALQUISIRASANTANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>13-03-2025 16:34:09</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-02-2026 13:09:36</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2533,17 +2541,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>20-02-2026 21:03:03</t>
+          <t>02-02-2026 13:12:52</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>20-02-2026 21:02:28</t>
+          <t>02-02-2026 13:11:40</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2553,7 +2561,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2563,7 +2571,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26130522537140003237</t>
+          <t>26090522010420001102</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2587,12 +2595,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>310494</t>
+          <t>341246</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2602,17 +2610,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ROMINA</t>
+          <t xml:space="preserve">ATZIRY GABRIELA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2622,7 +2630,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6241476864</t>
+          <t>5545626086</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2633,17 +2641,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-06-2008</t>
+          <t>26-03-2006</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ROMINAMENDOZA771@GMAIL.COM</t>
+          <t>SANDOVALATZIRY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20-08-2025 21:04:13</t>
+          <t>05-02-2026 09:21:15</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2658,22 +2666,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>19-02-2026 09:19:08</t>
+          <t>06-02-2026 11:30:26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2690,7 +2698,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26090522490090001681</t>
+          <t>26090522134390001286</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2700,12 +2708,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2722,12 +2730,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340507</t>
+          <t>340511</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2737,17 +2745,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>EDGAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VEZDUZCO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2757,7 +2765,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6611108616</t>
+          <t>6611146703</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2768,17 +2776,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-03-2010</t>
+          <t>06-01-2010</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
+          <t>HERRARAGONZEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 10:45:27</t>
+          <t>03-02-2026 10:48:54</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2803,7 +2811,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 10:46:51</t>
+          <t>03-02-2026 10:49:46</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2825,7 +2833,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26090522036400001145</t>
+          <t>26090522036450001146</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2849,12 +2857,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340800</t>
+          <t>342032</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2864,17 +2872,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t xml:space="preserve">MAGDA LAURA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ANDONAEGUI</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2884,67 +2892,63 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6643700182</t>
+          <t>6611721658</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOMAS DE BELEN</t>
+          <t>LUIS CABRERA  20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>10-07-1996</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
+          <t>NAJERAVILLA3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-02-2026 19:02:55</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 07:22:55</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 19:06:01</t>
+          <t>09-02-2026 07:26:06</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:31</t>
+          <t>09-02-2026 07:25:07</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2954,7 +2958,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2964,14 +2968,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26090522055130001172</t>
+          <t>26090522183260001338</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2988,12 +2992,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340894</t>
+          <t>340507</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +3007,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA SILVIA </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>VEZDUZCO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,79 +3027,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6611169305</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>HACIENDA SAN FERNANDO</t>
-        </is>
-      </c>
+          <t>6611108616</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-10-1988</t>
+          <t>10-03-2010</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
+          <t>PELAYOVERDUZCODIEGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 08:33:41</t>
+          <t>03-02-2026 10:45:27</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:43</t>
+          <t>03-02-2026 10:46:51</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:37:45</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3103,22 +3095,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26090522381310001574</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522036400001145</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3135,12 +3119,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341246</t>
+          <t>334877</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3134,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATZIRY GABRIELA </t>
+          <t>KAROL IRENE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,10 +3154,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5545626086</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6644046543</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OAXACA  2053</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3181,17 +3169,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26-03-2006</t>
+          <t>21-09-1997</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SANDOVALATZIRY@GMAIL.COM</t>
+          <t>MUNOZHERNANDEZKAROL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-02-2026 09:21:15</t>
+          <t>15-01-2026 00:11:29</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3201,36 +3189,44 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>06-02-2026 11:30:26</t>
+          <t>19-02-2026 13:40:21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>19-02-2026 13:39:32</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3238,22 +3234,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26090522134390001286</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522494370001695</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3270,12 +3258,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>340800</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3285,17 +3273,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAROL IRENE</t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>ANDONAEGUI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3305,32 +3293,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6644046543</t>
+          <t>6643700182</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OAXACA  2053</t>
+          <t>LOMAS DE BELEN</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-09-1997</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MUNOZHERNANDEZKAROL@GMAIL.COM</t>
+          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15-01-2026 00:11:29</t>
+          <t>03-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3345,27 +3333,27 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>19-02-2026 13:40:21</t>
+          <t>03-02-2026 19:06:01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19-02-2026 13:39:32</t>
+          <t>03-02-2026 19:05:31</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3385,14 +3373,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26090522494370001695</t>
+          <t>26090522055130001172</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3409,12 +3397,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>341476</t>
+          <t>340894</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3424,17 +3412,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTOHONY </t>
+          <t xml:space="preserve">ANA SILVIA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3444,67 +3432,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6611726857</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6611169305</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN FERNANDO</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>06-06-2009</t>
+          <t>21-10-1988</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
+          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>06-02-2026 06:06:25</t>
+          <t>04-02-2026 08:33:41</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>06-02-2026 06:07:12</t>
+          <t>16-02-2026 08:38:43</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:37:45</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3512,14 +3512,22 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26090522129910001272</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26090522381310001574</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3536,12 +3544,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341574</t>
+          <t>342083</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3551,17 +3559,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>ALAN YOSUEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t>ARREDONDO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OLIVAREZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3571,10 +3579,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7291799451</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6645807893</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CARRETERA LIBRE ENCENADA</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3582,56 +3594,60 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07-06-1991</t>
+          <t>03-09-1993</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>OLIVAREZVALDES354@GMAIL.COM</t>
+          <t>YOSUELMORENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>06-02-2026 14:15:10</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 09:56:51</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-02-2026 14:17:32</t>
+          <t>09-02-2026 09:59:58</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>09-02-2026 09:59:31</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3639,14 +3655,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26090522136960001293</t>
+          <t>26090522187170001346</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3663,12 +3679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>340995</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3678,17 +3694,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LESLIE ANGELICA</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AVALOS</t>
+          <t xml:space="preserve">CABELLO </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3698,32 +3714,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6612393040</t>
+          <t>6616162514</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BUENA VISTA</t>
+          <t>EL NOGAL 7207</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11-03-2003</t>
+          <t>07-02-1966</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ANGIELESLIE@GMAIL.COM</t>
+          <t>MCELEEZ5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 14:06:05</t>
+          <t>04-02-2026 13:46:53</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3744,7 +3760,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 14:10:01</t>
+          <t>04-02-2026 13:50:36</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3754,7 +3770,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>04-02-2026 14:09:27</t>
+          <t>04-02-2026 13:49:21</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3764,7 +3780,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3774,7 +3790,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26090522075300001207</t>
+          <t>26090522075050001206</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3786,24 +3802,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340995</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3813,17 +3829,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t xml:space="preserve">ANTOHONY </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABELLO </t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3833,14 +3849,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6616162514</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>EL NOGAL 7207</t>
-        </is>
-      </c>
+          <t>6611726857</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3848,60 +3860,56 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07-02-1966</t>
+          <t>06-06-2009</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MCELEEZ5@GMAIL.COM</t>
+          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>04-02-2026 13:46:53</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>06-02-2026 06:06:25</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-02-2026 13:50:36</t>
+          <t>06-02-2026 06:07:12</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>04-02-2026 13:49:21</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3909,14 +3917,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26090522075050001206</t>
+          <t>26090522129910001272</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3933,12 +3941,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>341574</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,17 +3956,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGDA LAURA </t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>VALDES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>OLIVAREZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3968,75 +3976,67 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6611721658</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>LUIS CABRERA  20</t>
-        </is>
-      </c>
+          <t>7291799451</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>10-07-1996</t>
+          <t>07-06-1991</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>NAJERAVILLA3@GMAIL.COM</t>
+          <t>OLIVAREZVALDES354@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 07:22:55</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>06-02-2026 14:15:10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 07:26:06</t>
+          <t>06-02-2026 14:17:32</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>09-02-2026 07:25:07</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26090522183260001338</t>
+          <t>26090522136960001293</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4068,12 +4068,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341958</t>
+          <t>341004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4083,17 +4083,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDIDO </t>
+          <t>LESLIE ANGELICA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>AVALOS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4103,67 +4103,75 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7224496778</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6612393040</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BUENA VISTA</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>02-02-1983</t>
+          <t>11-03-2003</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
+          <t>ANGIELESLIE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>08-02-2026 14:21:04</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 14:06:05</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>08-02-2026 14:23:23</t>
+          <t>04-02-2026 14:10:01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>04-02-2026 14:09:27</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4171,36 +4179,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26090522172990001325</t>
+          <t>26090522075300001207</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342022</t>
+          <t>293612</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>91110</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,17 +4218,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN URIEL </t>
+          <t>ASHLEY SOPHIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4230,28 +4238,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6611116361</t>
+          <t>6642018969</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12-01-2008</t>
+          <t>13-12-2010</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>URIELCORTEZ1212@GMAIL.COM</t>
+          <t>ANA.RODRIGUEZ300@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 07:08:58</t>
+          <t>19-05-2025 14:37:27</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4276,18 +4284,18 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:14</t>
+          <t>03-02-2026 12:59:16</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -4298,7 +4306,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26090522182720001335</t>
+          <t>26090522038960001153</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4322,12 +4330,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342083</t>
+          <t>341958</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4337,17 +4345,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ALAN YOSUEL</t>
+          <t xml:space="preserve">CANDIDO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ARREDONDO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4357,14 +4365,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6645807893</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>CARRETERA LIBRE ENCENADA</t>
-        </is>
-      </c>
+          <t>7224496778</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4372,60 +4376,56 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03-09-1993</t>
+          <t>02-02-1983</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>YOSUELMORENO@GMAIL.COM</t>
+          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 09:56:51</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>08-02-2026 14:21:04</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 09:59:58</t>
+          <t>08-02-2026 14:23:23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>09-02-2026 09:59:31</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4433,14 +4433,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26090522187170001346</t>
+          <t>26090522172990001325</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4457,12 +4457,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342121</t>
+          <t>342022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOMAS </t>
+          <t xml:space="preserve">CRISTIAN URIEL </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OLARTE</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6613322085</t>
+          <t>6611116361</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4503,17 +4503,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-02-2009</t>
+          <t>12-01-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LARTESLAZAE@GMAIL.COM</t>
+          <t>URIELCORTEZ1212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 11:46:22</t>
+          <t>09-02-2026 07:08:58</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 11:48:02</t>
+          <t>09-02-2026 07:10:14</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26090522189440001352</t>
+          <t>26090522182720001335</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4584,12 +4584,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342571</t>
+          <t>342553</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4599,17 +4599,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EDNA YADIRA</t>
+          <t xml:space="preserve">MARIA CRISTINA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELA CRUZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>DELOERA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4619,14 +4619,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3251050507</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>PABLO BONILLA 22</t>
-        </is>
-      </c>
+          <t>6611192305</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4634,38 +4630,42 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10-05-1995</t>
+          <t>26-02-1961</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>EDNADELACRUZ64@GMAIL.COM</t>
+          <t>DELOERAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 09:38:32</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>10-02-2026 08:47:39</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 09:19:27</t>
+          <t>12-02-2026 08:44:08</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4673,21 +4673,13 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:18:59</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4695,7 +4687,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26090522290010001489</t>
+          <t>26090522289600001486</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4710,7 +4702,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4727,12 +4719,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342563</t>
+          <t>342121</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4742,17 +4734,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ALEXIS SEBASTIAN</t>
+          <t xml:space="preserve">TOMAS </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACENCIO </t>
+          <t>OLARTE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4762,28 +4754,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6611400473</t>
+          <t>6613322085</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>07-05-2006</t>
+          <t>15-02-2009</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ACENCALEXIS@GMAIL.COM</t>
+          <t>LARTESLAZAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 09:22:29</t>
+          <t>09-02-2026 11:46:22</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4798,28 +4790,28 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 09:23:44</t>
+          <t>09-02-2026 11:48:02</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4830,14 +4822,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26090522226960001399</t>
+          <t>26090522189440001352</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4854,12 +4846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342570</t>
+          <t>342771</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4869,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARTHA ISABEL</t>
+          <t>LUZ VALERIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ARAMBULA</t>
+          <t>GERONIMO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4889,14 +4881,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6611362361</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>CUMBRES SAJAMA</t>
-        </is>
-      </c>
+          <t>6615273140</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4904,60 +4892,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>09-02-1988</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
+          <t>LUZVALERIAGARCIA01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 09:36:01</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>10-02-2026 17:54:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12-02-2026 09:25:39</t>
+          <t>10-02-2026 17:54:42</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:24:12</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4965,18 +4949,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26090522290130001490</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522241780001425</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4993,12 +4973,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342575</t>
+          <t>342571</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5008,17 +4988,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DEL ROSARIO </t>
+          <t>EDNA YADIRA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUEZ </t>
+          <t xml:space="preserve">DELA CRUZ </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5028,12 +5008,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6648438264</t>
+          <t>3251050507</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CALLE LAGUNA 2043</t>
+          <t>PABLO BONILLA 22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5043,17 +5023,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23-03-1981</t>
+          <t>10-05-1995</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
+          <t>EDNADELACRUZ64@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 10:09:05</t>
+          <t>10-02-2026 09:38:32</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5074,17 +5054,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 10:13:10</t>
+          <t>12-02-2026 09:19:27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>10-02-2026 10:12:39</t>
+          <t>12-02-2026 09:18:59</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5094,7 +5074,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5104,11 +5084,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26090522227950001405</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26090522290010001489</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>499</t>
@@ -5116,24 +5104,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342458</t>
+          <t>342563</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5143,17 +5131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA CAROLINA </t>
+          <t>ALEXIS SEBASTIAN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA </t>
+          <t xml:space="preserve">ACENCIO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSORIO </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5163,32 +5151,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6631533043</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>CUENCA DIAZ</t>
-        </is>
-      </c>
+          <t>6611400473</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>07-05-2006</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SAGAOS0910@GMAIL.COM</t>
+          <t>ACENCALEXIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:38</t>
+          <t>10-02-2026 09:22:29</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5198,44 +5182,36 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 19:56:45</t>
+          <t>10-02-2026 09:23:44</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:56:10</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5243,14 +5219,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26090522212640001380</t>
+          <t>26090522226960001399</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5267,12 +5243,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342553</t>
+          <t>342570</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5282,17 +5258,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA CRISTINA </t>
+          <t>MARTHA ISABEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DELOERA</t>
+          <t>ARAMBULA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5302,10 +5278,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6611192305</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6611362361</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CUMBRES SAJAMA</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5313,42 +5293,38 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>26-02-1961</t>
+          <t>09-02-1988</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>DELOERAMARTINEZ@GMAIL.COM</t>
+          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-02-2026 08:47:39</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 09:36:01</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 08:44:08</t>
+          <t>12-02-2026 09:25:39</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5356,13 +5332,21 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>12-02-2026 09:24:12</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5370,7 +5354,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26090522289600001486</t>
+          <t>26090522290130001490</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5378,14 +5362,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5402,12 +5382,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342772</t>
+          <t>342575</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5417,17 +5397,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FATIMA GUADALUPE</t>
+          <t xml:space="preserve">MARIA DEL ROSARIO </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">MARQUEZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GERONIMO</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5437,10 +5417,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6611162957</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6648438264</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CALLE LAGUNA 2043</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5448,42 +5432,38 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>03-10-2008</t>
+          <t>23-03-1981</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FATIMAGUADALUPEG76@GMAIL.COM</t>
+          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 17:56:14</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 10:09:05</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 17:57:08</t>
+          <t>10-02-2026 10:13:10</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5491,13 +5471,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>10-02-2026 10:12:39</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5505,36 +5493,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26090522241950001426</t>
+          <t>26090522227950001405</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340206</t>
+          <t>342458</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5544,17 +5532,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LIZETH GUADALUPE</t>
+          <t xml:space="preserve">GABRIELA CAROLINA </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">GAONA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t xml:space="preserve">OSORIO </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5564,63 +5552,67 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6648559380</t>
+          <t>6631533043</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>CUENCA DIAZ</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>20-12-1993</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>SOLANOLISETH93@GMAIL.COM</t>
+          <t>SAGAOS0910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-02-2026 15:21:09</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>09-02-2026 19:49:38</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-02-2026 15:25:17</t>
+          <t>09-02-2026 19:56:45</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-02-2026 15:24:50</t>
+          <t>09-02-2026 19:56:10</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5640,36 +5632,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26090522014340001109</t>
+          <t>26090522212640001380</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342771</t>
+          <t>342772</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5679,7 +5671,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LUZ VALERIA</t>
+          <t>FATIMA GUADALUPE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5699,7 +5691,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6615273140</t>
+          <t>6611162957</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5710,17 +5702,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>03-10-2008</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LUZVALERIAGARCIA01@GMAIL.COM</t>
+          <t>FATIMAGUADALUPEG76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-02-2026 17:54:00</t>
+          <t>10-02-2026 17:56:14</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5745,7 +5737,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 17:54:42</t>
+          <t>10-02-2026 17:57:08</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5767,7 +5759,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26090522241780001425</t>
+          <t>26090522241950001426</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5791,12 +5783,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343260</t>
+          <t>340206</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5806,17 +5798,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ALFONSO </t>
+          <t>LIZETH GUADALUPE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5826,32 +5818,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6611160032</t>
+          <t>6648559380</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PACIFICO 2651</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19-10-1970</t>
+          <t>20-12-1993</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
+          <t>SOLANOLISETH93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>12-02-2026 14:13:40</t>
+          <t>02-02-2026 15:21:09</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5872,17 +5864,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>12-02-2026 14:15:35</t>
+          <t>02-02-2026 15:25:17</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12-02-2026 14:14:58</t>
+          <t>02-02-2026 15:24:50</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5902,7 +5894,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26090522294330001500</t>
+          <t>26090522014340001109</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5914,12 +5906,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6045,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342629</t>
+          <t>343260</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6068,17 +6060,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JORGE ENRIQUE</t>
+          <t xml:space="preserve">LUIS ALFONSO </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6088,32 +6080,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6644644841</t>
+          <t>6611160032</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ROSA MAR</t>
+          <t>PACIFICO 2651</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28-10-1993</t>
+          <t>19-10-1970</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MELISAMARLUM1@GMAIL.COM</t>
+          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 14:18:11</t>
+          <t>12-02-2026 14:13:40</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6134,17 +6126,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 14:24:03</t>
+          <t>12-02-2026 14:15:35</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>10-02-2026 14:22:52</t>
+          <t>12-02-2026 14:14:58</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6164,7 +6156,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26090522232400001415</t>
+          <t>26090522294330001500</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6188,12 +6180,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>341089</t>
+          <t>342629</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6203,17 +6195,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GRISELDA</t>
+          <t>JORGE ENRIQUE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6223,12 +6215,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6612393915</t>
+          <t>6644644841</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COLONIA MORELOS</t>
+          <t>ROSA MAR</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6238,52 +6230,48 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17-01-1986</t>
+          <t>28-10-1993</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>MARIOORIVERAAV77@GMAIL.COM</t>
+          <t>MELISAMARLUM1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-02-2026 16:50:13</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:18:11</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:59</t>
+          <t>10-02-2026 14:24:03</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:19</t>
+          <t>10-02-2026 14:22:52</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6293,7 +6281,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6303,14 +6291,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26090522080820001212</t>
+          <t>26090522232400001415</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6327,12 +6315,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>340796</t>
+          <t>344421</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6342,32 +6330,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARILU </t>
+          <t xml:space="preserve">CASANDRA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>MELEMDREZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6645991198</t>
+          <t>6319726958</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JOSE MARIA IGLESIAS 20</t>
+          <t>ROSARITO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6377,17 +6365,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>06-04-1994</t>
+          <t>16-10-1993</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>LICORTRUIZ@GMAIL.COM</t>
+          <t>MELEMDREZFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>03-02-2026 18:55:15</t>
+          <t>17-02-2026 09:20:40</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6412,17 +6400,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:59</t>
+          <t>20-02-2026 09:43:23</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:08</t>
+          <t>20-02-2026 09:41:31</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6432,7 +6420,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6442,11 +6430,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26090522054800001170</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26090522522690001726</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>649</t>
@@ -6466,12 +6462,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343556</t>
+          <t>340796</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6481,17 +6477,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LAURA YAZMIN</t>
+          <t xml:space="preserve">MARILU </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CAPIZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6501,12 +6497,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6611352488</t>
+          <t>6645991198</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GALATEA MZA</t>
+          <t>JOSE MARIA IGLESIAS 20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6516,48 +6512,52 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>08-02-2003</t>
+          <t>06-04-1994</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>LAURACAPIZ5@GMAIL.COM</t>
+          <t>LICORTRUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:14</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>03-02-2026 18:55:15</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:22:43</t>
+          <t>03-02-2026 19:00:59</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:21:47</t>
+          <t>03-02-2026 19:00:08</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6577,36 +6577,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26090522326300001537</t>
+          <t>26090522054800001170</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Anton Omar Sanchez Ruiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343524</t>
+          <t>344826</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CLAUDIA ADRIANA</t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6636,35 +6636,39 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6611173965</t>
+          <t>9517836968</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LUCIO BLANCO</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13-04-1999</t>
+          <t>13-08-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
+          <t>BH462951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13-02-2026 16:01:41</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>18-02-2026 14:38:52</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6682,17 +6686,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>13-02-2026 16:08:34</t>
+          <t>18-02-2026 14:42:52</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13-02-2026 16:07:45</t>
+          <t>18-02-2026 14:42:22</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6712,7 +6716,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26090522323730001533</t>
+          <t>26090522463100001659</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6736,12 +6740,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344421</t>
+          <t>344920</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6751,99 +6755,87 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASANDRA </t>
+          <t xml:space="preserve">NAOMI NICOLE </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MELEMDREZ</t>
+          <t xml:space="preserve">AGUIRRE </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6611134520</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>18-03-2009</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CAMACHONAOIMI77@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:04:22</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:49:34</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>6319726958</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>16-10-1993</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>MELEMDREZFELIX@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>17-02-2026 09:20:40</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>20-02-2026 09:43:23</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>20-02-2026 09:41:31</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6851,7 +6843,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26090522522690001726</t>
+          <t>26090522530570001751</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6859,36 +6851,32 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343605</t>
+          <t>343556</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6898,99 +6886,95 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVAN </t>
+          <t>LAURA YAZMIN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>CAPIZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILEZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6611352488</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>GALATEA MZA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>08-02-2003</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LAURACAPIZ5@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:19:14</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:22:43</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:21:47</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>6195778145</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>LA BARCA</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>06-10-1971</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>CAGAOS0910@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>13-02-2026 19:48:54</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>13-02-2026 21:16:17</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>13-02-2026 21:15:42</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6998,40 +6982,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26090522331810001546</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522326300001537</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344826</t>
+          <t>341089</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7041,17 +7021,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t>GRISELDA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7061,67 +7041,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9517836968</t>
+          <t>6612393915</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
+          <t>COLONIA MORELOS</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>13-08-1999</t>
+          <t>17-01-1986</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BH462951@GMAIL.COM</t>
+          <t>MARIOORIVERAAV77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18-02-2026 14:38:52</t>
+          <t>04-02-2026 16:50:13</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-02-2026 14:42:52</t>
+          <t>04-02-2026 16:55:59</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18-02-2026 14:42:22</t>
+          <t>04-02-2026 16:55:19</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7131,7 +7111,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7141,14 +7121,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26090522463100001659</t>
+          <t>26090522080820001212</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7165,12 +7145,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344920</t>
+          <t>345346</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>87511</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7180,17 +7160,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAOMI NICOLE </t>
+          <t>ARNULFO MIGUEL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIRRE </t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7200,53 +7180,57 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6611134520</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>5634728993</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAN DE AYUTLA LOTE 12 </t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18-03-2009</t>
+          <t>23-05-1976</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CAMACHONAOIMI77@GMAIL.COM</t>
+          <t>MIGUEL.A.PEREZ0723@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-02-2026 18:04:22</t>
+          <t>20-02-2026 16:58:03</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:34</t>
+          <t>20-02-2026 17:03:21</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7254,13 +7238,21 @@
           <t>20-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>20-02-2026 17:02:35</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7268,18 +7260,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26090522530570001751</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522531130001753</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7435,12 +7423,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345346</t>
+          <t>343524</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7450,17 +7438,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ARNULFO MIGUEL</t>
+          <t>CLAUDIA ADRIANA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7470,39 +7458,35 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5634728993</t>
+          <t>6611173965</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAN DE AYUTLA LOTE 12 </t>
+          <t>LUCIO BLANCO</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23-05-1976</t>
+          <t>13-04-1999</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MIGUEL.A.PEREZ0723@GMAIL.COM</t>
+          <t>CLAUDIA.GOMEZ.99.SANTORS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>20-02-2026 16:58:03</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:01:41</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7520,17 +7504,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>20-02-2026 17:03:21</t>
+          <t>13-02-2026 16:08:34</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>20-02-2026 17:02:35</t>
+          <t>13-02-2026 16:07:45</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7550,7 +7534,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26090522531130001753</t>
+          <t>26090522323730001533</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7574,12 +7558,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>341943</t>
+          <t>343605</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7589,32 +7573,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAREL </t>
+          <t xml:space="preserve">IVAN </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">AVILEZ </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6611110729</t>
+          <t>6195778145</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ROSARITO</t>
+          <t>LA BARCA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7624,48 +7608,52 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>15-09-1998</t>
+          <t>06-10-1971</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>GONZALEZISRAEL98523@GMAIL.COM</t>
+          <t>CAGAOS0910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>08-02-2026 12:52:54</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>13-02-2026 19:48:54</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10-02-2026 13:26:35</t>
+          <t>13-02-2026 21:16:17</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>10-02-2026 13:25:41</t>
+          <t>13-02-2026 21:15:42</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7685,7 +7673,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26090522231320001412</t>
+          <t>26090522331810001546</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7693,14 +7681,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7987,12 +7971,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344823</t>
+          <t>342555</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8002,17 +7986,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROSA ELENA</t>
+          <t>JOSEFINA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>GUDILLO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>WENCESLAO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8022,14 +8006,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9515137595</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
-        </is>
-      </c>
+          <t>6611143877</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8037,64 +8017,56 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>02-03-1998</t>
+          <t>23-06-1960</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
+          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18-02-2026 14:26:16</t>
+          <t>10-02-2026 08:50:56</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>18-02-2026 14:37:29</t>
+          <t>12-02-2026 08:45:46</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>18-02-2026 14:36:30</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8102,14 +8074,22 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26090522462920001658</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+          <t>26090522289640001487</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8126,12 +8106,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342555</t>
+          <t>341943</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8141,17 +8121,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JOSEFINA</t>
+          <t xml:space="preserve">ISAREL </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GUDILLO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>WENCESLAO</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8161,67 +8141,75 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6611143877</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6611110729</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>23-06-1960</t>
+          <t>15-09-1998</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
+          <t>GONZALEZISRAEL98523@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10-02-2026 08:50:56</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 12:52:54</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:46</t>
+          <t>10-02-2026 13:26:35</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>10-02-2026 13:25:41</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8229,7 +8217,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26090522289640001487</t>
+          <t>26090522231320001412</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -8239,12 +8227,12 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8261,12 +8249,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343039</t>
+          <t>344823</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8276,17 +8264,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>ROSA ELENA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8296,35 +8284,39 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6862144489</t>
+          <t>9515137595</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PUERTO NUEVO</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-05-1979</t>
+          <t>02-03-1998</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:54</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>18-02-2026 14:26:16</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8342,17 +8334,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>11-02-2026 16:31:31</t>
+          <t>18-02-2026 14:37:29</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11-02-2026 16:29:22</t>
+          <t>18-02-2026 14:36:30</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8372,7 +8364,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26090522268680001467</t>
+          <t>26090522462920001658</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8384,24 +8376,24 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Anton Omar Sanchez Ruiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>343039</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8411,17 +8403,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MARIA CONCEPCION</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8431,32 +8423,32 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6611954909</t>
+          <t>6862144489</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TUXTLA GUTIERREZ</t>
+          <t>PUERTO NUEVO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>21-04-2000</t>
+          <t>06-05-1979</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>MARIAZAMORA5432@HOTMAIL.COM</t>
+          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:27:31</t>
+          <t>11-02-2026 16:24:54</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8477,17 +8469,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:59</t>
+          <t>11-02-2026 16:31:31</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:24</t>
+          <t>11-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8507,7 +8499,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26090522247060001432</t>
+          <t>26090522268680001467</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8519,24 +8511,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344063</t>
+          <t>345787</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>87952</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8546,17 +8538,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR </t>
+          <t>BRANDON ALEXANDER</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MENESSES</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8566,7 +8558,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6616165544</t>
+          <t>6611366844</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8577,22 +8569,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>30-04-2006</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ACOSTAARANDA@GMAIL.COM</t>
+          <t>MENESSEWSRAMIREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 13:14:13</t>
+          <t>23-02-2026 13:53:03</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8602,22 +8594,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>16-02-2026 13:15:43</t>
+          <t>23-02-2026 13:53:49</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -8634,14 +8626,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26090522388310001582</t>
+          <t>26090522581530001789</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8658,12 +8650,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343924</t>
+          <t>345795</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8673,17 +8665,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OSCAR DANIEL</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>MOURET</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8693,32 +8685,28 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6611162254</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>MARIANO ESCOBEDO 1</t>
-        </is>
-      </c>
+          <t>6611304257</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>30-03-1985</t>
+          <t>04-11-1999</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>OSCARTB42@GMAIL.COM</t>
+          <t>MOURET27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 06:13:03</t>
+          <t>23-02-2026 14:07:40</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8728,44 +8716,36 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 06:15:53</t>
+          <t>23-02-2026 14:09:50</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>16-02-2026 06:15:06</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8773,36 +8753,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26090522377270001563</t>
+          <t>26090522581870001790</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343964</t>
+          <t>344063</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8812,17 +8792,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DULCE NAYELY</t>
+          <t xml:space="preserve">CESAR </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8832,32 +8812,28 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6647907702</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>MAR DE ARAFURA 1881</t>
-        </is>
-      </c>
+          <t>6616165544</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>04-09-1989</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>SANHEZNAYELI@GMAIL.COM</t>
+          <t>ACOSTAARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 08:20:26</t>
+          <t>16-02-2026 13:14:13</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8867,22 +8843,22 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>16-02-2026 08:26:12</t>
+          <t>16-02-2026 13:15:43</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8890,21 +8866,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:25:33</t>
-        </is>
-      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8912,22 +8880,562 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26090522380980001572</t>
+          <t>26090522388310001582</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>342837</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20654</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MARIA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZAMORA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6611954909</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TUXTLA GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>21-04-2000</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>MARIAZAMORA5432@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:27:31</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:33:59</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:33:24</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26090522247060001432</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>343924</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21741</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OSCAR DANIEL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6611162254</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>MARIANO ESCOBEDO 1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>30-03-1985</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>OSCARTB42@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:13:03</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:15:53</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>16-02-2026 06:15:06</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26090522377270001563</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Carlos Abraham Mijares Fernandez</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>343964</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21781</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DULCE NAYELY</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6647907702</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>MAR DE ARAFURA 1881</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>04-09-1989</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>SANHEZNAYELI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:20:26</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:26:12</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:25:33</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26090522380980001572</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>345707</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>87872</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIAN </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CASTAÑEDA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6611304733</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>23-06-2000</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>CASTAÑEDAADRIANSANCHEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>23-02-2026 11:06:28</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>23-02-2026 11:07:27</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26090522576680001779</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -3123,12 +3123,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340774</t>
+          <t>334877</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AARON DE JESUS</t>
+          <t>KAROL IRENE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MUÑIZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3158,63 +3158,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6611193456</t>
+          <t>6644046543</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t>OAXACA  2053</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11-07-2000</t>
+          <t>21-09-1997</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>AARONRAMIREZ12323@GMAIL.COM</t>
+          <t>MUNOZHERNANDEZKAROL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-02-2026 18:09:17</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>15-01-2026 00:11:29</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-02-2026 18:14:38</t>
+          <t>19-02-2026 13:40:21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-02-2026 18:14:07</t>
+          <t>19-02-2026 13:39:32</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3234,14 +3238,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26090522052370001168</t>
+          <t>26090522494370001695</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3258,12 +3262,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>340774</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3273,17 +3277,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAROL IRENE</t>
+          <t>AARON DE JESUS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MUÑIZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3293,67 +3297,63 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6644046543</t>
+          <t>6611193456</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OAXACA  2053</t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-09-1997</t>
+          <t>11-07-2000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MUNOZHERNANDEZKAROL@GMAIL.COM</t>
+          <t>AARONRAMIREZ12323@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15-01-2026 00:11:29</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:09:17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>19-02-2026 13:40:21</t>
+          <t>03-02-2026 18:14:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19-02-2026 13:39:32</t>
+          <t>03-02-2026 18:14:07</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3373,14 +3373,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26090522494370001695</t>
+          <t>26090522052370001168</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -4199,12 +4199,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341476</t>
+          <t>343260</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTOHONY </t>
+          <t xml:space="preserve">LUIS ALFONSO </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4234,10 +4234,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6611726857</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6611160032</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PACIFICO 2651</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4245,56 +4249,60 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-06-2009</t>
+          <t>19-10-1970</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
+          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>06-02-2026 06:06:25</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 14:13:40</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>06-02-2026 06:07:12</t>
+          <t>12-02-2026 14:15:35</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>12-02-2026 14:14:58</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4302,14 +4310,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26090522129910001272</t>
+          <t>26090522294330001500</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4326,12 +4334,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343260</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4341,17 +4349,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ALFONSO </t>
+          <t xml:space="preserve">ANTOHONY </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4361,14 +4369,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6611160032</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>PACIFICO 2651</t>
-        </is>
-      </c>
+          <t>6611726857</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4376,60 +4380,56 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-10-1970</t>
+          <t>06-06-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ALFONSOSERRANO41@HOTMAIL.COM</t>
+          <t>ESCOBARPEREZANTON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12-02-2026 14:13:40</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>06-02-2026 06:06:25</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>12-02-2026 14:15:35</t>
+          <t>06-02-2026 06:07:12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>12-02-2026 14:14:58</t>
-        </is>
-      </c>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4437,14 +4437,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26090522294330001500</t>
+          <t>26090522129910001272</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4461,12 +4461,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340800</t>
+          <t>340206</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>LIZETH GUADALUPE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ANDONAEGUI</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4496,67 +4496,63 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6643700182</t>
+          <t>6648559380</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LOMAS DE BELEN</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>20-12-1993</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
+          <t>SOLANOLISETH93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:02:55</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 15:21:09</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:06:01</t>
+          <t>02-02-2026 15:25:17</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:31</t>
+          <t>02-02-2026 15:24:50</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4566,7 +4562,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4576,36 +4572,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26090522055130001172</t>
+          <t>26090522014340001109</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340894</t>
+          <t>340800</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,17 +4611,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA SILVIA </t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>ANDONAEGUI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4635,67 +4631,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6611169305</t>
+          <t>6643700182</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>HACIENDA SAN FERNANDO</t>
+          <t>LOMAS DE BELEN</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-10-1988</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
+          <t>MAURICIO.ANDONAEGUI.G@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>04-02-2026 08:33:41</t>
+          <t>03-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:43</t>
+          <t>03-02-2026 19:06:01</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>16-02-2026 08:37:45</t>
+          <t>03-02-2026 19:05:31</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4705,7 +4701,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4715,22 +4711,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26090522381310001574</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522055130001172</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4747,12 +4735,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>340894</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4762,17 +4750,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LESLIE ANGELICA</t>
+          <t xml:space="preserve">ANA SILVIA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AVALOS</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4782,12 +4770,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6612393040</t>
+          <t>6611169305</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BUENA VISTA</t>
+          <t>HACIENDA SAN FERNANDO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4797,20 +4785,24 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11-03-2003</t>
+          <t>21-10-1988</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ANGIELESLIE@GMAIL.COM</t>
+          <t>FIGUEROAANARAMIREZ@DGMAIL.OCOM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>04-02-2026 14:06:05</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>04-02-2026 08:33:41</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4828,17 +4820,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>04-02-2026 14:10:01</t>
+          <t>16-02-2026 08:38:43</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>04-02-2026 14:09:27</t>
+          <t>16-02-2026 08:37:45</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4858,11 +4850,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26090522075300001207</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26090522381310001574</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4870,24 +4870,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341958</t>
+          <t>341004</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4897,17 +4897,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDIDO </t>
+          <t>LESLIE ANGELICA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>AVALOS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4917,67 +4917,75 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7224496778</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6612393040</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BUENA VISTA</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>02-02-1983</t>
+          <t>11-03-2003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
+          <t>ANGIELESLIE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>08-02-2026 14:21:04</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 14:06:05</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>08-02-2026 14:23:23</t>
+          <t>04-02-2026 14:10:01</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>04-02-2026 14:09:27</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,36 +4993,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26090522172990001325</t>
+          <t>26090522075300001207</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342022</t>
+          <t>341958</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5032,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN URIEL </t>
+          <t xml:space="preserve">CANDIDO </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,7 +5052,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6611116361</t>
+          <t>7224496778</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5055,17 +5063,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12-01-2008</t>
+          <t>02-02-1983</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>URIELCORTEZ1212@GMAIL.COM</t>
+          <t>SANCHEZCANDIDO586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 07:08:58</t>
+          <t>08-02-2026 14:21:04</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5080,28 +5088,28 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:14</t>
+          <t>08-02-2026 14:23:23</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5112,14 +5120,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26090522182720001335</t>
+          <t>26090522172990001325</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5136,12 +5144,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340206</t>
+          <t>342022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5159,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LIZETH GUADALUPE</t>
+          <t xml:space="preserve">CRISTIAN URIEL </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,75 +5179,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6648559380</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>SAN FRANCISCO</t>
-        </is>
-      </c>
+          <t>6611116361</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>20-12-1993</t>
+          <t>12-01-2008</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SOLANOLISETH93@GMAIL.COM</t>
+          <t>URIELCORTEZ1212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 15:21:09</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>09-02-2026 07:08:58</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-02-2026 15:25:17</t>
+          <t>09-02-2026 07:10:14</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:24:50</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5247,24 +5247,24 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26090522014340001109</t>
+          <t>26090522182720001335</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>341089</t>
+          <t>344421</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GRISELDA</t>
+          <t xml:space="preserve">CASANDRA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MELEMDREZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6612393915</t>
+          <t>6319726958</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COLONIA MORELOS</t>
+          <t>ROSARITO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>17-01-1986</t>
+          <t>16-10-1993</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MARIOORIVERAAV77@GMAIL.COM</t>
+          <t>MELEMDREZFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>04-02-2026 16:50:13</t>
+          <t>17-02-2026 09:20:40</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:59</t>
+          <t>20-02-2026 09:43:23</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>04-02-2026 16:55:19</t>
+          <t>20-02-2026 09:41:31</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5513,11 +5513,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26090522080820001212</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26090522522690001726</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>649</t>
@@ -5537,12 +5545,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344421</t>
+          <t>341089</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5552,32 +5560,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASANDRA </t>
+          <t>GRISELDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MELEMDREZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6319726958</t>
+          <t>6612393915</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ROSARITO</t>
+          <t>COLONIA MORELOS</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5587,17 +5595,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>16-10-1993</t>
+          <t>17-01-1986</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MELEMDREZFELIX@GMAIL.COM</t>
+          <t>MARIOORIVERAAV77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-02-2026 09:20:40</t>
+          <t>04-02-2026 16:50:13</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5622,17 +5630,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>20-02-2026 09:43:23</t>
+          <t>04-02-2026 16:55:59</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20-02-2026 09:41:31</t>
+          <t>04-02-2026 16:55:19</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5642,7 +5650,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5652,19 +5660,11 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26090522522690001726</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522080820001212</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>649</t>
@@ -5684,12 +5684,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340796</t>
+          <t>344826</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARILU </t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5719,67 +5719,67 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6645991198</t>
+          <t>9517836968</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JOSE MARIA IGLESIAS 20</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06-04-1994</t>
+          <t>13-08-1999</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LICORTRUIZ@GMAIL.COM</t>
+          <t>BH462951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 18:55:15</t>
+          <t>18-02-2026 14:38:52</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:59</t>
+          <t>18-02-2026 14:42:52</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-02-2026 19:00:08</t>
+          <t>18-02-2026 14:42:22</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5799,36 +5799,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26090522054800001170</t>
+          <t>26090522463100001659</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344826</t>
+          <t>344920</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t xml:space="preserve">NAOMI NICOLE </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t xml:space="preserve">AGUIRRE </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5858,79 +5858,67 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9517836968</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
-        </is>
-      </c>
+          <t>6611134520</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>13-08-1999</t>
+          <t>18-03-2009</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BH462951@GMAIL.COM</t>
+          <t>CAMACHONAOIMI77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18-02-2026 14:38:52</t>
+          <t>18-02-2026 18:04:22</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-02-2026 14:42:52</t>
+          <t>20-02-2026 16:49:34</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>18-02-2026 14:42:22</t>
-        </is>
-      </c>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5938,19 +5926,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26090522463100001659</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26090522530570001751</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5962,12 +5954,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344920</t>
+          <t>340796</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5977,17 +5969,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAOMI NICOLE </t>
+          <t xml:space="preserve">MARILU </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIRRE </t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5997,10 +5989,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6611134520</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6645991198</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JOSE MARIA IGLESIAS 20</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6008,17 +6004,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18-03-2009</t>
+          <t>06-04-1994</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CAMACHONAOIMI77@GMAIL.COM</t>
+          <t>LICORTRUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-02-2026 18:04:22</t>
+          <t>03-02-2026 18:55:15</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6028,36 +6024,44 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:34</t>
+          <t>03-02-2026 19:00:59</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:00:08</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6065,28 +6069,24 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26090522530570001751</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522054800001170</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342563</t>
+          <t>345346</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>87511</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ALEXIS SEBASTIAN</t>
+          <t>ARNULFO MIGUEL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACENCIO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6263,67 +6263,79 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6611400473</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>5634728993</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAN DE AYUTLA LOTE 12 </t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>07-05-2006</t>
+          <t>23-05-1976</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ACENCALEXIS@GMAIL.COM</t>
+          <t>MIGUEL.A.PEREZ0723@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10-02-2026 09:22:29</t>
+          <t>20-02-2026 16:58:03</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10-02-2026 09:23:44</t>
+          <t>20-02-2026 17:03:21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>20-02-2026 17:02:35</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6331,14 +6343,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26090522226960001399</t>
+          <t>26090522531130001753</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6355,12 +6367,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342570</t>
+          <t>342563</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6370,17 +6382,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MARTHA ISABEL</t>
+          <t>ALEXIS SEBASTIAN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t xml:space="preserve">ACENCIO </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ARAMBULA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6390,14 +6402,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6611362361</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>CUMBRES SAJAMA</t>
-        </is>
-      </c>
+          <t>6611400473</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6405,60 +6413,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>09-02-1988</t>
+          <t>07-05-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
+          <t>ACENCALEXIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10-02-2026 09:36:01</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>10-02-2026 09:22:29</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 09:25:39</t>
+          <t>10-02-2026 09:23:44</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:24:12</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6466,18 +6470,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26090522290130001490</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522226960001399</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6494,12 +6494,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342575</t>
+          <t>342570</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6509,17 +6509,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DEL ROSARIO </t>
+          <t>MARTHA ISABEL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUEZ </t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>ARAMBULA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6648438264</t>
+          <t>6611362361</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CALLE LAGUNA 2043</t>
+          <t>CUMBRES SAJAMA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6544,17 +6544,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23-03-1981</t>
+          <t>09-02-1988</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
+          <t>SOISNEROSAARAMABULA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 10:09:05</t>
+          <t>10-02-2026 09:36:01</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 10:13:10</t>
+          <t>12-02-2026 09:25:39</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10-02-2026 10:12:39</t>
+          <t>12-02-2026 09:24:12</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6605,10 +6605,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26090522227950001405</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
+          <t>26090522290130001490</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6617,24 +6621,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345346</t>
+          <t>342575</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6644,17 +6648,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARNULFO MIGUEL</t>
+          <t xml:space="preserve">MARIA DEL ROSARIO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">MARQUEZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6664,39 +6668,35 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5634728993</t>
+          <t>6648438264</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAN DE AYUTLA LOTE 12 </t>
+          <t>CALLE LAGUNA 2043</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>23-05-1976</t>
+          <t>23-03-1981</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MIGUEL.A.PEREZ0723@GMAIL.COM</t>
+          <t>MARQUEZ.ROSARIO23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>20-02-2026 16:58:03</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 10:09:05</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6714,17 +6714,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>20-02-2026 17:03:21</t>
+          <t>10-02-2026 10:13:10</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>20-02-2026 17:02:35</t>
+          <t>10-02-2026 10:12:39</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26090522531130001753</t>
+          <t>26090522227950001405</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342629</t>
+          <t>342121</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6910,17 +6910,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JORGE ENRIQUE</t>
+          <t xml:space="preserve">TOMAS </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OLARTE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6930,75 +6930,67 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6644644841</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>ROSA MAR</t>
-        </is>
-      </c>
+          <t>6613322085</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>28-10-1993</t>
+          <t>15-02-2009</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MELISAMARLUM1@GMAIL.COM</t>
+          <t>LARTESLAZAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>10-02-2026 14:18:11</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>09-02-2026 11:46:22</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10-02-2026 14:24:03</t>
+          <t>09-02-2026 11:48:02</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>10-02-2026 14:22:52</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7006,14 +6998,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26090522232400001415</t>
+          <t>26090522189440001352</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7030,12 +7022,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342121</t>
+          <t>342629</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7045,17 +7037,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOMAS </t>
+          <t>JORGE ENRIQUE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OLARTE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7065,67 +7057,75 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6613322085</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6644644841</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ROSA MAR</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>15-02-2009</t>
+          <t>28-10-1993</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>LARTESLAZAE@GMAIL.COM</t>
+          <t>MELISAMARLUM1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>09-02-2026 11:46:22</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:18:11</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>09-02-2026 11:48:02</t>
+          <t>10-02-2026 14:24:03</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>10-02-2026 14:22:52</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26090522189440001352</t>
+          <t>26090522232400001415</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7157,12 +7157,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>341943</t>
+          <t>342352</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAREL </t>
+          <t>ALEXA CAMILA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>ZATARAIN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7192,32 +7192,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6611110729</t>
+          <t>6673421986</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ROSARITO</t>
+          <t>AMPLIACION REFORMA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15-09-1998</t>
+          <t>02-01-2006</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>GONZALEZISRAEL98523@GMAIL.COM</t>
+          <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>08-02-2026 12:52:54</t>
+          <t>09-02-2026 17:48:28</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7238,17 +7238,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10-02-2026 13:26:35</t>
+          <t>11-02-2026 17:26:32</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>10-02-2026 13:25:41</t>
+          <t>11-02-2026 17:25:59</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26090522231320001412</t>
+          <t>26090522271360001469</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -7288,24 +7288,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342458</t>
+          <t>341943</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7315,17 +7315,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA CAROLINA </t>
+          <t xml:space="preserve">ISAREL </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSORIO </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6631533043</t>
+          <t>6611110729</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CUENCA DIAZ</t>
+          <t>ROSARITO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7350,52 +7350,48 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>15-09-1998</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>SAGAOS0910@GMAIL.COM</t>
+          <t>GONZALEZISRAEL98523@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:38</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 12:52:54</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>09-02-2026 19:56:45</t>
+          <t>10-02-2026 13:26:35</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>09-02-2026 19:56:10</t>
+          <t>10-02-2026 13:25:41</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7415,14 +7411,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26090522212640001380</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
+          <t>26090522231320001412</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7439,12 +7443,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343556</t>
+          <t>342458</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7454,17 +7458,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LAURA YAZMIN</t>
+          <t xml:space="preserve">GABRIELA CAROLINA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CAPIZ</t>
+          <t xml:space="preserve">GAONA </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">OSORIO </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7474,63 +7478,67 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6611352488</t>
+          <t>6631533043</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>GALATEA MZA</t>
+          <t>CUENCA DIAZ</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>08-02-2003</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>LAURACAPIZ5@GMAIL.COM</t>
+          <t>SAGAOS0910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:14</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>09-02-2026 19:49:38</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>13-02-2026 17:22:43</t>
+          <t>09-02-2026 19:56:45</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13-02-2026 17:21:47</t>
+          <t>09-02-2026 19:56:10</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7550,36 +7558,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26090522326300001537</t>
+          <t>26090522212640001380</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Anton Omar Sanchez Ruiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342352</t>
+          <t>342555</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7589,17 +7597,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ALEXA CAMILA</t>
+          <t>JOSEFINA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>GUDILLO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ZATARAIN</t>
+          <t>WENCESLAO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7609,14 +7617,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6673421986</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>AMPLIACION REFORMA</t>
-        </is>
-      </c>
+          <t>6611143877</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7624,60 +7628,56 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>02-01-2006</t>
+          <t>23-06-1960</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ALEXACAMILAMEZAZATARAIN@GMAIL.COM</t>
+          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>09-02-2026 17:48:28</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>10-02-2026 08:50:56</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-02-2026 17:26:32</t>
+          <t>12-02-2026 08:45:46</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>11-02-2026 17:25:59</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26090522271360001469</t>
+          <t>26090522289640001487</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7695,34 +7695,34 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342767</t>
+          <t>343556</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7732,17 +7732,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LESLI TERESA</t>
+          <t>LAURA YAZMIN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CAPIZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GERONIMO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7752,10 +7752,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6611143806</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6611352488</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>GALATEA MZA</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7763,56 +7767,60 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>08-02-2003</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>LESLITERESAG09@GMAIL.COM</t>
+          <t>LAURACAPIZ5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 17:51:20</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 17:19:14</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 17:52:10</t>
+          <t>13-02-2026 17:22:43</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:21:47</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7820,36 +7828,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26090522241540001424</t>
+          <t>26090522326300001537</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342555</t>
+          <t>342767</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7859,17 +7867,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JOSEFINA</t>
+          <t>LESLI TERESA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GUDILLO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WENCESLAO</t>
+          <t>GERONIMO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7879,7 +7887,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6611143877</t>
+          <t>6611143806</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7890,17 +7898,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>23-06-1960</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>WENCESLAOJOPSEFINA@GMAIL.COM</t>
+          <t>LESLITERESAG09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 08:50:56</t>
+          <t>10-02-2026 17:51:20</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7925,12 +7933,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:46</t>
+          <t>10-02-2026 17:52:10</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -7947,19 +7955,11 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26090522289640001487</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522241540001424</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
           <t>549</t>
@@ -7979,12 +7979,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343039</t>
+          <t>346943</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>89108</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>BRIANA MICHAELL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8014,35 +8014,39 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6862144489</t>
+          <t>6611128257</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PUERTO NUEVO</t>
+          <t>EL DESCANSO 13</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>06-05-1979</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
+          <t>BRIANAMHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:54</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>27-02-2026 13:30:29</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8060,17 +8064,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>11-02-2026 16:31:31</t>
+          <t>27-02-2026 13:36:31</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11-02-2026 16:29:22</t>
+          <t>27-02-2026 13:35:28</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8090,7 +8094,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26090522268680001467</t>
+          <t>26090522711380001968</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8102,24 +8106,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Anton Omar Sanchez Ruiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>346943</t>
+          <t>346963</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>89108</t>
+          <t>89128</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8129,17 +8133,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BRIANA MICHAELL</t>
+          <t>EDWIN JULIAN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8149,57 +8153,53 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6611128257</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>EL DESCANSO 13</t>
-        </is>
-      </c>
+          <t>6611016162</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>26-06-2003</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BRIANAMHERNANDEZ@GMAIL.COM</t>
+          <t>EDWINCAROVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>27-02-2026 13:30:29</t>
+          <t>27-02-2026 14:43:05</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>27-02-2026 13:36:31</t>
+          <t>27-02-2026 14:44:54</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8207,21 +8207,13 @@
           <t>27-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>27-02-2026 13:35:28</t>
-        </is>
-      </c>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8229,14 +8221,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26090522711380001968</t>
+          <t>26090522712900001972</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8253,12 +8245,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>346963</t>
+          <t>343039</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>89128</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8268,17 +8260,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EDWIN JULIAN</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8288,10 +8280,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6611016162</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6862144489</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PUERTO NUEVO</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8299,56 +8295,60 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>26-06-2003</t>
+          <t>06-05-1979</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>EDWINCAROVALENZUELA@GMAIL.COM</t>
+          <t>LETICIAGRAJEDA364@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>27-02-2026 14:43:05</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>11-02-2026 16:24:54</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>27-02-2026 14:44:54</t>
+          <t>11-02-2026 16:31:31</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:29:22</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8356,24 +8356,24 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26090522712900001972</t>
+          <t>26090522268680001467</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar Sanchez Ruiz</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8793,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344302</t>
+          <t>344063</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8808,17 +8808,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t xml:space="preserve">CESAR </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BERMUDEZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6611357801</t>
+          <t>6616165544</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8839,17 +8839,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11-05-2006</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BERMUDEZALFREDO486@GMAIL.COM</t>
+          <t>ACOSTAARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 18:36:55</t>
+          <t>16-02-2026 13:14:13</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8864,17 +8864,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>16-02-2026 18:38:24</t>
+          <t>16-02-2026 13:15:43</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8896,24 +8896,24 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26090522405140001594</t>
+          <t>26090522388310001582</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344063</t>
+          <t>346648</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9062,17 +9062,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR </t>
+          <t>JUAN  OBED</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>GOCOBACHI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MAYORQIN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6616165544</t>
+          <t>6624335395</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9093,22 +9093,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>17-09-1990</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ACOSTAARANDA@GMAIL.COM</t>
+          <t>OBADGOCOBACHI7@MAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>16-02-2026 13:14:13</t>
+          <t>26-02-2026 08:58:28</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -9118,28 +9118,28 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>16-02-2026 13:15:43</t>
+          <t>26-02-2026 08:59:35</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V65" t="inlineStr"/>
@@ -9150,36 +9150,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26090522388310001582</t>
+          <t>26090522678460001916</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>346648</t>
+          <t>344302</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88813</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9189,17 +9189,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JUAN  OBED</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GOCOBACHI</t>
+          <t>BERMUDEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MAYORQIN</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6624335395</t>
+          <t>6611357801</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9220,22 +9220,22 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17-09-1990</t>
+          <t>11-05-2006</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>OBADGOCOBACHI7@MAIL.COM</t>
+          <t>BERMUDEZALFREDO486@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>26-02-2026 08:58:28</t>
+          <t>16-02-2026 18:36:55</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -9255,18 +9255,18 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>26-02-2026 08:59:35</t>
+          <t>16-02-2026 18:38:24</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V66" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26090522678460001916</t>
+          <t>26090522405140001594</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9440,12 +9440,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344823</t>
+          <t>343924</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9455,17 +9455,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ROSA ELENA</t>
+          <t>OSCAR DANIEL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9475,67 +9475,67 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>9515137595</t>
+          <t>6611162254</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JOSE AROS AGUILAR 1489-2</t>
+          <t>MARIANO ESCOBEDO 1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>02-03-1998</t>
+          <t>30-03-1985</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
+          <t>OSCARTB42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18-02-2026 14:26:16</t>
+          <t>16-02-2026 06:13:03</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>18-02-2026 14:37:29</t>
+          <t>16-02-2026 06:15:53</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>18-02-2026 14:36:30</t>
+          <t>16-02-2026 06:15:06</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9555,36 +9555,36 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26090522462920001658</t>
+          <t>26090522377270001563</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>344923</t>
+          <t>343964</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>DULCE NAYELY</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9614,28 +9614,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6611960769</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>6647907702</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>MAR DE ARAFURA 1881</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>30-09-2010</t>
+          <t>04-09-1989</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>SEBASTIANNHERNANDEZ01938@GMAIL.COM</t>
+          <t>SANHEZNAYELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18-02-2026 18:09:13</t>
+          <t>16-02-2026 08:20:26</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9645,36 +9649,44 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>25-02-2026 11:10:28</t>
+          <t>16-02-2026 08:26:12</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:25:33</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9682,44 +9694,36 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26090522650080001884</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522380980001572</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Carolina Diaz Martinez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>343924</t>
+          <t>344823</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9729,17 +9733,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OSCAR DANIEL</t>
+          <t>ROSA ELENA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9749,67 +9753,67 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6611162254</t>
+          <t>9515137595</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MARIANO ESCOBEDO 1</t>
+          <t>JOSE AROS AGUILAR 1489-2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>30-03-1985</t>
+          <t>02-03-1998</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>OSCARTB42@GMAIL.COM</t>
+          <t>ROSELXDANDRADEROBLES@GMAI.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>16-02-2026 06:13:03</t>
+          <t>18-02-2026 14:26:16</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>16-02-2026 06:15:53</t>
+          <t>18-02-2026 14:37:29</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>16-02-2026 06:15:06</t>
+          <t>18-02-2026 14:36:30</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9829,36 +9833,36 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26090522377270001563</t>
+          <t>26090522462920001658</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343964</t>
+          <t>344923</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9868,17 +9872,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DULCE NAYELY</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9888,32 +9892,28 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6647907702</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>MAR DE ARAFURA 1881</t>
-        </is>
-      </c>
+          <t>6611960769</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>04-09-1989</t>
+          <t>30-09-2010</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>SANHEZNAYELI@GMAIL.COM</t>
+          <t>SEBASTIANNHERNANDEZ01938@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>16-02-2026 08:20:26</t>
+          <t>18-02-2026 18:09:13</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9923,44 +9923,36 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>16-02-2026 08:26:12</t>
+          <t>25-02-2026 11:10:28</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:25:33</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9968,24 +9960,32 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26090522380980001572</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
+          <t>26090522650080001884</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carolina Diaz Martinez</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -10119,12 +10119,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>345795</t>
+          <t>346127</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>87960</t>
+          <t>88292</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10134,17 +10134,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MOURET</t>
+          <t>CHIQUITO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6611304257</t>
+          <t>6611079426</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10165,22 +10165,22 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04-11-1999</t>
+          <t>11-06-2007</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>MOURET27@GMAIL.COM</t>
+          <t>CHIQUITOVALERIA50@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>23-02-2026 14:07:40</t>
+          <t>24-02-2026 12:00:24</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -10190,22 +10190,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>23-02-2026 14:09:50</t>
+          <t>24-02-2026 12:01:08</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -10222,36 +10222,36 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26090522581870001790</t>
+          <t>26090522616910001819</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carolina Diaz Martinez</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>346173</t>
+          <t>345795</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>88338</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10261,17 +10261,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JOSE JUAN</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t>MOURET</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AUDELO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10281,28 +10281,28 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6441906269</t>
+          <t>6611304257</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>05-04-2010</t>
+          <t>04-11-1999</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>JCORRALAUDELO@GMAIL.COM</t>
+          <t>MOURET27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>24-02-2026 15:18:15</t>
+          <t>23-02-2026 14:07:40</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10317,22 +10317,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>24-02-2026 15:20:00</t>
+          <t>23-02-2026 14:09:50</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -10349,14 +10349,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26090522621970001828</t>
+          <t>26090522581870001790</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10373,12 +10373,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>346127</t>
+          <t>346173</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>88338</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10388,17 +10388,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t>JOSE JUAN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CHIQUITO</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>AUDELO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10408,33 +10408,33 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6611079426</t>
+          <t>6441906269</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>11-06-2007</t>
+          <t>05-04-2010</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CHIQUITOVALERIA50@GMAIL.COM</t>
+          <t>JCORRALAUDELO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>24-02-2026 12:00:24</t>
+          <t>24-02-2026 15:18:15</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -10444,17 +10444,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>24-02-2026 12:01:08</t>
+          <t>24-02-2026 15:20:00</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10476,36 +10476,36 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26090522616910001819</t>
+          <t>26090522621970001828</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Carolina Diaz Martinez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>346717</t>
+          <t>346304</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88882</t>
+          <t>88469</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10515,17 +10515,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10535,67 +10535,67 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6611243640</t>
+          <t>6612391543</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSARITO </t>
+          <t xml:space="preserve">CALLE PETEN </t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>26-02-1982</t>
+          <t>20-05-1997</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>FB1341700@GMAIL.COM</t>
+          <t>CARLITOSPONCE489@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>26-02-2026 14:39:11</t>
+          <t>24-02-2026 19:00:11</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>26-02-2026 14:56:18</t>
+          <t>24-02-2026 19:04:29</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>26-02-2026 14:54:28</t>
+          <t>24-02-2026 19:03:32</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10615,36 +10615,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26090522684060001928</t>
+          <t>26090522633450001844</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>346960</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>89125</t>
+          <t>87872</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GUSTAVO ISAI</t>
+          <t xml:space="preserve">ADRIAN </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6611466733</t>
+          <t>6611304733</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10685,17 +10685,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>09-10-2010</t>
+          <t>23-06-2000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>GUSTAVOISAI.1085@GMAIL.COM</t>
+          <t>CASTAÑEDAADRIANSANCHEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>27-02-2026 14:35:42</t>
+          <t>23-02-2026 11:06:28</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10720,18 +10720,18 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>27-02-2026 14:37:37</t>
+          <t>23-02-2026 11:07:27</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V77" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26090522712760001971</t>
+          <t>26090522576680001779</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
@@ -10766,12 +10766,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>346717</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>89260</t>
+          <t>88882</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10781,17 +10781,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JUAN ELI</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">BALDERAS </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10801,67 +10801,79 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6644533073</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>6611243640</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSARITO </t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>25-04-2001</t>
+          <t>26-02-1982</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>JUNIO20040611@GMAIL.COM</t>
+          <t>FB1341700@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>27-02-2026 21:32:39</t>
+          <t>26-02-2026 14:39:11</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>27-02-2026 21:34:53</t>
+          <t>26-02-2026 14:56:18</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr"/>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>26-02-2026 14:54:28</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10869,14 +10881,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26090522726450001981</t>
+          <t>26090522684060001928</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10893,12 +10905,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>345707</t>
+          <t>346960</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>87872</t>
+          <t>89125</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10908,17 +10920,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN </t>
+          <t>GUSTAVO ISAI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10928,7 +10940,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6611304733</t>
+          <t>6611466733</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10939,17 +10951,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>23-06-2000</t>
+          <t>09-10-2010</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CASTAÑEDAADRIANSANCHEZ@GMAIL.COM</t>
+          <t>GUSTAVOISAI.1085@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>23-02-2026 11:06:28</t>
+          <t>27-02-2026 14:35:42</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -10974,18 +10986,18 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>23-02-2026 11:07:27</t>
+          <t>27-02-2026 14:37:37</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V79" t="inlineStr"/>
@@ -10996,7 +11008,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26090522576680001779</t>
+          <t>26090522712760001971</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
@@ -11020,12 +11032,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>346304</t>
+          <t>347095</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>88469</t>
+          <t>89260</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11035,7 +11047,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>JUAN ELI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11045,7 +11057,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11055,14 +11067,10 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6612391543</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CALLE PETEN </t>
-        </is>
-      </c>
+          <t>6644533073</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -11070,17 +11078,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>20-05-1997</t>
+          <t>25-04-2001</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CARLITOSPONCE489@GMAIL.COM</t>
+          <t>JUNIO20040611@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>24-02-2026 19:00:11</t>
+          <t>27-02-2026 21:32:39</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11090,44 +11098,36 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>24-02-2026 19:04:29</t>
+          <t>27-02-2026 21:34:53</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>24-02-2026 19:03:32</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11135,24 +11135,24 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26090522633450001844</t>
+          <t>26090522726450001981</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carolina Diaz Martinez</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -11568,12 +11568,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carolina Diaz Martinez</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>336223</t>
+          <t>319204</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVANA MELISSA </t>
+          <t>GENJI ABRIL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABRERA </t>
+          <t>WONG</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6645529419</t>
+          <t>6645690211</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02-11-2006</t>
+          <t>08-04-2008</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IV.MELISSA.SR@GMAIL.COM</t>
+          <t>ABRILWRONG34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>19-01-2026 20:27:21</t>
+          <t>17-10-2025 12:19:22</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 12:59:44</t>
+          <t>03-03-2026 14:35:00</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,18 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26130522792280003806</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522841980002103</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347757</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAMILA NICOLE</t>
+          <t>AILED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,10 +740,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6651370122</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6632032484</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C ROSALIA</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -755,32 +755,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-05-2012</t>
+          <t>11-06-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+          <t>GARCIAADEBORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:12</t>
+          <t>28-03-2025 14:59:37</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -790,21 +790,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:16</t>
+          <t>03-03-2026 19:47:20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:46:37</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -812,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522807480002050</t>
+          <t>26090522859830002123</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -963,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347875</t>
+          <t>336223</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA MARIA </t>
+          <t xml:space="preserve">IVANA MELISSA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t xml:space="preserve">CABRERA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -998,7 +1006,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6643685663</t>
+          <t>6645529419</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,22 +1017,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-06-1964</t>
+          <t>02-11-2006</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+          <t>IV.MELISSA.SR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:27</t>
+          <t>19-01-2026 20:27:21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1034,17 +1042,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:41:52</t>
+          <t>02-03-2026 12:59:44</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1055,7 +1063,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1066,14 +1074,18 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090522817500002070</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26130522792280003806</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1090,12 +1102,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347523</t>
+          <t>347757</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>89922</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHRISTOPER ABRAHAM</t>
+          <t>CAMILA NICOLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RUBIO</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1125,33 +1137,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6647768405</t>
+          <t>6651370122</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-09-2009</t>
+          <t>10-05-2012</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+          <t>CAMILANICOLEGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:46</t>
+          <t>02-03-2026 17:39:12</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1161,17 +1173,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:05:54</t>
+          <t>02-03-2026 17:40:16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1182,7 +1194,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1193,14 +1205,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522790230002022</t>
+          <t>26090522807480002050</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1217,12 +1229,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347861</t>
+          <t>347634</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1232,17 +1244,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILSE </t>
+          <t>ZAHID RAFAEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1252,28 +1264,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6611286493</t>
+          <t>6641832101</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>08-12-1995</t>
+          <t>26-04-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ILSE.CHH8@GMAIL.COM</t>
+          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:37</t>
+          <t>02-03-2026 15:34:47</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1288,28 +1300,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:15</t>
+          <t>03-03-2026 14:27:26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1320,22 +1332,1086 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>26090522841560002101</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>347523</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>89688</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHRISTOPER ABRAHAM</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6647768405</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>02-09-2009</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:04:46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:05:54</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26090522790230002022</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347629</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>89794</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SANDY ITZEL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SALDAÑA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6632064102</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>18-02-2009</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SANDYITZEL000@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:24:16</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:26:15</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26090522841530002100</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Anton Omar  Sanchez</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90182</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DANIELA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAZ </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BADUY</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6642812643</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25-02-2010</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DANIELADIAZBAD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:57:43</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:58:30</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26090522838120002095</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348287</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90452</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MARIA DOLORES</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ITURRIU</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MILLER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6441033946</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV TRASNPENINSULAR </t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>03-10-1963</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MARIODOLESITURRIU@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:40:47</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:38</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:45:13</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26090522861560002128</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347875</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90040</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA MARIA </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANGUIANO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARIAS </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6643685663</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15-06-1964</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:40:27</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:41:52</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26090522817500002070</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348063</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90228</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MELISSA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CARDIEL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6644873362</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>17-05-2008</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CARDIEL1708@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:31:39</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:33:16</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26090522841930002102</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347808</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>89973</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LIZETH DANIELA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6611720452</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A PEMEX</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>04-01-2004</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DG2940547@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:19:35</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:37:10</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:35:06</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26090522851370002111</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347861</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ILSE </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6611286493</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>08-12-1995</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ILSE.CHH8@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:09:37</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:13:15</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>26090522815680002066</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>319204</t>
+          <t>297996</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GENJI ABRIL</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WONG</t>
+          <t>MOSQUEIRA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,33 +613,33 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6645690211</t>
+          <t>4427768901</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>08-04-2008</t>
+          <t>20-09-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ABRILWRONG34@GMAIL.COM</t>
+          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>17-10-2025 12:19:22</t>
+          <t>11-06-2025 21:10:26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,28 +649,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 14:35:00</t>
+          <t>04-03-2026 19:13:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26090522841980002103</t>
+          <t>26130522896860004073</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>285358</t>
+          <t>347375</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AILED</t>
+          <t xml:space="preserve">OSCAR RAFAEL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>AGUILLON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,67 +740,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6632032484</t>
+          <t>5628305473</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C ROSALIA</t>
+          <t>COLONET 651</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11-06-1998</t>
+          <t>15-11-1994</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GARCIAADEBORA@GMAIL.COM</t>
+          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-03-2025 14:59:37</t>
+          <t>02-03-2026 04:40:37</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 19:47:20</t>
+          <t>04-03-2026 04:44:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 19:46:37</t>
+          <t>04-03-2026 04:43:50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -820,14 +820,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522859830002123</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26090522863860002129</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346897</t>
+          <t>318692</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89062</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESMERALDA </t>
+          <t>MICHEL ELIZABETH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAZADOS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,7 +887,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6611074527</t>
+          <t>6611139633</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -890,22 +898,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-09-2012</t>
+          <t>11-04-2010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ESMERALDACAZADOS@GMAIL.COM</t>
+          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-02-2026 10:11:26</t>
+          <t>14-10-2025 13:44:28</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -915,22 +923,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:07</t>
+          <t>04-03-2026 13:32:16</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -947,14 +955,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26090522807210002049</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26090522881570002149</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1102,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347757</t>
+          <t>347523</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>89688</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CAMILA NICOLE</t>
+          <t>CHRISTOPER ABRAHAM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>RUBIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,33 +1153,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6651370122</t>
+          <t>6647768405</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-05-2012</t>
+          <t>02-09-2009</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:12</t>
+          <t>02-03-2026 12:04:46</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1173,17 +1189,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:16</t>
+          <t>02-03-2026 12:05:54</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1194,7 +1210,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1205,14 +1221,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522807480002050</t>
+          <t>26090522790230002022</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1229,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347634</t>
+          <t>319204</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89799</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1244,19 +1260,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ZAHID RAFAEL</t>
+          <t>GENJI ABRIL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>WONG</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>HERNANDEZ</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GARCIA</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>52</t>
@@ -1264,28 +1280,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6641832101</t>
+          <t>6645690211</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>26-04-2009</t>
+          <t>08-04-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
+          <t>ABRILWRONG34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 15:34:47</t>
+          <t>17-10-2025 12:19:22</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1310,7 +1326,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 14:27:26</t>
+          <t>03-03-2026 14:35:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1332,19 +1348,11 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26090522841560002101</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522841980002103</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>399</t>
@@ -1364,12 +1372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347523</t>
+          <t>346897</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>89062</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1379,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHRISTOPER ABRAHAM</t>
+          <t xml:space="preserve">ESMERALDA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CAZADOS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RUBIO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1399,33 +1407,33 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6647768405</t>
+          <t>6611074527</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02-09-2009</t>
+          <t>12-09-2012</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+          <t>ESMERALDACAZADOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:46</t>
+          <t>27-02-2026 10:11:26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1435,17 +1443,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:05:54</t>
+          <t>02-03-2026 17:37:07</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1456,7 +1464,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1467,14 +1475,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26090522790230002022</t>
+          <t>26090522807210002049</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1491,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,17 +1514,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANDY ITZEL</t>
+          <t xml:space="preserve">ROSA MARIA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ARIAS </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1526,7 +1534,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6632064102</t>
+          <t>6643685663</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,17 +1545,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>15-06-1964</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SANDYITZEL000@GMAIL.COM</t>
+          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 15:24:16</t>
+          <t>02-03-2026 19:40:27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1562,28 +1570,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:15</t>
+          <t>02-03-2026 19:41:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1594,44 +1602,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26090522841530002100</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522817500002070</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348017</t>
+          <t>347629</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DANIELA ALEJANDRA</t>
+          <t>SANDY ITZEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ </t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BADUY</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6642812643</t>
+          <t>6632064102</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-02-2010</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DANIELADIAZBAD@GMAIL.COM</t>
+          <t>SANDYITZEL000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 11:57:43</t>
+          <t>02-03-2026 15:24:16</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 11:58:30</t>
+          <t>03-03-2026 14:26:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1729,11 +1729,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26090522838120002095</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26090522841530002100</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>399</t>
@@ -1741,24 +1749,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348287</t>
+          <t>348082</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1768,17 +1776,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ITURRIU</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1788,14 +1796,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6441033946</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV TRASNPENINSULAR </t>
-        </is>
-      </c>
+          <t>6611130503</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1803,32 +1807,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>03-10-1963</t>
+          <t>21-05-2009</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MARIODOLESITURRIU@GMAIL.COM</t>
+          <t>FERNANDITAMARIN29@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 20:40:47</t>
+          <t>03-03-2026 15:20:32</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1838,29 +1842,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:38</t>
+          <t>05-03-2026 15:08:56</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:45:13</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1868,11 +1864,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26090522861560002128</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26090522918370002187</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1892,12 +1896,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347875</t>
+          <t>348287</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>90452</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1907,17 +1911,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA MARIA </t>
+          <t>MARIA DOLORES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t>ITURRIU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS </t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1927,10 +1931,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6643685663</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6441033946</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV TRASNPENINSULAR </t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1938,56 +1946,64 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-06-1964</t>
+          <t>03-10-1963</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+          <t>MARIODOLESITURRIU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:27</t>
+          <t>03-03-2026 20:40:47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:41:52</t>
+          <t>03-03-2026 20:51:38</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:45:13</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1995,14 +2011,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522817500002070</t>
+          <t>26090522861560002128</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2019,12 +2035,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348063</t>
+          <t>347808</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2034,17 +2050,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>LIZETH DANIELA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARDIEL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2054,10 +2070,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6644873362</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6611720452</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A PEMEX</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2065,42 +2085,42 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17-05-2008</t>
+          <t>04-01-2004</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CARDIEL1708@GMAIL.COM</t>
+          <t>DG2940547@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 14:31:39</t>
+          <t>02-03-2026 18:19:35</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 14:33:16</t>
+          <t>03-03-2026 17:37:10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2108,13 +2128,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:35:06</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2122,14 +2150,22 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522841930002102</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26090522851370002111</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2146,12 +2182,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347808</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89973</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2161,17 +2197,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LIZETH DANIELA</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>CARDIEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2181,14 +2217,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6611720452</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CAMINO VIEJO A PEMEX</t>
-        </is>
-      </c>
+          <t>6644873362</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2196,42 +2228,42 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-01-2004</t>
+          <t>17-05-2008</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DG2940547@GMAIL.COM</t>
+          <t>CARDIEL1708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:35</t>
+          <t>03-03-2026 14:31:39</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:10</t>
+          <t>03-03-2026 14:33:16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2239,21 +2271,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:35:06</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2261,22 +2285,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522851370002111</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522841930002102</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2293,12 +2309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347861</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2308,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILSE </t>
+          <t>AILED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2328,10 +2344,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6611286493</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6632032484</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C ROSALIA</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2339,56 +2359,64 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08-12-1995</t>
+          <t>11-06-1998</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ILSE.CHH8@GMAIL.COM</t>
+          <t>GARCIAADEBORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:37</t>
+          <t>28-03-2025 14:59:37</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:15</t>
+          <t>03-03-2026 19:47:20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:46:37</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2396,24 +2424,540 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522815680002066</t>
+          <t>26090522859830002123</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>347757</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>89922</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CAMILA NICOLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GASTELUM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BURGOS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6651370122</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>10-05-2012</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:39:12</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:40:16</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26090522807480002050</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>347861</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ILSE </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6611286493</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>08-12-1995</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ILSE.CHH8@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:09:37</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:13:15</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26090522815680002066</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90182</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DANIELA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAZ </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BADUY</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6642812643</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>25-02-2010</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DANIELADIAZBAD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:57:43</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:58:30</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26090522838120002095</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>347634</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>89799</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ZAHID RAFAEL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6641832101</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>26-04-2009</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:34:47</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:27:26</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26090522841560002101</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Anton Omar  Sanchez</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>297996</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95494</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>AILED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MOSQUEIRA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,43 +613,47 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4427768901</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6632032484</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C ROSALIA</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-09-2004</t>
+          <t>11-06-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
+          <t>GARCIAADEBORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11-06-2025 21:10:26</t>
+          <t>28-03-2025 14:59:37</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 19:13:48</t>
+          <t>03-03-2026 19:47:20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:46:37</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26130522896860004073</t>
+          <t>26090522859830002123</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347375</t>
+          <t>336223</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR RAFAEL </t>
+          <t xml:space="preserve">IVANA MELISSA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">CABRERA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGUILLON</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,79 +752,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5628305473</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>COLONET 651</t>
-        </is>
-      </c>
+          <t>6645529419</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15-11-1994</t>
+          <t>02-11-2006</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
+          <t>IV.MELISSA.SR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:37</t>
+          <t>19-01-2026 20:27:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 04:44:49</t>
+          <t>02-03-2026 12:59:44</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>04-03-2026 04:43:50</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522863860002129</t>
+          <t>26130522792280003806</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -828,14 +828,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>318692</t>
+          <t>319204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MICHEL ELIZABETH</t>
+          <t>GENJI ABRIL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>WONG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6611139633</t>
+          <t>6645690211</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -898,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11-04-2010</t>
+          <t>08-04-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
+          <t>ABRILWRONG34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>14-10-2025 13:44:28</t>
+          <t>17-10-2025 12:19:22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -933,18 +929,18 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 13:32:16</t>
+          <t>03-03-2026 14:35:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -955,19 +951,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26090522881570002149</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522841980002103</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>399</t>
@@ -987,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>336223</t>
+          <t>318692</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVANA MELISSA </t>
+          <t>MICHEL ELIZABETH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABRERA </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,7 +1010,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6645529419</t>
+          <t>6611139633</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,22 +1021,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-11-2006</t>
+          <t>11-04-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IV.MELISSA.SR@GMAIL.COM</t>
+          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19-01-2026 20:27:21</t>
+          <t>14-10-2025 13:44:28</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1058,28 +1046,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:59:44</t>
+          <t>04-03-2026 13:32:16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26130522792280003806</t>
+          <t>26090522881570002149</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1098,10 +1086,14 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347523</t>
+          <t>297996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHRISTOPER ABRAHAM</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MOSQUEIRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RUBIO</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,7 +1145,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6647768405</t>
+          <t>4427768901</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,22 +1156,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-09-2009</t>
+          <t>20-09-2004</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:46</t>
+          <t>11-06-2025 21:10:26</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1189,28 +1181,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:05:54</t>
+          <t>04-03-2026 19:13:48</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1221,14 +1213,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522790230002022</t>
+          <t>26130522896860004073</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1245,12 +1237,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>319204</t>
+          <t>347523</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>89688</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1252,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GENJI ABRIL</t>
+          <t>CHRISTOPER ABRAHAM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WONG</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RUBIO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,28 +1272,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6645690211</t>
+          <t>6647768405</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>08-04-2008</t>
+          <t>02-09-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ABRILWRONG34@GMAIL.COM</t>
+          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17-10-2025 12:19:22</t>
+          <t>02-03-2026 12:04:46</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1326,12 +1318,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 14:35:00</t>
+          <t>02-03-2026 12:05:54</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1348,7 +1340,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26090522841980002103</t>
+          <t>26090522790230002022</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1458,7 +1450,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1499,12 +1491,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347875</t>
+          <t>347375</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,17 +1506,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA MARIA </t>
+          <t xml:space="preserve">OSCAR RAFAEL </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS </t>
+          <t>AGUILLON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1534,28 +1526,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6643685663</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>5628305473</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COLONET 651</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-06-1964</t>
+          <t>15-11-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:27</t>
+          <t>02-03-2026 04:40:37</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1565,36 +1561,44 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:41:52</t>
+          <t>04-03-2026 04:44:49</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:43:50</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1602,14 +1606,22 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26090522817500002070</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26090522863860002129</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1626,12 +1638,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>347634</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1641,17 +1653,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANDY ITZEL</t>
+          <t>ZAHID RAFAEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1661,28 +1673,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6632064102</t>
+          <t>6641832101</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>26-04-2009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SANDYITZEL000@GMAIL.COM</t>
+          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:24:16</t>
+          <t>02-03-2026 15:34:47</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,12 +1719,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:15</t>
+          <t>03-03-2026 14:27:26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1729,7 +1741,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26090522841530002100</t>
+          <t>26090522841560002101</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1761,12 +1773,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348082</t>
+          <t>347757</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>89922</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1776,17 +1788,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>CAMILA NICOLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1796,7 +1808,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6611130503</t>
+          <t>6651370122</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1807,17 +1819,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-05-2009</t>
+          <t>10-05-2012</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FERNANDITAMARIN29@GMAIL.COM</t>
+          <t>CAMILANICOLEGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 15:20:32</t>
+          <t>02-03-2026 17:39:12</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1842,18 +1854,18 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 15:08:56</t>
+          <t>02-03-2026 17:40:16</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1864,19 +1876,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26090522918370002187</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522807480002050</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1896,12 +1900,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348287</t>
+          <t>347629</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1911,17 +1915,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>SANDY ITZEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ITURRIU</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1931,14 +1935,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6441033946</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV TRASNPENINSULAR </t>
-        </is>
-      </c>
+          <t>6632064102</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1946,64 +1946,56 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>03-10-1963</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MARIODOLESITURRIU@GMAIL.COM</t>
+          <t>SANDYITZEL000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 20:40:47</t>
+          <t>02-03-2026 15:24:16</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:38</t>
+          <t>03-03-2026 14:26:15</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:45:13</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2011,36 +2003,44 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522861560002128</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26090522841530002100</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347808</t>
+          <t>348017</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89973</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LIZETH DANIELA</t>
+          <t>DANIELA ALEJANDRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">DIAZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>BADUY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2070,14 +2070,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6611720452</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CAMINO VIEJO A PEMEX</t>
-        </is>
-      </c>
+          <t>6642812643</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2085,64 +2081,56 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>04-01-2004</t>
+          <t>25-02-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DG2940547@GMAIL.COM</t>
+          <t>DANIELADIAZBAD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:35</t>
+          <t>03-03-2026 11:57:43</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:10</t>
+          <t>03-03-2026 11:58:30</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:35:06</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2150,22 +2138,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522851370002111</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522838120002095</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2182,12 +2162,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348063</t>
+          <t>347808</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2177,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>LIZETH DANIELA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CARDIEL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,10 +2197,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6644873362</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6611720452</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A PEMEX</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2228,56 +2212,64 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>17-05-2008</t>
+          <t>04-01-2004</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CARDIEL1708@GMAIL.COM</t>
+          <t>DG2940547@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 14:31:39</t>
+          <t>02-03-2026 18:19:35</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 14:33:16</t>
+          <t>03-03-2026 17:37:10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:35:06</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2285,14 +2277,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522841930002102</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26090522851370002111</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2309,12 +2309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>285358</t>
+          <t>347861</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AILED</t>
+          <t xml:space="preserve">ILSE </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,14 +2344,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6632032484</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>C ROSALIA</t>
-        </is>
-      </c>
+          <t>6611286493</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2359,64 +2355,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11-06-1998</t>
+          <t>08-12-1995</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>GARCIAADEBORA@GMAIL.COM</t>
+          <t>ILSE.CHH8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>28-03-2025 14:59:37</t>
+          <t>02-03-2026 19:09:37</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 19:47:20</t>
+          <t>02-03-2026 19:13:15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:46:37</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2424,14 +2412,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522859830002123</t>
+          <t>26090522815680002066</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2448,12 +2436,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347757</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2463,17 +2451,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CAMILA NICOLE</t>
+          <t xml:space="preserve">ROSA MARIA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t xml:space="preserve">ARIAS </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2483,7 +2471,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6651370122</t>
+          <t>6643685663</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2494,22 +2482,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10-05-2012</t>
+          <t>15-06-1964</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:12</t>
+          <t>02-03-2026 19:40:27</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2519,22 +2507,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:16</t>
+          <t>02-03-2026 19:41:52</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2551,14 +2539,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26090522807480002050</t>
+          <t>26090522817500002070</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2575,12 +2563,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347861</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2590,17 +2578,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILSE </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CARDIEL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2610,7 +2598,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6611286493</t>
+          <t>6644873362</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2621,17 +2609,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>08-12-1995</t>
+          <t>17-05-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ILSE.CHH8@GMAIL.COM</t>
+          <t>CARDIEL1708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:37</t>
+          <t>03-03-2026 14:31:39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2646,28 +2634,28 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:15</t>
+          <t>03-03-2026 14:33:16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2678,14 +2666,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26090522815680002066</t>
+          <t>26090522841930002102</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2702,12 +2690,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348017</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2717,17 +2705,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DANIELA ALEJANDRA</t>
+          <t>MONICA ANDREA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ </t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BADUY</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2737,7 +2725,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6642812643</t>
+          <t>6644795244</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2748,17 +2736,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25-02-2010</t>
+          <t>29-10-2009</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DANIELADIAZBAD@GMAIL.COM</t>
+          <t>MROSASG09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 11:57:43</t>
+          <t>05-03-2026 15:10:46</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2783,12 +2771,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 11:58:30</t>
+          <t>06-03-2026 15:13:58</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2805,11 +2793,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26090522838120002095</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26090522952140002207</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>399</t>
@@ -2829,12 +2825,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347634</t>
+          <t>349159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89799</t>
+          <t>91324</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2844,120 +2840,803 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ZAHID RAFAEL</t>
+          <t>JANETH MONSERRATH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6643499569</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>25-02-1998</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MONSEJ584@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:13:07</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:20:27</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:18:53</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26090522976000002231</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Anton Omar  Sanchez</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348722</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90887</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CARMEN LIZBETH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>REDONDO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>6641832101</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>26-04-2009</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>02-03-2026 15:34:47</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6611356413</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C RUMOROSA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>04-05-1990</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>KEVENDANIEL101@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:17:47</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:07:57</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:22:33</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26090522951900002206</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349266</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91431</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VARELA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NECOECHEA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6611731894</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>16-05-2009</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FERNANDAVN162009@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:51:42</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:53:01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26090522988200002238</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349264</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91429</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MARIA DEL REFUGI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NECOECHEA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6611190907</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C TECATE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13-06-1986</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MARIANECOECHEAZ13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:44:16</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:49:29</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:48:54</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26090522988160002237</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348082</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90247</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FERNANDA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MARIN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MORAN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6611130503</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>21-05-2009</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FERNANDITAMARIN29@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:20:32</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sin contrato</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>COBACH $399</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>03-03-2026 14:27:26</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:08:56</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>26090522841560002101</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26090522918370002187</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>JACQUELINE DOLORES MURILLO DELGADO</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Anton Omar  Sanchez</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>con rutina</t>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348287</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90452</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MARIA DOLORES</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ITURRIU</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MILLER</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6441033946</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV TRASNPENINSULAR </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>03-10-1963</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MARIODOLESITURRIU@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:40:47</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:38</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:45:13</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26090522861560002128</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>285358</t>
+          <t>311271</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AILED</t>
+          <t>KARMA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MICHAELE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MCCARTHY LUCIER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6632032484</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>C ROSALIA</t>
-        </is>
-      </c>
+          <t>6611965942</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -628,64 +624,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11-06-1998</t>
+          <t>20-02-2008</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>GARCIAADEBORA@GMAIL.COM</t>
+          <t>KARMA.M.LUCIER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>28-03-2025 14:59:37</t>
+          <t>26-08-2025 16:38:27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 19:47:20</t>
+          <t>09-03-2026 17:20:14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:46:37</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,36 +681,44 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26090522859830002123</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26090523017100002277</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Abraham Mijares Fernandez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>336223</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVANA MELISSA </t>
+          <t>AILED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABRERA </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,10 +748,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645529419</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6632032484</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C ROSALIA</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -763,32 +763,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-11-2006</t>
+          <t>11-06-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IV.MELISSA.SR@GMAIL.COM</t>
+          <t>GARCIAADEBORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>19-01-2026 20:27:21</t>
+          <t>28-03-2025 14:59:37</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -798,21 +798,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:59:44</t>
+          <t>03-03-2026 19:47:20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:46:37</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,14 +828,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26130522792280003806</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090522859830002123</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -848,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>319204</t>
+          <t>297996</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GENJI ABRIL</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WONG</t>
+          <t>MOSQUEIRA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,33 +887,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6645690211</t>
+          <t>4427768901</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08-04-2008</t>
+          <t>20-09-2004</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ABRILWRONG34@GMAIL.COM</t>
+          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>17-10-2025 12:19:22</t>
+          <t>11-06-2025 21:10:26</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -919,28 +923,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 14:35:00</t>
+          <t>04-03-2026 19:13:48</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -951,14 +955,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26090522841980002103</t>
+          <t>26130522896860004073</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>318692</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MICHEL ELIZABETH</t>
+          <t>PAULA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>SALCEDO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6611139633</t>
+          <t>6646948087</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,17 +1025,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11-04-2010</t>
+          <t>03-03-2008</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
+          <t>PAULAGABRIELASALCEDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>14-10-2025 13:44:28</t>
+          <t>10-02-2025 13:24:31</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1056,18 +1060,18 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 13:32:16</t>
+          <t>10-03-2026 13:44:53</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1078,19 +1082,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090522881570002149</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090523051690002315</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>399</t>
@@ -1110,12 +1106,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>297996</t>
+          <t>298120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95494</t>
+          <t>95618</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1121,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>CARLOS FRANCISCO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MOSQUEIRA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,7 +1141,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4427768901</t>
+          <t>6863381346</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,22 +1152,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-09-2004</t>
+          <t>05-01-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
+          <t>CARLOSFRANCIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11-06-2025 21:10:26</t>
+          <t>12-06-2025 18:48:31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1181,28 +1177,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 19:13:48</t>
+          <t>16-03-2026 19:13:46</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1213,14 +1209,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26130522896860004073</t>
+          <t>26090523232510002508</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1237,12 +1233,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347523</t>
+          <t>336223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,17 +1248,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CHRISTOPER ABRAHAM</t>
+          <t xml:space="preserve">IVANA MELISSA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">CABRERA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RUBIO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1272,33 +1268,33 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6647768405</t>
+          <t>6645529419</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-09-2009</t>
+          <t>02-11-2006</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+          <t>IV.MELISSA.SR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:46</t>
+          <t>19-01-2026 20:27:21</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1308,17 +1304,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:05:54</t>
+          <t>02-03-2026 12:59:44</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1340,14 +1336,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26090522790230002022</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26130522792280003806</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346897</t>
+          <t>318692</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89062</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESMERALDA </t>
+          <t>MICHEL ELIZABETH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAZADOS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6611074527</t>
+          <t>6611139633</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,22 +1410,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12-09-2012</t>
+          <t>11-04-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ESMERALDACAZADOS@GMAIL.COM</t>
+          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>27-02-2026 10:11:26</t>
+          <t>14-10-2025 13:44:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1435,22 +1435,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:07</t>
+          <t>04-03-2026 13:32:16</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1467,14 +1467,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26090522807210002049</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26090522881570002149</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1491,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347375</t>
+          <t>319204</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,17 +1514,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR RAFAEL </t>
+          <t>GENJI ABRIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>WONG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AGUILLON</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1526,32 +1534,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5628305473</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>COLONET 651</t>
-        </is>
-      </c>
+          <t>6645690211</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-11-1994</t>
+          <t>08-04-2008</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
+          <t>ABRILWRONG34@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:37</t>
+          <t>17-10-2025 12:19:22</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1561,44 +1565,36 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 04:44:49</t>
+          <t>03-03-2026 14:35:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>04-03-2026 04:43:50</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1606,22 +1602,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26090522863860002129</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090522841980002103</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1638,12 +1626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347634</t>
+          <t>346897</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89799</t>
+          <t>89062</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,17 +1641,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ZAHID RAFAEL</t>
+          <t xml:space="preserve">ESMERALDA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CAZADOS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1673,33 +1661,33 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6641832101</t>
+          <t>6611074527</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-04-2009</t>
+          <t>12-09-2012</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
+          <t>ESMERALDACAZADOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:34:47</t>
+          <t>27-02-2026 10:11:26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1709,28 +1697,28 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 14:27:26</t>
+          <t>02-03-2026 17:37:07</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1741,44 +1729,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26090522841560002101</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522807210002049</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347757</t>
+          <t>344083</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1788,17 +1768,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CAMILA NICOLE</t>
+          <t>NAHOMI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1808,7 +1788,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6651370122</t>
+          <t>6611144495</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,17 +1799,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10-05-2012</t>
+          <t>21-05-2009</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+          <t>NAHOMIPAEZ56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:12</t>
+          <t>16-02-2026 13:57:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1854,18 +1834,18 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:16</t>
+          <t>18-03-2026 16:25:37</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1876,7 +1856,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26090522807480002050</t>
+          <t>26090523296390002581</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1900,12 +1880,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>347634</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1915,17 +1895,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SANDY ITZEL</t>
+          <t>ZAHID RAFAEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1935,28 +1915,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6632064102</t>
+          <t>6641832101</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>26-04-2009</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SANDYITZEL000@GMAIL.COM</t>
+          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:24:16</t>
+          <t>02-03-2026 15:34:47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1981,7 +1961,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:15</t>
+          <t>03-03-2026 14:27:26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2003,7 +1983,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522841530002100</t>
+          <t>26090522841560002101</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2035,12 +2015,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348017</t>
+          <t>347523</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>89688</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2050,17 +2030,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DANIELA ALEJANDRA</t>
+          <t>CHRISTOPER ABRAHAM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BADUY</t>
+          <t>RUBIO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2070,28 +2050,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6642812643</t>
+          <t>6647768405</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-02-2010</t>
+          <t>02-09-2009</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DANIELADIAZBAD@GMAIL.COM</t>
+          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 11:57:43</t>
+          <t>02-03-2026 12:04:46</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2116,12 +2096,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 11:58:30</t>
+          <t>02-03-2026 12:05:54</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2138,7 +2118,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522838120002095</t>
+          <t>26090522790230002022</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2162,12 +2142,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347808</t>
+          <t>347629</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89973</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2177,17 +2157,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LIZETH DANIELA</t>
+          <t>SANDY ITZEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2197,14 +2177,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6611720452</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CAMINO VIEJO A PEMEX</t>
-        </is>
-      </c>
+          <t>6632064102</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2212,42 +2188,42 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-01-2004</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DG2940547@GMAIL.COM</t>
+          <t>SANDYITZEL000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:35</t>
+          <t>02-03-2026 15:24:16</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:10</t>
+          <t>03-03-2026 14:26:15</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2255,21 +2231,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:35:06</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2277,7 +2245,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522851370002111</t>
+          <t>26090522841530002100</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2292,29 +2260,29 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347861</t>
+          <t>347375</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2292,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILSE </t>
+          <t xml:space="preserve">OSCAR RAFAEL </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>AGUILLON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,28 +2312,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6611286493</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>5628305473</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COLONET 651</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08-12-1995</t>
+          <t>15-11-1994</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ILSE.CHH8@GMAIL.COM</t>
+          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:37</t>
+          <t>02-03-2026 04:40:37</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2375,36 +2347,44 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:15</t>
+          <t>04-03-2026 04:44:49</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:43:50</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2412,14 +2392,22 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522815680002066</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26090522863860002129</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2436,12 +2424,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347875</t>
+          <t>347757</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>89922</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2451,17 +2439,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA MARIA </t>
+          <t>CAMILA NICOLE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS </t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2471,7 +2459,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643685663</t>
+          <t>6651370122</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2482,22 +2470,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-06-1964</t>
+          <t>10-05-2012</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+          <t>CAMILANICOLEGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:27</t>
+          <t>02-03-2026 17:39:12</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2507,17 +2495,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:41:52</t>
+          <t>02-03-2026 17:40:16</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2539,14 +2527,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26090522817500002070</t>
+          <t>26090522807480002050</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2563,12 +2551,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348063</t>
+          <t>347808</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,17 +2566,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>LIZETH DANIELA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CARDIEL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2598,10 +2586,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6644873362</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6611720452</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A PEMEX</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2609,42 +2601,42 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17-05-2008</t>
+          <t>04-01-2004</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CARDIEL1708@GMAIL.COM</t>
+          <t>DG2940547@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 14:31:39</t>
+          <t>02-03-2026 18:19:35</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 14:33:16</t>
+          <t>03-03-2026 17:37:10</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2652,13 +2644,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:35:06</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2666,14 +2666,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26090522841930002102</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26090522851370002111</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2690,12 +2698,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348717</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90882</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2705,17 +2713,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MONICA ANDREA</t>
+          <t xml:space="preserve">ROSA MARIA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">ARIAS </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2725,7 +2733,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6644795244</t>
+          <t>6643685663</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2736,17 +2744,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29-10-2009</t>
+          <t>15-06-1964</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MROSASG09@GMAIL.COM</t>
+          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>05-03-2026 15:10:46</t>
+          <t>02-03-2026 19:40:27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2761,28 +2769,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>06-03-2026 15:13:58</t>
+          <t>02-03-2026 19:41:52</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2793,22 +2801,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26090522952140002207</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522817500002070</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349159</t>
+          <t>348017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2840,17 +2840,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JANETH MONSERRATH</t>
+          <t>DANIELA ALEJANDRA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t xml:space="preserve">DIAZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BADUY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2860,14 +2860,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6643499569</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
+          <t>6642812643</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2875,64 +2871,56 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-02-1998</t>
+          <t>25-02-2010</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MONSEJ584@GMAIL.COM</t>
+          <t>DANIELADIAZBAD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-03-2026 14:13:07</t>
+          <t>03-03-2026 11:57:43</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>07-03-2026 14:20:27</t>
+          <t>03-03-2026 11:58:30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>07-03-2026 14:18:53</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2940,36 +2928,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26090522976000002231</t>
+          <t>26090522838120002095</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348722</t>
+          <t>347861</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90887</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2979,17 +2967,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARMEN LIZBETH</t>
+          <t xml:space="preserve">ILSE </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>REDONDO</t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2999,14 +2987,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6611356413</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>C RUMOROSA</t>
-        </is>
-      </c>
+          <t>6611286493</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3014,64 +2998,56 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>04-05-1990</t>
+          <t>08-12-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>KEVENDANIEL101@GMAIL.COM</t>
+          <t>ILSE.CHH8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-03-2026 15:17:47</t>
+          <t>02-03-2026 19:09:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-03-2026 15:07:57</t>
+          <t>02-03-2026 19:13:15</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>05-03-2026 15:22:33</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3079,14 +3055,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26090522951900002206</t>
+          <t>26090522815680002066</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3103,12 +3079,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349266</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91431</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3118,17 +3094,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NECOECHEA</t>
+          <t>CARDIEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3138,7 +3114,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6611731894</t>
+          <t>6644873362</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3149,22 +3125,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>17-05-2008</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>FERNANDAVN162009@GMAIL.COM</t>
+          <t>CARDIEL1708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>08-03-2026 14:51:42</t>
+          <t>03-03-2026 14:31:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3174,22 +3150,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>08-03-2026 14:53:01</t>
+          <t>03-03-2026 14:33:16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3206,14 +3182,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26090522988200002238</t>
+          <t>26090522841930002102</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3230,12 +3206,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349264</t>
+          <t>348082</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91429</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3245,17 +3221,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARIA DEL REFUGI</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NECOECHEA</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ZAMBRANO</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3265,14 +3241,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6611190907</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>C TECATE</t>
-        </is>
-      </c>
+          <t>6611130503</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3280,64 +3252,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-06-1986</t>
+          <t>21-05-2009</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MARIANECOECHEAZ13@GMAIL.COM</t>
+          <t>FERNANDITAMARIN29@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>08-03-2026 14:44:16</t>
+          <t>03-03-2026 15:20:32</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>08-03-2026 14:49:29</t>
+          <t>05-03-2026 15:08:56</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>08-03-2026 14:48:54</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3345,14 +3309,22 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26090522988160002237</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26090522918370002187</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3369,12 +3341,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348082</t>
+          <t>348722</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3384,17 +3356,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>CARMEN LIZBETH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>REDONDO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3404,10 +3376,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6611130503</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6611356413</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C RUMOROSA</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3415,32 +3391,32 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21-05-2009</t>
+          <t>04-05-1990</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FERNANDITAMARIN29@GMAIL.COM</t>
+          <t>KEVENDANIEL101@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 15:20:32</t>
+          <t>05-03-2026 15:17:47</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3450,7 +3426,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-03-2026 15:08:56</t>
+          <t>06-03-2026 15:07:57</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3458,13 +3434,21 @@
           <t>04-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:22:33</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3472,19 +3456,11 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26090522918370002187</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522951900002206</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>549</t>
@@ -3504,137 +3480,3984 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>348717</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90882</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MONICA ANDREA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ROSAS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6644795244</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>29-10-2009</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MROSASG09@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:10:46</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:13:58</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26090522952140002207</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>348287</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>90452</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>PABELLON RTO</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>MARIA DOLORES</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>ITURRIU</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>MILLER</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>6441033946</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">AV TRASNPENINSULAR </t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>03-10-1963</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>MARIODOLESITURRIU@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>03-03-2026 20:40:47</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Inscripcion $150</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>03-03-2026 20:51:38</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>03-03-2026 20:45:13</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>26090522861560002128</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>349264</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>91429</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MARIA DEL REFUGI</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NECOECHEA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6611190907</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C TECATE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13-06-1986</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MARIANECOECHEAZ13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:44:16</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:49:29</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:48:54</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26090522988160002237</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Juan Lomeli Salcedo</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349159</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>91324</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JANETH MONSERRATH</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6643499569</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25-02-1998</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MONSEJ584@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:13:07</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:20:27</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:18:53</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26090522976000002231</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Anton Omar  Sanchez</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349296</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91461</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5625561352</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BLEVD VILLAS DEL MAR 4128</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>24-05-1966</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ALAAVARADOALVARADODIANAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:52:31</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:27:36</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:26:49</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26090523043720002296</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349773</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91938</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CATALINA DE JESUS </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ALGANDAR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZAMORA </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6647968582</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>18-06-1982</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CATHERINEALG18@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:44:54</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:51:47</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:50:42</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26090523045970002300</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>349987</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92152</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ESMERALDA </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALDEZ </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERRERA </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6612872366</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>15-08-2001</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>VALDEZMARES427@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:19:01</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:36:01</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26090523068880002347</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349346</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>91511</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ALEXIS GERARDO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BATALLA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OLGUIN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6634343460</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CAJOR SERVICIOS 10440</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>02-03-2002</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ALEXSOLGUIN337@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:00:53</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:03:13</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:02:23</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26090523002810002251</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349874</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>92039</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JENIFER ANABEL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>JAUREGUI</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6611473621</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>15-01-2010</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>JENIFERANABELALVAREZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:46:34</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:48:05</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26090523055630002327</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>349876</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>92041</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ANGELICA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CARIÑO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6641589128</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>23-05-2010</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ANGELICAGABRIELA245@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:50:40</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:52:42</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26090523055740002328</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>349992</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>92157</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZULEY </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANA </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEÑA </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6611112856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>22-11-2012</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PENAPATRICIA905@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:28:07</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:31:36</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26090523068610002346</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>349266</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>91431</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VARELA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NECOECHEA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6611731894</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>16-05-2009</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>FERNANDAVN162009@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:51:42</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:53:01</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26090522988200002238</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Juan Lomeli Salcedo</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349776</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91941</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CINTHIA GISELLE </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBARRA </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALGANDAR </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6631094746</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>21-12-2003</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CINTHIAALGANDAR69@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:56:07</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:59:09</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26090523046130002301</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350164</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92329</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NAVARRO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6611958733</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>05-06-2006</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JUANMANUEL663@OUTCLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>11-03-2026 17:13:07</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>11-03-2026 17:14:19</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26090523094660002389</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>350081</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>92246</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTOR LEONARDO </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIOS </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AGUIAR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6647135005</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>26-06-2010</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>RIOSAGUIAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>11-03-2026 11:36:57</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>13-03-2026 13:31:09</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26090523152510002451</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>350098</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>92263</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRUZ </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6648569826</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>21-05-2010</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CRUZGARCIAMARI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11-03-2026 13:01:47</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>11-03-2026 13:03:26</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26090523088080002373</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>350009</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>92174</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6641688071</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>19-04-1998</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CARLOS.SANCHEZ.LOPEZ19@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10-03-2026 20:15:38</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:15:31</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26090523272820002558</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>350345</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>92509</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL DAVID </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVANDO </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELAZQUEZ </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6611355598</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25-04-2011</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ANGELDAVIDOVANDO69@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:28:47</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:31:01</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26090523123540002419</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>350352</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>92516</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA MICHELLE </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6642223351</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>21-10-2008</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MIRANDAANDRADE05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:57:05</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:59:07</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26090523124220002420</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>350990</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>93154</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6647804341</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>04-05-1997</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>FRANCOMARTINESABIGAIL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:07:12</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:08:56</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:08:22</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26090523207810002477</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Carlos Abraham Mijares Fernandez</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>351458</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>93622</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FATIMA JERALDINE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3111038971</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14-05-2003</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>FATIMAJLG1405@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:55:51</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:56:22</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:55:53</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26090523252140002538</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Carolina Diaz Martinez</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>351306</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>93470</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FURQUIM</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FURQUIN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6632065651</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>01-03-2009</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>BRUNOFHEYSE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:40:59</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:41:52</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26090523231220002506</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>351473</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>93637</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DILAR</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ESCOBAR</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HERNADEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6648159828</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>04-06-2010</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ESCOBARHERNANDEZDILAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:10:54</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:12:19</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26090523251210002535</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>350259</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>92423</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ANGEL ISMAEL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LAGUNAS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ORDUÑO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6641752193</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>07-03-2007</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>AISMAELORGUNO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>12-03-2026 07:11:20</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>12-03-2026 07:12:10</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26090523116100002404</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>351681</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>93845</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABRAHAM ISRAEL </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOSA </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACIAS </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6644937393</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>03-03-1998</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ABRAHAM10ESPINOSSA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:21:35</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:28:34</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:27:25</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26090523270130002556</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351535</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>93699</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAUL </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ANGEL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CEJA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6198300487</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>17-03-2000</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>RAUL3CEJA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:12:01</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:00:05</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:59:10</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26090523257610002547</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351579</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93743</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTORIA </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>JAYOVANA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>GRAY</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>9096301617</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>01-01-1996</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>TREX96.VG@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:51:18</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:53:16</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26090523259790002550</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>351813</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>93977</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE LUIS </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BARRERA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6611118707</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>16-01-2008</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BRRERRASURAREZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:13:11</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:14:18</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26090523290860002575</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>351461</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>93625</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JULISSA NOEMI</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>GUERRERO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6676930667</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>02-03-2005</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CORRALESGUERRERO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>17-03-2026 11:04:10</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>18-03-2026 11:02:38</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>18-03-2026 11:01:57</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26090523288760002570</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>351815</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>93979</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PABLO DANIEL </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6124414560</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>11-12-1999</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>TRUJILLOMEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:19:07</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:20:50</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26090523291070002576</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PABELLON RTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>285358</t>
+          <t>297996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AILED</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MOSQUEIRA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,47 +748,43 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6632032484</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C ROSALIA</t>
-        </is>
-      </c>
+          <t>4427768901</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11-06-1998</t>
+          <t>20-09-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GARCIAADEBORA@GMAIL.COM</t>
+          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-03-2025 14:59:37</t>
+          <t>11-06-2025 21:10:26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -798,29 +794,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 19:47:20</t>
+          <t>04-03-2026 19:13:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:46:37</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,7 +816,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522859830002123</t>
+          <t>26130522896860004073</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -852,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>297996</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>95494</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>PAULA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MOSQUEIRA</t>
+          <t>SALCEDO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,33 +875,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4427768901</t>
+          <t>6646948087</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-09-2004</t>
+          <t>03-03-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CRISTHIANMOSQUEIRACARO@GMAIL.COM</t>
+          <t>PAULAGABRIELASALCEDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11-06-2025 21:10:26</t>
+          <t>10-02-2025 13:24:31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -923,28 +911,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 19:13:48</t>
+          <t>10-03-2026 13:44:53</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -955,14 +943,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26130522896860004073</t>
+          <t>26090523051690002315</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -979,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>278181</t>
+          <t>318692</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PAULA</t>
+          <t>MICHEL ELIZABETH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SALCEDO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,7 +1002,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6646948087</t>
+          <t>6611139633</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,17 +1013,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>03-03-2008</t>
+          <t>11-04-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PAULAGABRIELASALCEDOGARCIA@GMAIL.COM</t>
+          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10-02-2025 13:24:31</t>
+          <t>14-10-2025 13:44:28</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1060,18 +1048,18 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10-03-2026 13:44:53</t>
+          <t>04-03-2026 13:32:16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1082,11 +1070,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090523051690002315</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26090522881570002149</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>399</t>
@@ -1106,12 +1102,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>298120</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95618</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CARLOS FRANCISCO</t>
+          <t>AILED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,67 +1137,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863381346</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6632032484</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C ROSALIA</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05-01-2006</t>
+          <t>11-06-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CARLOSFRANCIS@GMAIL.COM</t>
+          <t>GARCIAADEBORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12-06-2025 18:48:31</t>
+          <t>28-03-2025 14:59:37</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>16-03-2026 19:13:46</t>
+          <t>03-03-2026 19:47:20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:46:37</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1209,14 +1217,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090523232510002508</t>
+          <t>26090522859830002123</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1233,12 +1241,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>336223</t>
+          <t>298120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>95618</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1248,17 +1256,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVANA MELISSA </t>
+          <t>CARLOS FRANCISCO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABRERA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1268,33 +1276,33 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6645529419</t>
+          <t>6863381346</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-11-2006</t>
+          <t>05-01-2006</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IV.MELISSA.SR@GMAIL.COM</t>
+          <t>CARLOSFRANCIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19-01-2026 20:27:21</t>
+          <t>12-06-2025 18:48:31</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1304,22 +1312,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:59:44</t>
+          <t>16-03-2026 19:13:46</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1336,18 +1344,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26130522792280003806</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26090523232510002508</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1364,12 +1368,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>318692</t>
+          <t>336223</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1379,17 +1383,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MICHEL ELIZABETH</t>
+          <t xml:space="preserve">IVANA MELISSA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">CABRERA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1399,7 +1403,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6611139633</t>
+          <t>6645529419</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,22 +1414,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11-04-2010</t>
+          <t>02-11-2006</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHGOMEZACOSTAMI@GMAIL.COM</t>
+          <t>IV.MELISSA.SR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14-10-2025 13:44:28</t>
+          <t>19-01-2026 20:27:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1435,28 +1439,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 13:32:16</t>
+          <t>02-03-2026 12:59:44</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26090522881570002149</t>
+          <t>26130522792280003806</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1475,14 +1479,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1880,12 +1880,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347634</t>
+          <t>347375</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89799</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZAHID RAFAEL</t>
+          <t xml:space="preserve">OSCAR RAFAEL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AGUILLON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1915,10 +1915,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6641832101</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>5628305473</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COLONET 651</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1926,17 +1930,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-04-2009</t>
+          <t>15-11-1994</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
+          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:34:47</t>
+          <t>02-03-2026 04:40:37</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1946,36 +1950,44 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 14:27:26</t>
+          <t>04-03-2026 04:44:49</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>04-03-2026 04:43:50</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1983,7 +1995,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26090522841560002101</t>
+          <t>26090522863860002129</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1993,34 +2005,34 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347523</t>
+          <t>347629</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2030,19 +2042,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHRISTOPER ABRAHAM</t>
+          <t>SANDY ITZEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>SALDAÑA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>RODRIGUEZ</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>RUBIO</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>52</t>
@@ -2050,28 +2062,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6647768405</t>
+          <t>6632064102</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02-09-2009</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
+          <t>SANDYITZEL000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:46</t>
+          <t>02-03-2026 15:24:16</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2096,12 +2108,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:05:54</t>
+          <t>03-03-2026 14:26:15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2118,11 +2130,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26090522790230002022</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26090522841530002100</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>399</t>
@@ -2130,24 +2150,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>347523</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89688</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2157,17 +2177,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SANDY ITZEL</t>
+          <t>CHRISTOPER ABRAHAM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RUBIO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2177,28 +2197,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6632064102</t>
+          <t>6647768405</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>02-09-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SANDYITZEL000@GMAIL.COM</t>
+          <t>RUBIORODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 15:24:16</t>
+          <t>02-03-2026 12:04:46</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2223,12 +2243,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:15</t>
+          <t>02-03-2026 12:05:54</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2245,19 +2265,11 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26090522841530002100</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522790230002022</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>399</t>
@@ -2265,24 +2277,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347375</t>
+          <t>347634</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2292,17 +2304,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR RAFAEL </t>
+          <t>ZAHID RAFAEL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGUILLON</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2312,14 +2324,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5628305473</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>COLONET 651</t>
-        </is>
-      </c>
+          <t>6641832101</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2327,17 +2335,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15-11-1994</t>
+          <t>26-04-2009</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>AGUILLONMORALESOSCAR@GMAIL.COM</t>
+          <t>ZAHIDHERNANDEZ2309@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:37</t>
+          <t>02-03-2026 15:34:47</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2347,44 +2355,36 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-03-2026 04:44:49</t>
+          <t>03-03-2026 14:27:26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>04-03-2026 04:43:50</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26090522863860002129</t>
+          <t>26090522841560002101</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2402,34 +2402,34 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347757</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CAMILA NICOLE</t>
+          <t xml:space="preserve">ROSA MARIA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t xml:space="preserve">ARIAS </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6651370122</t>
+          <t>6643685663</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2470,22 +2470,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10-05-2012</t>
+          <t>15-06-1964</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CAMILANICOLEGAS@GMAIL.COM</t>
+          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:12</t>
+          <t>02-03-2026 19:40:27</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:16</t>
+          <t>02-03-2026 19:41:52</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26090522807480002050</t>
+          <t>26090522817500002070</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2551,12 +2551,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347808</t>
+          <t>347757</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89973</t>
+          <t>89922</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIZETH DANIELA</t>
+          <t>CAMILA NICOLE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2586,14 +2586,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6611720452</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CAMINO VIEJO A PEMEX</t>
-        </is>
-      </c>
+          <t>6651370122</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2601,32 +2597,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>04-01-2004</t>
+          <t>10-05-2012</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DG2940547@GMAIL.COM</t>
+          <t>CAMILANICOLEGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:35</t>
+          <t>02-03-2026 17:39:12</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2636,29 +2632,21 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:10</t>
+          <t>02-03-2026 17:40:16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:35:06</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2666,19 +2654,11 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26090522851370002111</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522807480002050</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -2698,12 +2678,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347875</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2713,17 +2693,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA MARIA </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS </t>
+          <t>CARDIEL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2733,7 +2713,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6643685663</t>
+          <t>6644873362</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2744,17 +2724,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-06-1964</t>
+          <t>17-05-2008</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DENISSE_PANEDERIA@GMAIL.COM</t>
+          <t>CARDIEL1708@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:27</t>
+          <t>03-03-2026 14:31:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2769,28 +2749,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:41:52</t>
+          <t>03-03-2026 14:33:16</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2801,14 +2781,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26090522817500002070</t>
+          <t>26090522841930002102</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2825,12 +2805,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348017</t>
+          <t>347808</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2840,17 +2820,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DANIELA ALEJANDRA</t>
+          <t>LIZETH DANIELA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BADUY</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2860,10 +2840,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6642812643</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6611720452</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A PEMEX</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2871,42 +2855,42 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-02-2010</t>
+          <t>04-01-2004</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>DANIELADIAZBAD@GMAIL.COM</t>
+          <t>DG2940547@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 11:57:43</t>
+          <t>02-03-2026 18:19:35</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 11:58:30</t>
+          <t>03-03-2026 17:37:10</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2914,13 +2898,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:35:06</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2928,14 +2920,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26090522838120002095</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26090522851370002111</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347861</t>
+          <t>348017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILSE </t>
+          <t>DANIELA ALEJANDRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">DIAZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>BADUY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6611286493</t>
+          <t>6642812643</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2998,17 +2998,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>08-12-1995</t>
+          <t>25-02-2010</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ILSE.CHH8@GMAIL.COM</t>
+          <t>DANIELADIAZBAD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:37</t>
+          <t>03-03-2026 11:57:43</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3023,28 +3023,28 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:15</t>
+          <t>03-03-2026 11:58:30</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26090522815680002066</t>
+          <t>26090522838120002095</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3079,12 +3079,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348063</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,17 +3094,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>MONICA ANDREA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CARDIEL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6644873362</t>
+          <t>6644795244</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3125,17 +3125,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>17-05-2008</t>
+          <t>29-10-2009</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CARDIEL1708@GMAIL.COM</t>
+          <t>MROSASG09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 14:31:39</t>
+          <t>05-03-2026 15:10:46</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 14:33:16</t>
+          <t>06-03-2026 15:13:58</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3182,11 +3182,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26090522841930002102</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26090522952140002207</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>399</t>
@@ -3341,12 +3349,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348722</t>
+          <t>348287</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90887</t>
+          <t>90452</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3356,17 +3364,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CARMEN LIZBETH</t>
+          <t>MARIA DOLORES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>REDONDO</t>
+          <t>ITURRIU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3376,12 +3384,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6611356413</t>
+          <t>6441033946</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C RUMOROSA</t>
+          <t xml:space="preserve">AV TRASNPENINSULAR </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3391,17 +3399,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04-05-1990</t>
+          <t>03-10-1963</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KEVENDANIEL101@GMAIL.COM</t>
+          <t>MARIODOLESITURRIU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-03-2026 15:17:47</t>
+          <t>03-03-2026 20:40:47</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3426,17 +3434,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>06-03-2026 15:07:57</t>
+          <t>03-03-2026 20:51:38</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>05-03-2026 15:22:33</t>
+          <t>03-03-2026 20:45:13</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3456,7 +3464,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26090522951900002206</t>
+          <t>26090522861560002128</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3480,12 +3488,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348717</t>
+          <t>347861</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90882</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3495,17 +3503,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MONICA ANDREA</t>
+          <t xml:space="preserve">ILSE </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3515,7 +3523,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6644795244</t>
+          <t>6611286493</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,17 +3534,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29-10-2009</t>
+          <t>08-12-1995</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MROSASG09@GMAIL.COM</t>
+          <t>ILSE.CHH8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-03-2026 15:10:46</t>
+          <t>02-03-2026 19:09:37</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3551,28 +3559,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-03-2026 15:13:58</t>
+          <t>02-03-2026 19:13:15</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3583,22 +3591,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26090522952140002207</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
-        </is>
-      </c>
+          <t>26090522815680002066</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348287</t>
+          <t>349159</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>91324</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>JANETH MONSERRATH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ITURRIU</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6441033946</t>
+          <t>6643499569</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV TRASNPENINSULAR </t>
+          <t>ROSARITO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3665,17 +3665,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-10-1963</t>
+          <t>25-02-1998</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MARIODOLESITURRIU@GMAIL.COM</t>
+          <t>MONSEJ584@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 20:40:47</t>
+          <t>07-03-2026 14:13:07</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:38</t>
+          <t>07-03-2026 14:20:27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-03-2026 20:45:13</t>
+          <t>07-03-2026 14:18:53</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26090522861560002128</t>
+          <t>26090522976000002231</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3742,24 +3742,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>349264</t>
+          <t>349296</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>91429</t>
+          <t>91461</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3769,32 +3769,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARIA DEL REFUGI</t>
+          <t xml:space="preserve">DIANA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NECOECHEA</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ZAMBRANO</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6611190907</t>
+          <t>5625561352</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C TECATE</t>
+          <t>BLEVD VILLAS DEL MAR 4128</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13-06-1986</t>
+          <t>24-05-1966</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MARIANECOECHEAZ13@GMAIL.COM</t>
+          <t>ALAAVARADOALVARADODIANAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>08-03-2026 14:44:16</t>
+          <t>09-03-2026 06:52:31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3824,32 +3824,32 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>08-03-2026 14:49:29</t>
+          <t>10-03-2026 07:27:36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>08-03-2026 14:48:54</t>
+          <t>10-03-2026 07:26:49</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3869,36 +3869,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26090522988160002237</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26090523043720002296</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>349159</t>
+          <t>349773</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>91938</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3908,17 +3916,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JANETH MONSERRATH</t>
+          <t xml:space="preserve">CATALINA DE JESUS </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>ALGANDAR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ZAMORA </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3928,7 +3936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6643499569</t>
+          <t>6647968582</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3943,52 +3951,52 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-02-1998</t>
+          <t>18-06-1982</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MONSEJ584@GMAIL.COM</t>
+          <t>CATHERINEALG18@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>07-03-2026 14:13:07</t>
+          <t>10-03-2026 08:44:54</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>07-03-2026 14:20:27</t>
+          <t>10-03-2026 08:51:47</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>07-03-2026 14:18:53</t>
+          <t>10-03-2026 08:50:42</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4008,36 +4016,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26090522976000002231</t>
+          <t>26090523045970002300</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Anton Omar  Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349296</t>
+          <t>349987</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91461</t>
+          <t>92152</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4047,99 +4055,87 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA </t>
+          <t xml:space="preserve">MARIA ESMERALDA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t xml:space="preserve">VALDEZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t xml:space="preserve">HERRERA </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6612872366</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15-08-2001</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>VALDEZMARES427@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:19:01</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:36:01</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>5625561352</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>BLEVD VILLAS DEL MAR 4128</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>24-05-1966</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>ALAAVARADOALVARADODIANAN@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>09-03-2026 06:52:31</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>10-03-2026 07:27:36</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>10-03-2026 07:26:49</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4147,22 +4143,18 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26090523043720002296</t>
+          <t>26090523068880002347</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4179,12 +4171,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349773</t>
+          <t>349264</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91938</t>
+          <t>91429</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4194,17 +4186,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CATALINA DE JESUS </t>
+          <t>MARIA DEL REFUGI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ALGANDAR</t>
+          <t>NECOECHEA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAMORA </t>
+          <t>ZAMBRANO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4214,12 +4206,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6647968582</t>
+          <t>6611190907</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROSARITO</t>
+          <t>C TECATE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4229,17 +4221,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-06-1982</t>
+          <t>13-06-1986</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CATHERINEALG18@ICLOUD.COM</t>
+          <t>MARIANECOECHEAZ13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-03-2026 08:44:54</t>
+          <t>08-03-2026 14:44:16</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4264,17 +4256,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-03-2026 08:51:47</t>
+          <t>08-03-2026 14:49:29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>10-03-2026 08:50:42</t>
+          <t>08-03-2026 14:48:54</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4294,7 +4286,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26090523045970002300</t>
+          <t>26090522988160002237</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4306,24 +4298,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>349987</t>
+          <t>349266</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92152</t>
+          <t>91431</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4333,17 +4325,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ESMERALDA </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALDEZ </t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA </t>
+          <t>NECOECHEA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4353,7 +4345,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6612872366</t>
+          <t>6611731894</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4364,17 +4356,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15-08-2001</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VALDEZMARES427@GMAIL.COM</t>
+          <t>FERNANDAVN162009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-03-2026 19:19:01</t>
+          <t>08-03-2026 14:51:42</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4399,12 +4391,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-03-2026 19:36:01</t>
+          <t>08-03-2026 14:53:01</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4421,14 +4413,10 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26090523068880002347</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26090522988200002238</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4437,24 +4425,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>349346</t>
+          <t>349992</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>92157</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4464,17 +4452,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ALEXIS GERARDO</t>
+          <t xml:space="preserve">ZULEY </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BATALLA</t>
+          <t xml:space="preserve">SANTANA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OLGUIN</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4484,47 +4472,43 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6634343460</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CAJOR SERVICIOS 10440</t>
-        </is>
-      </c>
+          <t>6611112856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>02-03-2002</t>
+          <t>22-11-2012</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALEXSOLGUIN337@GMAIL.COM</t>
+          <t>PENAPATRICIA905@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-03-2026 10:00:53</t>
+          <t>10-03-2026 19:28:07</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4534,29 +4518,21 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-03-2026 10:03:13</t>
+          <t>10-03-2026 19:31:36</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>09-03-2026 10:02:23</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4564,7 +4540,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26090523002810002251</t>
+          <t>26090523068610002346</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4588,12 +4564,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>349874</t>
+          <t>350098</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4603,17 +4579,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JENIFER ANABEL</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4623,7 +4599,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6611473621</t>
+          <t>6648569826</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4634,17 +4610,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>15-01-2010</t>
+          <t>21-05-2010</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JENIFERANABELALVAREZ@GMAIL.COM</t>
+          <t>CRUZGARCIAMARI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-03-2026 15:46:34</t>
+          <t>11-03-2026 13:01:47</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4669,12 +4645,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-03-2026 15:48:05</t>
+          <t>11-03-2026 13:03:26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4691,7 +4667,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26090523055630002327</t>
+          <t>26090523088080002373</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4715,12 +4691,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>349876</t>
+          <t>350164</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>92329</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,17 +4706,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ANGELICA GABRIELA</t>
+          <t xml:space="preserve">JUAN </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CARIÑO</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4750,33 +4726,33 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6641589128</t>
+          <t>6611958733</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>23-05-2010</t>
+          <t>05-06-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ANGELICAGABRIELA245@GMAIL.COM</t>
+          <t>JUANMANUEL663@OUTCLOUD.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-03-2026 15:50:40</t>
+          <t>11-03-2026 17:13:07</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4786,22 +4762,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-03-2026 15:52:42</t>
+          <t>11-03-2026 17:14:19</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4818,14 +4794,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26090523055740002328</t>
+          <t>26090523094660002389</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4842,12 +4818,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>349992</t>
+          <t>349776</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>92157</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4857,17 +4833,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZULEY </t>
+          <t xml:space="preserve">CINTHIA GISELLE </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTANA </t>
+          <t xml:space="preserve">IBARRA </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t xml:space="preserve">ALGANDAR </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4877,7 +4853,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6611112856</t>
+          <t>6631094746</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4888,17 +4864,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22-11-2012</t>
+          <t>21-12-2003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PENAPATRICIA905@GMAIL.COM</t>
+          <t>CINTHIAALGANDAR69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-03-2026 19:28:07</t>
+          <t>10-03-2026 08:56:07</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4923,7 +4899,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-03-2026 19:31:36</t>
+          <t>10-03-2026 08:59:09</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4945,7 +4921,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26090523068610002346</t>
+          <t>26090523046130002301</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4969,12 +4945,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>349266</t>
+          <t>350009</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>91431</t>
+          <t>92174</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4984,17 +4960,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NECOECHEA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5004,28 +4980,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6611731894</t>
+          <t>6641688071</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>19-04-1998</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>FERNANDAVN162009@GMAIL.COM</t>
+          <t>CARLOS.SANCHEZ.LOPEZ19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>08-03-2026 14:51:42</t>
+          <t>10-03-2026 20:15:38</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5050,18 +5026,18 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>08-03-2026 14:53:01</t>
+          <t>17-03-2026 20:15:31</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5072,7 +5048,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26090522988200002238</t>
+          <t>26090523272820002558</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5084,24 +5060,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Juan Lomeli Salcedo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>349776</t>
+          <t>350345</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5111,17 +5087,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CINTHIA GISELLE </t>
+          <t xml:space="preserve">ANGEL DAVID </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBARRA </t>
+          <t xml:space="preserve">OVANDO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALGANDAR </t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5131,28 +5107,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6631094746</t>
+          <t>6611355598</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21-12-2003</t>
+          <t>25-04-2011</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CINTHIAALGANDAR69@GMAIL.COM</t>
+          <t>ANGELDAVIDOVANDO69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-03-2026 08:56:07</t>
+          <t>12-03-2026 14:28:47</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5177,12 +5153,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-03-2026 08:59:09</t>
+          <t>12-03-2026 14:31:01</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5199,7 +5175,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26090523046130002301</t>
+          <t>26090523123540002419</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5223,12 +5199,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>350164</t>
+          <t>349346</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>92329</t>
+          <t>91511</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5238,17 +5214,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN </t>
+          <t>ALEXIS GERARDO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>BATALLA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5258,10 +5234,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6611958733</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6634343460</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CAJOR SERVICIOS 10440</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5269,32 +5249,32 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>05-06-2006</t>
+          <t>02-03-2002</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JUANMANUEL663@OUTCLOUD.COM</t>
+          <t>ALEXSOLGUIN337@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>11-03-2026 17:13:07</t>
+          <t>09-03-2026 10:00:53</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5304,21 +5284,29 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-03-2026 17:14:19</t>
+          <t>09-03-2026 10:03:13</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:02:23</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5326,7 +5314,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26090523094660002389</t>
+          <t>26090523002810002251</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5350,12 +5338,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>350081</t>
+          <t>351681</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>92246</t>
+          <t>93845</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5365,17 +5353,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR LEONARDO </t>
+          <t xml:space="preserve">ABRAHAM ISRAEL </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIOS </t>
+          <t xml:space="preserve">ESPINOSA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AGUIAR</t>
+          <t xml:space="preserve">MACIAS </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5385,10 +5373,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6647135005</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6644937393</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5396,56 +5388,64 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26-06-2010</t>
+          <t>03-03-1998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>RIOSAGUIAR@GMAIL.COM</t>
+          <t>ABRAHAM10ESPINOSSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>11-03-2026 11:36:57</t>
+          <t>17-03-2026 19:21:35</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>13-03-2026 13:31:09</t>
+          <t>17-03-2026 19:28:34</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:27:25</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5453,22 +5453,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26090523152510002451</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090523270130002556</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5485,12 +5477,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>350098</t>
+          <t>351458</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>92263</t>
+          <t>93622</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5500,17 +5492,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>FATIMA JERALDINE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5520,10 +5512,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6648569826</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>3111038971</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5531,17 +5527,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21-05-2010</t>
+          <t>14-05-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CRUZGARCIAMARI@GMAIL.COM</t>
+          <t>FATIMAJLG1405@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11-03-2026 13:01:47</t>
+          <t>17-03-2026 10:55:51</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5551,36 +5547,44 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>11-03-2026 13:03:26</t>
+          <t>17-03-2026 12:56:22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:55:53</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5588,36 +5592,44 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26090523088080002373</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26090523252140002538</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carolina Diaz Martinez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>350009</t>
+          <t>352460</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>92174</t>
+          <t>94624</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5627,17 +5639,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t xml:space="preserve">MARGARITA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BEZARES</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5647,28 +5659,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6641688071</t>
+          <t>6648555880</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19-04-1998</t>
+          <t>08-09-1963</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CARLOS.SANCHEZ.LOPEZ19@GMAIL.COM</t>
+          <t>BEZARESHERNADEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-03-2026 20:15:38</t>
+          <t>21-03-2026 08:31:37</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5693,12 +5705,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-03-2026 20:15:31</t>
+          <t>21-03-2026 08:41:53</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>20-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5715,7 +5727,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26090523272820002558</t>
+          <t>26090523388970002648</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5739,12 +5751,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>350345</t>
+          <t>351306</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>92509</t>
+          <t>93470</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5754,17 +5766,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL DAVID </t>
+          <t xml:space="preserve">BRUNO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVANDO </t>
+          <t>FURQUIM</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>FURQUIN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5774,7 +5786,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6611355598</t>
+          <t>6632065651</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5785,17 +5797,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>25-04-2011</t>
+          <t>01-03-2009</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ANGELDAVIDOVANDO69@GMAIL.COM</t>
+          <t>BRUNOFHEYSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>12-03-2026 14:28:47</t>
+          <t>16-03-2026 18:40:59</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5820,12 +5832,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>12-03-2026 14:31:01</t>
+          <t>16-03-2026 18:41:52</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -5842,7 +5854,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26090523123540002419</t>
+          <t>26090523231220002506</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5866,12 +5878,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>350352</t>
+          <t>348722</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>92516</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5881,17 +5893,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRANDA MICHELLE </t>
+          <t>CARMEN LIZBETH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>REDONDO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5901,10 +5913,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6642223351</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6611356413</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C RUMOROSA</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5912,56 +5928,64 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-10-2008</t>
+          <t>04-05-1990</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>MIRANDAANDRADE05@GMAIL.COM</t>
+          <t>KEVENDANIEL101@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>12-03-2026 14:57:05</t>
+          <t>05-03-2026 15:17:47</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>12-03-2026 14:59:07</t>
+          <t>06-03-2026 15:07:57</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:22:33</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5969,14 +5993,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26090523124220002420</t>
+          <t>26090522951900002206</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5993,12 +6017,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>350990</t>
+          <t>351535</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93154</t>
+          <t>93699</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6008,17 +6032,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ABIGAIL</t>
+          <t xml:space="preserve">RAUL </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CEJA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6028,7 +6052,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6647804341</t>
+          <t>6198300487</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6038,22 +6062,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>04-05-1997</t>
+          <t>17-03-2000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>FRANCOMARTINESABIGAIL@GMAIL.COM</t>
+          <t>RAUL3CEJA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-03-2026 08:07:12</t>
+          <t>17-03-2026 15:12:01</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6068,27 +6092,27 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-03-2026 08:08:56</t>
+          <t>17-03-2026 16:00:05</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>16-03-2026 08:08:22</t>
+          <t>17-03-2026 15:59:10</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6098,7 +6122,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6108,36 +6132,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26090523207810002477</t>
+          <t>26090523257610002547</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Carlos Abraham Mijares Fernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>351458</t>
+          <t>351579</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93622</t>
+          <t>93743</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6147,17 +6171,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FATIMA JERALDINE</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>JAYOVANA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GRAY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6167,14 +6191,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3111038971</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
+          <t>9096301617</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6182,17 +6202,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14-05-2003</t>
+          <t>01-01-1996</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FATIMAJLG1405@GMAIL.COM</t>
+          <t>TREX96.VG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>17-03-2026 10:55:51</t>
+          <t>17-03-2026 16:51:18</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6202,44 +6222,36 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17-03-2026 12:56:22</t>
+          <t>17-03-2026 16:53:16</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>17-03-2026 12:55:53</t>
-        </is>
-      </c>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6247,44 +6259,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26090523252140002538</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
-        </is>
-      </c>
+          <t>26090523259790002550</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Carolina Diaz Martinez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>351306</t>
+          <t>352719</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>94883</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6294,17 +6298,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO </t>
+          <t xml:space="preserve">AURELIA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FURQUIM</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FURQUIN</t>
+          <t>BRANBILA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6314,67 +6318,79 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6632065651</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6611171394</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HIDALGO10</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01-03-2009</t>
+          <t>11-08-1974</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BRUNOFHEYSE@GMAIL.COM</t>
+          <t>AZUSAN_74@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-03-2026 18:40:59</t>
+          <t>23-03-2026 10:55:26</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-03-2026 18:41:52</t>
+          <t>23-03-2026 11:03:56</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>23-03-2026 11:02:54</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6382,14 +6398,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26090523231220002506</t>
+          <t>26090523422540002683</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6406,12 +6422,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>351473</t>
+          <t>352948</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93637</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6421,17 +6437,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DILAR</t>
+          <t>SANDRA POLET</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HERNADEZ</t>
+          <t>TINOCO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6441,28 +6457,28 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6648159828</t>
+          <t>6644044263</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>29-02-1988</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ESCOBARHERNANDEZDILAN@GMAIL.COM</t>
+          <t>SANDRAGUTIERREZTINOCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17-03-2026 12:10:54</t>
+          <t>23-03-2026 19:22:04</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6477,28 +6493,28 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>17-03-2026 12:12:19</t>
+          <t>23-03-2026 20:15:00</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>23-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -6509,14 +6525,22 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26090523251210002535</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26090523447290002724</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6533,12 +6557,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>350259</t>
+          <t>352962</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>92423</t>
+          <t>95126</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6548,17 +6572,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ANGEL ISMAEL</t>
+          <t xml:space="preserve">DAMIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LAGUNAS</t>
+          <t xml:space="preserve">ESTRADA </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t xml:space="preserve">IÑIGUEZ </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6568,33 +6592,33 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6641752193</t>
+          <t>6645493128</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>07-03-2007</t>
+          <t>05-02-2009</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>AISMAELORGUNO@GMAIL.COM</t>
+          <t>DAMIENGOGO927@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>12-03-2026 07:11:20</t>
+          <t>23-03-2026 19:47:40</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -6604,22 +6628,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-03-2026 07:12:10</t>
+          <t>23-03-2026 19:49:32</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -6636,14 +6660,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26090523116100002404</t>
+          <t>26090523445830002723</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6660,12 +6684,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>351681</t>
+          <t>352463</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>93845</t>
+          <t>94627</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6675,99 +6699,87 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABRAHAM ISRAEL </t>
+          <t>DIANA GEORGINA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOSA </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACIAS </t>
+          <t>IÑIGUEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6644937393</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
+          <t>7025596271</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>03-03-1998</t>
+          <t>08-11-2013</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ABRAHAM10ESPINOSSA@GMAIL.COM</t>
+          <t>ESTRADAIÑIGUEZG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>17-03-2026 19:21:35</t>
+          <t>21-03-2026 08:43:57</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>17-03-2026 19:28:34</t>
+          <t>21-03-2026 08:49:52</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>17-03-2026 19:27:25</t>
-        </is>
-      </c>
+          <t>20-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6775,14 +6787,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26090523270130002556</t>
+          <t>26090523389150002649</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6799,12 +6811,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>351535</t>
+          <t>351813</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>93977</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6814,17 +6826,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAUL </t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CEJA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6834,14 +6846,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6198300487</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>ROSARITO</t>
-        </is>
-      </c>
+          <t>6611118707</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6849,64 +6857,56 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17-03-2000</t>
+          <t>16-01-2008</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>RAUL3CEJA@GMAIL.COM</t>
+          <t>BRRERRASURAREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17-03-2026 15:12:01</t>
+          <t>18-03-2026 13:13:11</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>17-03-2026 16:00:05</t>
+          <t>18-03-2026 13:14:18</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>17-03-2026 15:59:10</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6914,14 +6914,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26090523257610002547</t>
+          <t>26090523290860002575</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6938,12 +6938,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>351579</t>
+          <t>350259</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93743</t>
+          <t>92423</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6953,17 +6953,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>ANGEL ISMAEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JAYOVANA</t>
+          <t>LAGUNAS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GRAY</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9096301617</t>
+          <t>6641752193</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6984,22 +6984,22 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>01-01-1996</t>
+          <t>07-03-2007</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>TREX96.VG@GMAIL.COM</t>
+          <t>AISMAELORGUNO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>17-03-2026 16:51:18</t>
+          <t>12-03-2026 07:11:20</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -7009,28 +7009,28 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-03-2026 16:53:16</t>
+          <t>12-03-2026 07:12:10</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>16-06-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -7041,14 +7041,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26090523259790002550</t>
+          <t>26090523116100002404</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7065,12 +7065,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>351813</t>
+          <t>352810</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93977</t>
+          <t>94974</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7080,17 +7080,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>ALMA JULIANA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7100,67 +7100,79 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6611118707</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6611077248</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MACLOVIO HERRERA</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>16-01-2008</t>
+          <t>09-09-2003</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BRRERRASURAREZ@GMAIL.COM</t>
+          <t>AGIL080220@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-03-2026 13:13:11</t>
+          <t>23-03-2026 16:10:47</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-03-2026 13:14:18</t>
+          <t>23-03-2026 16:14:11</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:13:47</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7168,36 +7180,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26090523290860002575</t>
+          <t>26090523431450002700</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Anton Omar  Sanchez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>351461</t>
+          <t>352855</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93625</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7207,17 +7219,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JULISSA NOEMI</t>
+          <t>BRANDON</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>RANGEL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>COLLAZO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7227,67 +7239,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6676930667</t>
+          <t>6643372491</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ROSARITO</t>
+          <t>SAN IGNASIO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>02-03-2005</t>
+          <t>13-05-2000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CORRALESGUERRERO@GMAIL.COM</t>
+          <t>BRACOLLAZO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>17-03-2026 11:04:10</t>
+          <t>23-03-2026 17:25:27</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-03-2026 11:02:38</t>
+          <t>23-03-2026 19:05:16</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18-03-2026 11:01:57</t>
+          <t>23-03-2026 19:04:51</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7307,7 +7319,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26090523288760002570</t>
+          <t>26090523442860002718</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7317,34 +7329,34 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Lomeli Salcedo</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>351815</t>
+          <t>352725</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93979</t>
+          <t>94889</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7354,17 +7366,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">PABLO DANIEL </t>
+          <t xml:space="preserve">ANTONIA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7374,67 +7386,79 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6124414560</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6611146266</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>GUADALUPE VICTORIA 2</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>11-12-1999</t>
+          <t>13-06-1964</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRUJILLOMEZ@GMAIL.COM</t>
+          <t>SALAZARANTONI64@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18-03-2026 13:19:07</t>
+          <t>23-03-2026 11:08:26</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>18-03-2026 13:20:50</t>
+          <t>23-03-2026 11:10:35</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>23-03-2026 11:09:59</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7442,22 +7466,2686 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26090523291070002576</t>
+          <t>26090523422740002686</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>352858</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>95022</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AGUSTIN ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOMEZ </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NEGRETE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6646756982</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RIO EUFRA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>04-02-1995</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>AGUSTIN.GOMEZNEGRETE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:29:31</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:01:31</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:00:39</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26090523442640002717</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>JACQUELINE DOLORES MURILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Juan Lomeli Salcedo</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>354059</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>96223</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VICTOR MANUEL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUNA </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6643476048</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>09-04-2008</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LUBNACHAVEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>30-03-2026 06:19:45</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>30-03-2026 06:21:10</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26090523616990002927</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>354094</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>96258</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>YSAURY AVILENNE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LOPEZ GUERRA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6462587322</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CUERNAVACA 193</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>11-11-1989</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PAOVELL22DYC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:40:49</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:50:45</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:48:37</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26090523622160002938</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>352727</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>94891</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>JARED DANIEL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CORDOVA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>APARICIO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6642879331</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>01-05-2010</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CODOVAJARED17@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>23-03-2026 11:18:28</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>23-03-2026 11:19:37</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26090523422980002687</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>353228</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>95392</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REYES </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVO </t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>8991621913</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>MEXICALI 40</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>26-05-1986</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>PEDRO.REYES.OLIVO@OUTLOK.ES</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:43:26</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:10:56</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:10:37</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26090523545380002859</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Juan Lomeli Salcedo</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>353222</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>95386</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIDE NOHEMI </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUERRERO </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>8992251072</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>MEXICALI 40</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>24-11-1999</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NOHEMI.06MARTINEZ24@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:39:03</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:06:48</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:05:54</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26090523545110002858</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Juan Lomeli Salcedo</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>353996</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>96160</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NELY </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>URBINA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6615273738</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>11-09-1965</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>RUFINAVELAZQUEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>29-03-2026 10:19:06</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>29-03-2026 12:23:07</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26090523605530002920</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>354101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>96265</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>KAREN JAQUELLINE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CORONEL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NAVA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6647817546</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>04-04-2003</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CORONELNAVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:51:13</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:53:29</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26090523620710002933</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>353552</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>95716</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GETZEMANI</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6611966637</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE MARIA MORES </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>25-08-2001</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>GTZMNLPZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:35:11</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:45</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:10</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26090523533980002835</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>354220</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>96384</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6611165906</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>06-10-2006</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>PARRA20612@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:17:03</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:18:24</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26090523629590002948</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>349874</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>92039</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JENIFER ANABEL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JAUREGUI</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6611473621</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>15-01-2010</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>JENIFERANABELALVAREZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:46:34</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:48:05</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26090523055630002327</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>349876</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>92041</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ANGELICA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CARIÑO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6641589128</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>23-05-2010</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ANGELICAGABRIELA245@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:50:40</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:52:42</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26090523055740002328</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>351461</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>93625</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>JULISSA NOEMI</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>GUERRERO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6676930667</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>02-03-2005</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>CORRALESGUERRERO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>17-03-2026 11:04:10</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>18-03-2026 11:02:38</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>18-03-2026 11:01:57</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26090523288760002570</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>350081</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>92246</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTOR LEONARDO </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIOS </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AGUIAR</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6647135005</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>26-06-2010</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>RIOSAGUIAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>11-03-2026 11:36:57</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>13-03-2026 13:31:09</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26090523152510002451</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN SEGURA PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>350352</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>92516</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA MICHELLE </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6642223351</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>21-10-2008</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>MIRANDAANDRADE05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:57:05</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:59:07</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26090523124220002420</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>351815</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>93979</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PABLO DANIEL </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6124414560</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>11-12-1999</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>TRUJILLOMEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:19:07</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:20:50</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26090523291070002576</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>350990</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>93154</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6647804341</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ROSARITO</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>04-05-1997</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>FRANCOMARTINESABIGAIL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:07:12</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:08:56</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:08:22</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26090523207810002477</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Carlos Abraham Mijares Fernandez</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>351473</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>93637</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DILAR</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ESCOBAR</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>HERNADEZ</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6648159828</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>04-06-2010</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>ESCOBARHERNANDEZDILAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:10:54</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:12:19</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26090523251210002535</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>353665</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>95829</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRANDON NOE </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LORENZO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3349425981</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>03-12-2010</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>ORENZOBRANDON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>27-03-2026 05:10:00</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>27-03-2026 05:11:43</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26090523551070002866</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>353531</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>95695</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARGARITA </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6518428296</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>06-04-1961</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>HERNANDEZMEDINA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>26-03-2026 11:37:11</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>26-03-2026 11:39:31</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26090523532090002828</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
